--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>17600</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.819999992847443</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.769999980926514</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.805000007152557</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -62894,10 +62894,10 @@
         <v>17600</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.819999992847443</v>
+        <v>0.829999983310699</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.769999980926514</v>
+        <v>0.785000026226044</v>
       </c>
       <c r="E2719" t="n">
         <v>0.805000007152557</v>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -62932,6 +62932,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.829999983310699</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>84000</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.824999988079071</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.824999988079071</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="C2715" t="n">
         <v>0.839999973773956</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.810000002384186</v>
+        <v>0.839999973773956</v>
       </c>
       <c r="E2715" t="n">
         <v>0.839999973773956</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.810000002384186</v>
+        <v>0.839999973773956</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.829999983310699</v>
+        <v>0.839999973773956</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.805000007152557</v>
+        <v>0.810000002384186</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.824999988079071</v>
+        <v>0.839999973773956</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.819999992847443</v>
+        <v>0.810000002384186</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,19 +62842,19 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>6800</v>
+        <v>4000</v>
       </c>
       <c r="C2717" t="n">
-        <v>0.819999992847443</v>
+        <v>0.829999983310699</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.790000021457672</v>
+        <v>0.805000007152557</v>
       </c>
       <c r="E2717" t="n">
-        <v>0.790000021457672</v>
+        <v>0.824999988079071</v>
       </c>
       <c r="F2717" t="n">
         <v>0.819999992847443</v>
@@ -62865,19 +62865,19 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>10000</v>
+        <v>6800</v>
       </c>
       <c r="C2718" t="n">
         <v>0.819999992847443</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.785000026226044</v>
+        <v>0.790000021457672</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.795000016689301</v>
+        <v>0.790000021457672</v>
       </c>
       <c r="F2718" t="n">
         <v>0.819999992847443</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>17600</v>
+        <v>10000</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.829999983310699</v>
+        <v>0.819999992847443</v>
       </c>
       <c r="D2719" t="n">
         <v>0.785000026226044</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.805000007152557</v>
+        <v>0.795000016689301</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.829999983310699</v>
+        <v>0.819999992847443</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,19 +62911,19 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>0</v>
+        <v>17600</v>
       </c>
       <c r="C2720" t="n">
         <v>0.829999983310699</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.829999983310699</v>
+        <v>0.785000026226044</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.829999983310699</v>
+        <v>0.805000007152557</v>
       </c>
       <c r="F2720" t="n">
         <v>0.829999983310699</v>
@@ -62934,7 +62934,7 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
         <v>0</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>84000</v>
+        <v>0</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.899999976158142</v>
+        <v>0.829999983310699</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.824999988079071</v>
+        <v>0.829999983310699</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.824999988079071</v>
+        <v>0.829999983310699</v>
       </c>
       <c r="F2722" t="n">
-        <v>0.920000016689301</v>
+        <v>0.829999983310699</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>16800</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -63116,6 +63116,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="G2729" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="F2730"/>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -63254,6 +63254,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2735">
+      <c r="A2735" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2735" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2735" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F2735" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -63277,6 +63277,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F2736" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>18400</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -63316,7 +63316,9 @@
       <c r="E2737" t="n">
         <v>0.904999971389771</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.930000007152557</v>
+      </c>
       <c r="G2737" t="s">
         <v>7</v>
       </c>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -63323,6 +63323,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="F2738" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -63392,6 +63392,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2741">
+      <c r="A2741" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2741" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C2741" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D2741" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>0.930000007152557</v>
+      </c>
+      <c r="G2741" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>1.52042269706726</v>
+        <v>1.52042245864868</v>
       </c>
       <c r="H3" t="n">
         <v>2400</v>
@@ -514,7 +514,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G5" t="n">
-        <v>1.43918442726135</v>
+        <v>1.43918418884277</v>
       </c>
       <c r="H5" t="n">
         <v>10800</v>
@@ -572,7 +572,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G7" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H7" t="n">
         <v>3600</v>
@@ -601,7 +601,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G9" t="n">
-        <v>1.39372062683105</v>
+        <v>1.39372074604034</v>
       </c>
       <c r="H9" t="n">
         <v>1600</v>
@@ -659,7 +659,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G10" t="n">
-        <v>1.39372062683105</v>
+        <v>1.39372074604034</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G11" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H11" t="n">
         <v>2400</v>
@@ -717,7 +717,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G13" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G14" t="n">
-        <v>1.33931362628937</v>
+        <v>1.33931350708008</v>
       </c>
       <c r="H14" t="n">
         <v>2800</v>
@@ -804,7 +804,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G15" t="n">
-        <v>1.31919014453888</v>
+        <v>1.31919026374817</v>
       </c>
       <c r="H15" t="n">
         <v>4000</v>
@@ -833,7 +833,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G16" t="n">
-        <v>1.33856809139252</v>
+        <v>1.33856821060181</v>
       </c>
       <c r="H16" t="n">
         <v>1600</v>
@@ -891,7 +891,7 @@
         <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30428409576416</v>
+        <v>1.30428397655487</v>
       </c>
       <c r="H18" t="n">
         <v>8800</v>
@@ -920,7 +920,7 @@
         <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.30428409576416</v>
+        <v>1.30428397655487</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.26701891422272</v>
+        <v>1.26701867580414</v>
       </c>
       <c r="H20" t="n">
         <v>5600</v>
@@ -978,7 +978,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>1.29981231689453</v>
+        <v>1.29981219768524</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.27447187900543</v>
+        <v>1.27447199821472</v>
       </c>
       <c r="H22" t="n">
         <v>1200</v>
@@ -1036,7 +1036,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G23" t="n">
-        <v>1.22379112243652</v>
+        <v>1.22379100322723</v>
       </c>
       <c r="H23" t="n">
         <v>5600</v>
@@ -1065,7 +1065,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G24" t="n">
-        <v>1.22379112243652</v>
+        <v>1.22379100322723</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G25" t="n">
-        <v>1.190997838974</v>
+        <v>1.19099771976471</v>
       </c>
       <c r="H25" t="n">
         <v>2800</v>
@@ -1181,7 +1181,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G28" t="n">
-        <v>0.991255879402161</v>
+        <v>0.991256058216095</v>
       </c>
       <c r="H28" t="n">
         <v>4000</v>
@@ -1239,7 +1239,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>0.961443722248077</v>
+        <v>0.961443603038788</v>
       </c>
       <c r="H30" t="n">
         <v>2400</v>
@@ -1268,7 +1268,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>0.976349771022797</v>
+        <v>0.976349890232086</v>
       </c>
       <c r="H31" t="n">
         <v>4800</v>
@@ -1326,7 +1326,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>1.01734161376953</v>
+        <v>1.01734149456024</v>
       </c>
       <c r="H33" t="n">
         <v>4000</v>
@@ -1384,7 +1384,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G35" t="n">
-        <v>1.01510572433472</v>
+        <v>1.01510560512543</v>
       </c>
       <c r="H35" t="n">
         <v>4400</v>
@@ -1413,7 +1413,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G36" t="n">
-        <v>0.995727717876434</v>
+        <v>0.995727837085724</v>
       </c>
       <c r="H36" t="n">
         <v>2000</v>
@@ -1442,7 +1442,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G37" t="n">
-        <v>1.01212453842163</v>
+        <v>1.01212441921234</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1471,7 +1471,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G38" t="n">
-        <v>1.02106809616089</v>
+        <v>1.02106821537018</v>
       </c>
       <c r="H38" t="n">
         <v>400</v>
@@ -1500,7 +1500,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G39" t="n">
-        <v>1.02106809616089</v>
+        <v>1.02106821537018</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1529,7 +1529,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G40" t="n">
-        <v>1.02106809616089</v>
+        <v>1.02106821537018</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G41" t="n">
-        <v>1.02106809616089</v>
+        <v>1.02106821537018</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G44" t="n">
-        <v>0.983802795410156</v>
+        <v>0.983802855014801</v>
       </c>
       <c r="H44" t="n">
         <v>7200</v>
@@ -1674,7 +1674,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>0.976349771022797</v>
+        <v>0.976349890232086</v>
       </c>
       <c r="H45" t="n">
         <v>3600</v>
@@ -1703,7 +1703,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G46" t="n">
-        <v>0.983802795410156</v>
+        <v>0.983802855014801</v>
       </c>
       <c r="H46" t="n">
         <v>5600</v>
@@ -1732,7 +1732,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>0.976349771022797</v>
+        <v>0.976349890232086</v>
       </c>
       <c r="H47" t="n">
         <v>400</v>
@@ -1761,7 +1761,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G48" t="n">
-        <v>0.976349771022797</v>
+        <v>0.976349890232086</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G49" t="n">
-        <v>0.994237124919891</v>
+        <v>0.994237184524536</v>
       </c>
       <c r="H49" t="n">
         <v>2400</v>
@@ -1819,7 +1819,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G50" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H50" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>0.953990638256073</v>
+        <v>0.953990757465363</v>
       </c>
       <c r="H51" t="n">
         <v>8400</v>
@@ -1877,7 +1877,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G52" t="n">
-        <v>0.953990638256073</v>
+        <v>0.953990757465363</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>0.961443722248077</v>
+        <v>0.961443603038788</v>
       </c>
       <c r="H53" t="n">
         <v>18800</v>
@@ -1935,7 +1935,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G54" t="n">
-        <v>0.967406034469604</v>
+        <v>0.967406153678894</v>
       </c>
       <c r="H54" t="n">
         <v>7200</v>
@@ -1964,7 +1964,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H55" t="n">
         <v>800</v>
@@ -1993,7 +1993,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G56" t="n">
-        <v>0.968151569366455</v>
+        <v>0.96815150976181</v>
       </c>
       <c r="H56" t="n">
         <v>1200</v>
@@ -2022,7 +2022,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G57" t="n">
-        <v>0.968151569366455</v>
+        <v>0.96815150976181</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G58" t="n">
-        <v>0.95026421546936</v>
+        <v>0.950264096260071</v>
       </c>
       <c r="H58" t="n">
         <v>400</v>
@@ -2080,7 +2080,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>0.946537554264069</v>
+        <v>0.946537435054779</v>
       </c>
       <c r="H59" t="n">
         <v>400</v>
@@ -2109,7 +2109,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>0.961443722248077</v>
+        <v>0.961443603038788</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G61" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H61" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H62" t="n">
         <v>2400</v>
@@ -2196,7 +2196,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G63" t="n">
-        <v>1.05833327770233</v>
+        <v>1.05833339691162</v>
       </c>
       <c r="H63" t="n">
         <v>28400</v>
@@ -2254,7 +2254,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G65" t="n">
-        <v>0.991255879402161</v>
+        <v>0.991256058216095</v>
       </c>
       <c r="H65" t="n">
         <v>7200</v>
@@ -2283,7 +2283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.991255879402161</v>
+        <v>0.991256058216095</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H67" t="n">
         <v>6000</v>
@@ -2341,7 +2341,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H68" t="n">
         <v>4800</v>
@@ -2370,7 +2370,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G69" t="n">
-        <v>0.969642162322998</v>
+        <v>0.969642043113708</v>
       </c>
       <c r="H69" t="n">
         <v>6400</v>
@@ -2399,7 +2399,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G70" t="n">
-        <v>0.958462417125702</v>
+        <v>0.958462536334991</v>
       </c>
       <c r="H70" t="n">
         <v>8400</v>
@@ -2428,7 +2428,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>0.961443722248077</v>
+        <v>0.961443603038788</v>
       </c>
       <c r="H71" t="n">
         <v>24800</v>
@@ -2457,7 +2457,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H72" t="n">
         <v>6000</v>
@@ -2486,7 +2486,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G73" t="n">
-        <v>0.940575122833252</v>
+        <v>0.940575242042542</v>
       </c>
       <c r="H73" t="n">
         <v>2400</v>
@@ -2515,7 +2515,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H74" t="n">
         <v>8000</v>
@@ -2544,7 +2544,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>0.946537554264069</v>
+        <v>0.946537435054779</v>
       </c>
       <c r="H75" t="n">
         <v>17200</v>
@@ -2573,7 +2573,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G76" t="n">
-        <v>0.932376861572266</v>
+        <v>0.932376801967621</v>
       </c>
       <c r="H76" t="n">
         <v>13200</v>
@@ -2602,7 +2602,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G77" t="n">
-        <v>0.924178421497345</v>
+        <v>0.9241783618927</v>
       </c>
       <c r="H77" t="n">
         <v>4800</v>
@@ -2660,7 +2660,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G79" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H79" t="n">
         <v>27200</v>
@@ -2747,7 +2747,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G82" t="n">
-        <v>0.943556427955627</v>
+        <v>0.943556487560272</v>
       </c>
       <c r="H82" t="n">
         <v>7200</v>
@@ -2776,7 +2776,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>0.912998855113983</v>
+        <v>0.912998795509338</v>
       </c>
       <c r="H83" t="n">
         <v>15600</v>
@@ -2805,7 +2805,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G84" t="n">
-        <v>0.983802795410156</v>
+        <v>0.983802855014801</v>
       </c>
       <c r="H84" t="n">
         <v>51600</v>
@@ -2834,7 +2834,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G85" t="n">
-        <v>0.998709082603455</v>
+        <v>0.99870902299881</v>
       </c>
       <c r="H85" t="n">
         <v>12000</v>
@@ -2950,7 +2950,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G89" t="n">
-        <v>0.991255879402161</v>
+        <v>0.991256058216095</v>
       </c>
       <c r="H89" t="n">
         <v>30000</v>
@@ -2979,7 +2979,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>0.983325898647308</v>
+        <v>0.983325839042664</v>
       </c>
       <c r="H90" t="n">
         <v>14400</v>
@@ -3008,7 +3008,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G91" t="n">
-        <v>0.996013998985291</v>
+        <v>0.996014058589935</v>
       </c>
       <c r="H91" t="n">
         <v>8400</v>
@@ -3037,7 +3037,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G92" t="n">
-        <v>1.03725028038025</v>
+        <v>1.03725016117096</v>
       </c>
       <c r="H92" t="n">
         <v>7600</v>
@@ -3095,7 +3095,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G94" t="n">
-        <v>1.04438734054565</v>
+        <v>1.04438722133636</v>
       </c>
       <c r="H94" t="n">
         <v>1200</v>
@@ -3124,7 +3124,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G95" t="n">
-        <v>1.0102881193161</v>
+        <v>1.01028800010681</v>
       </c>
       <c r="H95" t="n">
         <v>10400</v>
@@ -3182,7 +3182,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G97" t="n">
-        <v>1.01187407970428</v>
+        <v>1.011873960495</v>
       </c>
       <c r="H97" t="n">
         <v>400</v>
@@ -3211,7 +3211,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G98" t="n">
-        <v>1.01187407970428</v>
+        <v>1.011873960495</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G100" t="n">
-        <v>0.990462899208069</v>
+        <v>0.990462839603424</v>
       </c>
       <c r="H100" t="n">
         <v>13200</v>
@@ -3298,7 +3298,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G101" t="n">
-        <v>0.957156836986542</v>
+        <v>0.957156777381897</v>
       </c>
       <c r="H101" t="n">
         <v>43600</v>
@@ -3327,7 +3327,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G102" t="n">
-        <v>0.947640717029572</v>
+        <v>0.947640657424927</v>
       </c>
       <c r="H102" t="n">
         <v>25200</v>
@@ -3356,7 +3356,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G103" t="n">
-        <v>0.947640717029572</v>
+        <v>0.947640657424927</v>
       </c>
       <c r="H103" t="n">
         <v>400</v>
@@ -3385,7 +3385,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G104" t="n">
-        <v>0.947640717029572</v>
+        <v>0.947640657424927</v>
       </c>
       <c r="H104" t="n">
         <v>6400</v>
@@ -3443,7 +3443,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G106" t="n">
-        <v>0.919885516166687</v>
+        <v>0.919885456562042</v>
       </c>
       <c r="H106" t="n">
         <v>7600</v>
@@ -3472,7 +3472,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G107" t="n">
-        <v>0.919885516166687</v>
+        <v>0.919885456562042</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G108" t="n">
-        <v>0.919885516166687</v>
+        <v>0.919885456562042</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G111" t="n">
-        <v>0.919885516166687</v>
+        <v>0.919885456562042</v>
       </c>
       <c r="H111" t="n">
         <v>800</v>
@@ -3617,7 +3617,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G112" t="n">
-        <v>0.919885516166687</v>
+        <v>0.919885456562042</v>
       </c>
       <c r="H112" t="n">
         <v>4800</v>
@@ -3646,7 +3646,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G113" t="n">
-        <v>0.919885516166687</v>
+        <v>0.919885456562042</v>
       </c>
       <c r="H113" t="n">
         <v>1200</v>
@@ -3675,7 +3675,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G114" t="n">
-        <v>0.903232455253601</v>
+        <v>0.903232395648956</v>
       </c>
       <c r="H114" t="n">
         <v>19200</v>
@@ -3704,7 +3704,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G115" t="n">
-        <v>0.904025375843048</v>
+        <v>0.904025435447693</v>
       </c>
       <c r="H115" t="n">
         <v>800</v>
@@ -3733,7 +3733,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G116" t="n">
-        <v>0.911955416202545</v>
+        <v>0.911955535411835</v>
       </c>
       <c r="H116" t="n">
         <v>4400</v>
@@ -3762,7 +3762,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G117" t="n">
-        <v>0.911955416202545</v>
+        <v>0.911955535411835</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G118" t="n">
-        <v>0.884993255138397</v>
+        <v>0.884993314743042</v>
       </c>
       <c r="H118" t="n">
         <v>4800</v>
@@ -3820,7 +3820,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G119" t="n">
-        <v>0.915920436382294</v>
+        <v>0.915920495986938</v>
       </c>
       <c r="H119" t="n">
         <v>2000</v>
@@ -3849,7 +3849,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>0.915920436382294</v>
+        <v>0.915920495986938</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>0.915920436382294</v>
+        <v>0.915920495986938</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G122" t="n">
-        <v>0.864375174045563</v>
+        <v>0.864375233650208</v>
       </c>
       <c r="H122" t="n">
         <v>59600</v>
@@ -3965,7 +3965,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>0.824724912643433</v>
+        <v>0.824724972248077</v>
       </c>
       <c r="H124" t="n">
         <v>2800</v>
@@ -3994,7 +3994,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G125" t="n">
-        <v>0.753354489803314</v>
+        <v>0.753354549407959</v>
       </c>
       <c r="H125" t="n">
         <v>19200</v>
@@ -4023,7 +4023,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>0.796969771385193</v>
+        <v>0.796969711780548</v>
       </c>
       <c r="H126" t="n">
         <v>42400</v>
@@ -4052,7 +4052,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G127" t="n">
-        <v>0.800934851169586</v>
+        <v>0.800934791564941</v>
       </c>
       <c r="H127" t="n">
         <v>400</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.800934851169586</v>
+        <v>0.800934791564941</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G130" t="n">
-        <v>0.753354489803314</v>
+        <v>0.753354549407959</v>
       </c>
       <c r="H130" t="n">
         <v>1600</v>
@@ -4197,7 +4197,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G132" t="n">
-        <v>0.729564368724823</v>
+        <v>0.729564428329468</v>
       </c>
       <c r="H132" t="n">
         <v>2000</v>
@@ -4255,7 +4255,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G134" t="n">
-        <v>0.80252081155777</v>
+        <v>0.802520751953125</v>
       </c>
       <c r="H134" t="n">
         <v>18000</v>
@@ -4371,7 +4371,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>0.823931932449341</v>
+        <v>0.823931992053986</v>
       </c>
       <c r="H138" t="n">
         <v>2400</v>
@@ -4400,7 +4400,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G139" t="n">
-        <v>0.823931932449341</v>
+        <v>0.823931992053986</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G140" t="n">
-        <v>0.828689873218536</v>
+        <v>0.828689932823181</v>
       </c>
       <c r="H140" t="n">
         <v>8000</v>
@@ -4458,7 +4458,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G141" t="n">
-        <v>0.831861972808838</v>
+        <v>0.831862032413483</v>
       </c>
       <c r="H141" t="n">
         <v>4800</v>
@@ -4487,7 +4487,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>0.83265495300293</v>
+        <v>0.832655012607574</v>
       </c>
       <c r="H142" t="n">
         <v>2000</v>
@@ -4516,7 +4516,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G143" t="n">
-        <v>0.83979195356369</v>
+        <v>0.839792013168335</v>
       </c>
       <c r="H143" t="n">
         <v>90800</v>
@@ -4545,7 +4545,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G144" t="n">
-        <v>0.835034012794495</v>
+        <v>0.835034072399139</v>
       </c>
       <c r="H144" t="n">
         <v>11600</v>
@@ -4574,7 +4574,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G145" t="n">
-        <v>0.835034012794495</v>
+        <v>0.835034072399139</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G146" t="n">
-        <v>0.835034012794495</v>
+        <v>0.835034072399139</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>0.835034012794495</v>
+        <v>0.835034072399139</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G148" t="n">
-        <v>0.851687073707581</v>
+        <v>0.851687014102936</v>
       </c>
       <c r="H148" t="n">
         <v>2000</v>
@@ -4748,7 +4748,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G151" t="n">
-        <v>0.808864831924438</v>
+        <v>0.808864772319794</v>
       </c>
       <c r="H151" t="n">
         <v>5600</v>
@@ -4777,7 +4777,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>0.808864831924438</v>
+        <v>0.808864772319794</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G153" t="n">
-        <v>0.808864831924438</v>
+        <v>0.808864772319794</v>
       </c>
       <c r="H153" t="n">
         <v>2000</v>
@@ -4835,7 +4835,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>0.808864831924438</v>
+        <v>0.808864772319794</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>0.824724912643433</v>
+        <v>0.824724972248077</v>
       </c>
       <c r="H155" t="n">
         <v>5600</v>
@@ -4893,7 +4893,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>0.824724912643433</v>
+        <v>0.824724972248077</v>
       </c>
       <c r="H156" t="n">
         <v>2400</v>
@@ -4922,7 +4922,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G157" t="n">
-        <v>0.808071851730347</v>
+        <v>0.808071792125702</v>
       </c>
       <c r="H157" t="n">
         <v>1600</v>
@@ -5096,7 +5096,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G163" t="n">
-        <v>0.747010469436646</v>
+        <v>0.747010409832001</v>
       </c>
       <c r="H163" t="n">
         <v>2000</v>
@@ -5125,7 +5125,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G164" t="n">
-        <v>0.747010469436646</v>
+        <v>0.747010409832001</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G165" t="n">
-        <v>0.761284530162811</v>
+        <v>0.761284589767456</v>
       </c>
       <c r="H165" t="n">
         <v>2800</v>
@@ -5241,7 +5241,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G168" t="n">
-        <v>0.753354489803314</v>
+        <v>0.753354549407959</v>
       </c>
       <c r="H168" t="n">
         <v>2000</v>
@@ -5299,7 +5299,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G170" t="n">
-        <v>0.751768529415131</v>
+        <v>0.751768469810486</v>
       </c>
       <c r="H170" t="n">
         <v>13600</v>
@@ -5502,7 +5502,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G177" t="n">
-        <v>0.794590771198273</v>
+        <v>0.794590711593628</v>
       </c>
       <c r="H177" t="n">
         <v>28400</v>
@@ -5734,7 +5734,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G185" t="n">
-        <v>0.761284530162811</v>
+        <v>0.761284589767456</v>
       </c>
       <c r="H185" t="n">
         <v>4800</v>
@@ -5763,7 +5763,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G186" t="n">
-        <v>0.717669188976288</v>
+        <v>0.717669248580933</v>
       </c>
       <c r="H186" t="n">
         <v>10800</v>
@@ -5821,7 +5821,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G188" t="n">
-        <v>0.713704288005829</v>
+        <v>0.713704228401184</v>
       </c>
       <c r="H188" t="n">
         <v>86400</v>
@@ -5879,7 +5879,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G190" t="n">
-        <v>0.689121127128601</v>
+        <v>0.689121186733246</v>
       </c>
       <c r="H190" t="n">
         <v>10000</v>
@@ -5908,7 +5908,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G191" t="n">
-        <v>0.689121127128601</v>
+        <v>0.689121186733246</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G195" t="n">
-        <v>0.634403824806213</v>
+        <v>0.634403884410858</v>
       </c>
       <c r="H195" t="n">
         <v>15200</v>
@@ -6227,7 +6227,7 @@
         <v>0.72299998998642</v>
       </c>
       <c r="G202" t="n">
-        <v>0.573342382907867</v>
+        <v>0.573342442512512</v>
       </c>
       <c r="H202" t="n">
         <v>28400</v>
@@ -6285,7 +6285,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>0.555499851703644</v>
+        <v>0.555499792098999</v>
       </c>
       <c r="H204" t="n">
         <v>38000</v>
@@ -6372,7 +6372,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G207" t="n">
-        <v>0.547173321247101</v>
+        <v>0.547173261642456</v>
       </c>
       <c r="H207" t="n">
         <v>53600</v>
@@ -6401,7 +6401,7 @@
         <v>0.722500026226044</v>
       </c>
       <c r="G208" t="n">
-        <v>0.572945892810822</v>
+        <v>0.572945952415466</v>
       </c>
       <c r="H208" t="n">
         <v>74800</v>
@@ -6604,7 +6604,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G215" t="n">
-        <v>0.569377481937408</v>
+        <v>0.569377362728119</v>
       </c>
       <c r="H215" t="n">
         <v>22400</v>
@@ -6662,7 +6662,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G217" t="n">
-        <v>0.547173321247101</v>
+        <v>0.547173261642456</v>
       </c>
       <c r="H217" t="n">
         <v>24400</v>
@@ -6720,7 +6720,7 @@
         <v>0.715499997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>0.567394852638245</v>
+        <v>0.567394912242889</v>
       </c>
       <c r="H219" t="n">
         <v>18000</v>
@@ -6749,7 +6749,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G220" t="n">
-        <v>0.539243221282959</v>
+        <v>0.539243280887604</v>
       </c>
       <c r="H220" t="n">
         <v>26400</v>
@@ -6836,7 +6836,7 @@
         <v>0.689499974250793</v>
       </c>
       <c r="G223" t="n">
-        <v>0.54677677154541</v>
+        <v>0.546776711940765</v>
       </c>
       <c r="H223" t="n">
         <v>800</v>
@@ -6923,7 +6923,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G226" t="n">
-        <v>0.515453100204468</v>
+        <v>0.515453040599823</v>
       </c>
       <c r="H226" t="n">
         <v>62800</v>
@@ -6981,7 +6981,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>0.513867139816284</v>
+        <v>0.513867080211639</v>
       </c>
       <c r="H228" t="n">
         <v>34800</v>
@@ -7010,7 +7010,7 @@
         <v>0.625500023365021</v>
       </c>
       <c r="G229" t="n">
-        <v>0.496024489402771</v>
+        <v>0.496024459600449</v>
       </c>
       <c r="H229" t="n">
         <v>18000</v>
@@ -7068,7 +7068,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G231" t="n">
-        <v>0.551138281822205</v>
+        <v>0.551138341426849</v>
       </c>
       <c r="H231" t="n">
         <v>14800</v>
@@ -7126,7 +7126,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G233" t="n">
-        <v>0.539243221282959</v>
+        <v>0.539243280887604</v>
       </c>
       <c r="H233" t="n">
         <v>20800</v>
@@ -7155,7 +7155,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G234" t="n">
-        <v>0.531313180923462</v>
+        <v>0.531313240528107</v>
       </c>
       <c r="H234" t="n">
         <v>4800</v>
@@ -7184,7 +7184,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G235" t="n">
-        <v>0.531313180923462</v>
+        <v>0.531313240528107</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G237" t="n">
-        <v>0.551138281822205</v>
+        <v>0.551138341426849</v>
       </c>
       <c r="H237" t="n">
         <v>2800</v>
@@ -7271,7 +7271,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G238" t="n">
-        <v>0.527348160743713</v>
+        <v>0.527348220348358</v>
       </c>
       <c r="H238" t="n">
         <v>9200</v>
@@ -7358,7 +7358,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G241" t="n">
-        <v>0.539243221282959</v>
+        <v>0.539243280887604</v>
       </c>
       <c r="H241" t="n">
         <v>13200</v>
@@ -7387,7 +7387,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G242" t="n">
-        <v>0.539243221282959</v>
+        <v>0.539243280887604</v>
       </c>
       <c r="H242" t="n">
         <v>8000</v>
@@ -7619,7 +7619,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G250" t="n">
-        <v>0.551931262016296</v>
+        <v>0.551931321620941</v>
       </c>
       <c r="H250" t="n">
         <v>72000</v>
@@ -7706,7 +7706,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G253" t="n">
-        <v>0.615371763706207</v>
+        <v>0.615371704101562</v>
       </c>
       <c r="H253" t="n">
         <v>42000</v>
@@ -7822,7 +7822,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G257" t="n">
-        <v>0.665330946445465</v>
+        <v>0.66533100605011</v>
       </c>
       <c r="H257" t="n">
         <v>88400</v>
@@ -7880,7 +7880,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>0.777144730091095</v>
+        <v>0.77714467048645</v>
       </c>
       <c r="H259" t="n">
         <v>194400</v>
@@ -7996,7 +7996,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G263" t="n">
-        <v>0.80727881193161</v>
+        <v>0.807278871536255</v>
       </c>
       <c r="H263" t="n">
         <v>35600</v>
@@ -8025,7 +8025,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>0.796969771385193</v>
+        <v>0.796969711780548</v>
       </c>
       <c r="H264" t="n">
         <v>3600</v>
@@ -8054,7 +8054,7 @@
         <v>1.00699996948242</v>
       </c>
       <c r="G265" t="n">
-        <v>0.798555791378021</v>
+        <v>0.798555672168732</v>
       </c>
       <c r="H265" t="n">
         <v>2000</v>
@@ -8083,7 +8083,7 @@
         <v>1.00699996948242</v>
       </c>
       <c r="G266" t="n">
-        <v>0.798555791378021</v>
+        <v>0.798555672168732</v>
       </c>
       <c r="H266" t="n">
         <v>6000</v>
@@ -8112,7 +8112,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G267" t="n">
-        <v>0.800934851169586</v>
+        <v>0.800934791564941</v>
       </c>
       <c r="H267" t="n">
         <v>14000</v>
@@ -8141,7 +8141,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G268" t="n">
-        <v>0.778334200382233</v>
+        <v>0.778334140777588</v>
       </c>
       <c r="H268" t="n">
         <v>4400</v>
@@ -8228,7 +8228,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>0.777144730091095</v>
+        <v>0.77714467048645</v>
       </c>
       <c r="H271" t="n">
         <v>4800</v>
@@ -8344,7 +8344,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>0.777144730091095</v>
+        <v>0.77714467048645</v>
       </c>
       <c r="H275" t="n">
         <v>7200</v>
@@ -8402,7 +8402,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G277" t="n">
-        <v>0.768421649932861</v>
+        <v>0.768421590328217</v>
       </c>
       <c r="H277" t="n">
         <v>1200</v>
@@ -8431,7 +8431,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G278" t="n">
-        <v>0.761284530162811</v>
+        <v>0.761284589767456</v>
       </c>
       <c r="H278" t="n">
         <v>13200</v>
@@ -8605,7 +8605,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G284" t="n">
-        <v>0.754147529602051</v>
+        <v>0.754147469997406</v>
       </c>
       <c r="H284" t="n">
         <v>17600</v>
@@ -8692,7 +8692,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G287" t="n">
-        <v>0.666123926639557</v>
+        <v>0.666123986244202</v>
       </c>
       <c r="H287" t="n">
         <v>27200</v>
@@ -8750,7 +8750,7 @@
         <v>0.800499975681305</v>
       </c>
       <c r="G289" t="n">
-        <v>0.634800255298615</v>
+        <v>0.634800314903259</v>
       </c>
       <c r="H289" t="n">
         <v>12800</v>
@@ -8779,7 +8779,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G290" t="n">
-        <v>0.642333805561066</v>
+        <v>0.64233386516571</v>
       </c>
       <c r="H290" t="n">
         <v>23200</v>
@@ -8808,7 +8808,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G291" t="n">
-        <v>0.653435945510864</v>
+        <v>0.653435885906219</v>
       </c>
       <c r="H291" t="n">
         <v>9200</v>
@@ -8837,7 +8837,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G292" t="n">
-        <v>0.662158966064453</v>
+        <v>0.662158906459808</v>
       </c>
       <c r="H292" t="n">
         <v>8000</v>
@@ -8866,7 +8866,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G293" t="n">
-        <v>0.664538025856018</v>
+        <v>0.664537966251373</v>
       </c>
       <c r="H293" t="n">
         <v>14400</v>
@@ -8895,7 +8895,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G294" t="n">
-        <v>0.646298825740814</v>
+        <v>0.646298885345459</v>
       </c>
       <c r="H294" t="n">
         <v>14800</v>
@@ -8953,7 +8953,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G296" t="n">
-        <v>0.65819388628006</v>
+        <v>0.658193945884705</v>
       </c>
       <c r="H296" t="n">
         <v>19200</v>
@@ -9011,7 +9011,7 @@
         <v>0.888999998569489</v>
       </c>
       <c r="G298" t="n">
-        <v>0.70498126745224</v>
+        <v>0.704981207847595</v>
       </c>
       <c r="H298" t="n">
         <v>102400</v>
@@ -9040,7 +9040,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G299" t="n">
-        <v>0.674054026603699</v>
+        <v>0.674053966999054</v>
       </c>
       <c r="H299" t="n">
         <v>47200</v>
@@ -9127,7 +9127,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G302" t="n">
-        <v>0.672468066215515</v>
+        <v>0.67246800661087</v>
       </c>
       <c r="H302" t="n">
         <v>10000</v>
@@ -9156,7 +9156,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G303" t="n">
-        <v>0.674054026603699</v>
+        <v>0.674053966999054</v>
       </c>
       <c r="H303" t="n">
         <v>6000</v>
@@ -9243,7 +9243,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G306" t="n">
-        <v>0.65819388628006</v>
+        <v>0.658193945884705</v>
       </c>
       <c r="H306" t="n">
         <v>12800</v>
@@ -9272,7 +9272,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G307" t="n">
-        <v>0.66295200586319</v>
+        <v>0.662951946258545</v>
       </c>
       <c r="H307" t="n">
         <v>5200</v>
@@ -9301,7 +9301,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G308" t="n">
-        <v>0.672864556312561</v>
+        <v>0.672864496707916</v>
       </c>
       <c r="H308" t="n">
         <v>2800</v>
@@ -9330,7 +9330,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G309" t="n">
-        <v>0.672864556312561</v>
+        <v>0.672864496707916</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G310" t="n">
-        <v>0.674054026603699</v>
+        <v>0.674053966999054</v>
       </c>
       <c r="H310" t="n">
         <v>10400</v>
@@ -9388,7 +9388,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G311" t="n">
-        <v>0.662158966064453</v>
+        <v>0.662158906459808</v>
       </c>
       <c r="H311" t="n">
         <v>50000</v>
@@ -9475,7 +9475,7 @@
         <v>0.826499998569489</v>
       </c>
       <c r="G314" t="n">
-        <v>0.655418455600739</v>
+        <v>0.655418395996094</v>
       </c>
       <c r="H314" t="n">
         <v>190000</v>
@@ -9533,7 +9533,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G316" t="n">
-        <v>0.654228925704956</v>
+        <v>0.654228866100311</v>
       </c>
       <c r="H316" t="n">
         <v>20400</v>
@@ -9562,7 +9562,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>0.649470925331116</v>
+        <v>0.649470865726471</v>
       </c>
       <c r="H317" t="n">
         <v>30000</v>
@@ -9620,7 +9620,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G319" t="n">
-        <v>0.698637187480927</v>
+        <v>0.698637127876282</v>
       </c>
       <c r="H319" t="n">
         <v>65200</v>
@@ -9649,7 +9649,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G320" t="n">
-        <v>0.689121127128601</v>
+        <v>0.689121186733246</v>
       </c>
       <c r="H320" t="n">
         <v>149200</v>
@@ -9736,7 +9736,7 @@
         <v>0.923500001430511</v>
       </c>
       <c r="G323" t="n">
-        <v>0.732339859008789</v>
+        <v>0.732339918613434</v>
       </c>
       <c r="H323" t="n">
         <v>146800</v>
@@ -9794,7 +9794,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G325" t="n">
-        <v>0.722427368164062</v>
+        <v>0.722427308559418</v>
       </c>
       <c r="H325" t="n">
         <v>19600</v>
@@ -9823,7 +9823,7 @@
         <v>0.952499985694885</v>
       </c>
       <c r="G326" t="n">
-        <v>0.755337059497833</v>
+        <v>0.755336999893188</v>
       </c>
       <c r="H326" t="n">
         <v>210000</v>
@@ -9852,7 +9852,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G327" t="n">
-        <v>0.780316710472107</v>
+        <v>0.780316770076752</v>
       </c>
       <c r="H327" t="n">
         <v>180800</v>
@@ -9910,7 +9910,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G329" t="n">
-        <v>0.808071851730347</v>
+        <v>0.808071792125702</v>
       </c>
       <c r="H329" t="n">
         <v>504400</v>
@@ -9968,7 +9968,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G331" t="n">
-        <v>0.816794812679291</v>
+        <v>0.816794872283936</v>
       </c>
       <c r="H331" t="n">
         <v>171600</v>
@@ -9997,7 +9997,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G332" t="n">
-        <v>0.836619913578033</v>
+        <v>0.836619973182678</v>
       </c>
       <c r="H332" t="n">
         <v>138000</v>
@@ -10026,7 +10026,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G333" t="n">
-        <v>0.836619913578033</v>
+        <v>0.836619973182678</v>
       </c>
       <c r="H333" t="n">
         <v>26800</v>
@@ -10055,7 +10055,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G334" t="n">
-        <v>0.836619913578033</v>
+        <v>0.836619973182678</v>
       </c>
       <c r="H334" t="n">
         <v>52400</v>
@@ -10084,7 +10084,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G335" t="n">
-        <v>0.850101113319397</v>
+        <v>0.850101053714752</v>
       </c>
       <c r="H335" t="n">
         <v>56000</v>
@@ -10113,7 +10113,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G336" t="n">
-        <v>0.854859113693237</v>
+        <v>0.854859054088593</v>
       </c>
       <c r="H336" t="n">
         <v>76400</v>
@@ -10258,7 +10258,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>0.855356454849243</v>
+        <v>0.855356514453888</v>
       </c>
       <c r="H341" t="n">
         <v>45200</v>
@@ -10287,7 +10287,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G342" t="n">
-        <v>0.847011566162109</v>
+        <v>0.847011506557465</v>
       </c>
       <c r="H342" t="n">
         <v>92000</v>
@@ -10316,7 +10316,7 @@
         <v>1.0110000371933</v>
       </c>
       <c r="G343" t="n">
-        <v>0.843673646450043</v>
+        <v>0.843673586845398</v>
       </c>
       <c r="H343" t="n">
         <v>36400</v>
@@ -10403,7 +10403,7 @@
         <v>1.00899994373322</v>
       </c>
       <c r="G346" t="n">
-        <v>0.842004597187042</v>
+        <v>0.842004537582397</v>
       </c>
       <c r="H346" t="n">
         <v>32400</v>
@@ -10432,7 +10432,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G347" t="n">
-        <v>0.838666677474976</v>
+        <v>0.838666617870331</v>
       </c>
       <c r="H347" t="n">
         <v>16000</v>
@@ -10548,7 +10548,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G351" t="n">
-        <v>0.805286884307861</v>
+        <v>0.805286824703217</v>
       </c>
       <c r="H351" t="n">
         <v>7200</v>
@@ -10606,7 +10606,7 @@
         <v>0.949500024318695</v>
       </c>
       <c r="G353" t="n">
-        <v>0.792352199554443</v>
+        <v>0.792352259159088</v>
       </c>
       <c r="H353" t="n">
         <v>20800</v>
@@ -10635,7 +10635,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G354" t="n">
-        <v>0.867039442062378</v>
+        <v>0.867039382457733</v>
       </c>
       <c r="H354" t="n">
         <v>297600</v>
@@ -10693,7 +10693,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G356" t="n">
-        <v>0.968013167381287</v>
+        <v>0.968013226985931</v>
       </c>
       <c r="H356" t="n">
         <v>754800</v>
@@ -10722,7 +10722,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G357" t="n">
-        <v>1.14075338840485</v>
+        <v>1.14075350761414</v>
       </c>
       <c r="H357" t="n">
         <v>584400</v>
@@ -10780,7 +10780,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G359" t="n">
-        <v>1.11071181297302</v>
+        <v>1.11071157455444</v>
       </c>
       <c r="H359" t="n">
         <v>314400</v>
@@ -10925,7 +10925,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G364" t="n">
-        <v>1.01391041278839</v>
+        <v>1.01391053199768</v>
       </c>
       <c r="H364" t="n">
         <v>24400</v>
@@ -10954,7 +10954,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G365" t="n">
-        <v>0.973854720592499</v>
+        <v>0.973854660987854</v>
       </c>
       <c r="H365" t="n">
         <v>172400</v>
@@ -11012,7 +11012,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G367" t="n">
-        <v>0.997220575809479</v>
+        <v>0.997220516204834</v>
       </c>
       <c r="H367" t="n">
         <v>41200</v>
@@ -11128,7 +11128,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G371" t="n">
-        <v>1.10069787502289</v>
+        <v>1.1006977558136</v>
       </c>
       <c r="H371" t="n">
         <v>264800</v>
@@ -11302,7 +11302,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G377" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H377" t="n">
         <v>12000</v>
@@ -11389,7 +11389,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G380" t="n">
-        <v>0.991378962993622</v>
+        <v>0.991379022598267</v>
       </c>
       <c r="H380" t="n">
         <v>3600</v>
@@ -11447,7 +11447,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G382" t="n">
-        <v>0.976358115673065</v>
+        <v>0.97635817527771</v>
       </c>
       <c r="H382" t="n">
         <v>22800</v>
@@ -11476,7 +11476,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G383" t="n">
-        <v>0.979696094989777</v>
+        <v>0.979696154594421</v>
       </c>
       <c r="H383" t="n">
         <v>25200</v>
@@ -11505,7 +11505,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G384" t="n">
-        <v>0.961337268352509</v>
+        <v>0.961337149143219</v>
       </c>
       <c r="H384" t="n">
         <v>13200</v>
@@ -11534,7 +11534,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G385" t="n">
-        <v>0.950488924980164</v>
+        <v>0.950488865375519</v>
       </c>
       <c r="H385" t="n">
         <v>35600</v>
@@ -11563,7 +11563,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>0.954661428928375</v>
+        <v>0.954661309719086</v>
       </c>
       <c r="H386" t="n">
         <v>22000</v>
@@ -11592,7 +11592,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G387" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H387" t="n">
         <v>65200</v>
@@ -11621,7 +11621,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G388" t="n">
-        <v>0.997220575809479</v>
+        <v>0.997220516204834</v>
       </c>
       <c r="H388" t="n">
         <v>8000</v>
@@ -11650,7 +11650,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G389" t="n">
-        <v>0.97802722454071</v>
+        <v>0.978027164936066</v>
       </c>
       <c r="H389" t="n">
         <v>7200</v>
@@ -11679,7 +11679,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G390" t="n">
-        <v>0.968013167381287</v>
+        <v>0.968013226985931</v>
       </c>
       <c r="H390" t="n">
         <v>20000</v>
@@ -11708,7 +11708,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G391" t="n">
-        <v>0.971351265907288</v>
+        <v>0.971351206302643</v>
       </c>
       <c r="H391" t="n">
         <v>7600</v>
@@ -11737,7 +11737,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G392" t="n">
-        <v>0.971351265907288</v>
+        <v>0.971351206302643</v>
       </c>
       <c r="H392" t="n">
         <v>2400</v>
@@ -11824,7 +11824,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G395" t="n">
-        <v>0.968013167381287</v>
+        <v>0.968013226985931</v>
       </c>
       <c r="H395" t="n">
         <v>9600</v>
@@ -11853,7 +11853,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G396" t="n">
-        <v>0.975523710250854</v>
+        <v>0.97552365064621</v>
       </c>
       <c r="H396" t="n">
         <v>20400</v>
@@ -11940,7 +11940,7 @@
         <v>1.125</v>
       </c>
       <c r="G399" t="n">
-        <v>0.938805878162384</v>
+        <v>0.938805818557739</v>
       </c>
       <c r="H399" t="n">
         <v>400</v>
@@ -12027,7 +12027,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G402" t="n">
-        <v>1.04144883155823</v>
+        <v>1.04144871234894</v>
       </c>
       <c r="H402" t="n">
         <v>101200</v>
@@ -12056,7 +12056,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G403" t="n">
-        <v>1.03477275371552</v>
+        <v>1.0347728729248</v>
       </c>
       <c r="H403" t="n">
         <v>32400</v>
@@ -12085,7 +12085,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>1.03477275371552</v>
+        <v>1.0347728729248</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G405" t="n">
-        <v>1.03060030937195</v>
+        <v>1.03060019016266</v>
       </c>
       <c r="H405" t="n">
         <v>6000</v>
@@ -12143,7 +12143,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G406" t="n">
-        <v>1.03060030937195</v>
+        <v>1.03060019016266</v>
       </c>
       <c r="H406" t="n">
         <v>36800</v>
@@ -12172,7 +12172,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.0723249912262</v>
+        <v>1.07232487201691</v>
       </c>
       <c r="H407" t="n">
         <v>139600</v>
@@ -12201,7 +12201,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>1.05396604537964</v>
+        <v>1.05396616458893</v>
       </c>
       <c r="H408" t="n">
         <v>126800</v>
@@ -12259,7 +12259,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G410" t="n">
-        <v>1.03477275371552</v>
+        <v>1.0347728729248</v>
       </c>
       <c r="H410" t="n">
         <v>7600</v>
@@ -12288,7 +12288,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G411" t="n">
-        <v>1.02893126010895</v>
+        <v>1.02893137931824</v>
       </c>
       <c r="H411" t="n">
         <v>37200</v>
@@ -12317,7 +12317,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H412" t="n">
         <v>53200</v>
@@ -12346,7 +12346,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G413" t="n">
-        <v>0.986372053623199</v>
+        <v>0.986372113227844</v>
       </c>
       <c r="H413" t="n">
         <v>21200</v>
@@ -12404,7 +12404,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G415" t="n">
-        <v>0.971351265907288</v>
+        <v>0.971351206302643</v>
       </c>
       <c r="H415" t="n">
         <v>30800</v>
@@ -12462,7 +12462,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G417" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H417" t="n">
         <v>60000</v>
@@ -12578,7 +12578,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G421" t="n">
-        <v>0.968013167381287</v>
+        <v>0.968013226985931</v>
       </c>
       <c r="H421" t="n">
         <v>800</v>
@@ -12607,7 +12607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G422" t="n">
-        <v>0.976358115673065</v>
+        <v>0.97635817527771</v>
       </c>
       <c r="H422" t="n">
         <v>11200</v>
@@ -12636,7 +12636,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G423" t="n">
-        <v>0.994717061519623</v>
+        <v>0.994717121124268</v>
       </c>
       <c r="H423" t="n">
         <v>400</v>
@@ -12665,7 +12665,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G424" t="n">
-        <v>0.979696094989777</v>
+        <v>0.979696154594421</v>
       </c>
       <c r="H424" t="n">
         <v>9200</v>
@@ -12694,7 +12694,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G425" t="n">
-        <v>0.979696094989777</v>
+        <v>0.979696154594421</v>
       </c>
       <c r="H425" t="n">
         <v>400</v>
@@ -12752,7 +12752,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G427" t="n">
-        <v>0.97802722454071</v>
+        <v>0.978027164936066</v>
       </c>
       <c r="H427" t="n">
         <v>31600</v>
@@ -12810,7 +12810,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G429" t="n">
-        <v>0.9880411028862</v>
+        <v>0.988041043281555</v>
       </c>
       <c r="H429" t="n">
         <v>5200</v>
@@ -12868,7 +12868,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G431" t="n">
-        <v>0.981365084648132</v>
+        <v>0.981365144252777</v>
       </c>
       <c r="H431" t="n">
         <v>3600</v>
@@ -12926,7 +12926,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G433" t="n">
-        <v>0.962171733379364</v>
+        <v>0.962171792984009</v>
       </c>
       <c r="H433" t="n">
         <v>32800</v>
@@ -12955,7 +12955,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G434" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H434" t="n">
         <v>10000</v>
@@ -13071,7 +13071,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G438" t="n">
-        <v>0.91794353723526</v>
+        <v>0.91794365644455</v>
       </c>
       <c r="H438" t="n">
         <v>164800</v>
@@ -13100,7 +13100,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G439" t="n">
-        <v>0.957999289035797</v>
+        <v>0.957999169826508</v>
       </c>
       <c r="H439" t="n">
         <v>80000</v>
@@ -13129,7 +13129,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G440" t="n">
-        <v>0.91794353723526</v>
+        <v>0.91794365644455</v>
       </c>
       <c r="H440" t="n">
         <v>138000</v>
@@ -13216,7 +13216,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G443" t="n">
-        <v>0.900419235229492</v>
+        <v>0.900419116020203</v>
       </c>
       <c r="H443" t="n">
         <v>11600</v>
@@ -13245,7 +13245,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G444" t="n">
-        <v>0.932964503765106</v>
+        <v>0.932964384555817</v>
       </c>
       <c r="H444" t="n">
         <v>26400</v>
@@ -13361,7 +13361,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G448" t="n">
-        <v>0.947985470294952</v>
+        <v>0.947985410690308</v>
       </c>
       <c r="H448" t="n">
         <v>54000</v>
@@ -13419,7 +13419,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G450" t="n">
-        <v>0.954661428928375</v>
+        <v>0.954661309719086</v>
       </c>
       <c r="H450" t="n">
         <v>4800</v>
@@ -13448,7 +13448,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G451" t="n">
-        <v>0.94130951166153</v>
+        <v>0.941309452056885</v>
       </c>
       <c r="H451" t="n">
         <v>49600</v>
@@ -13506,7 +13506,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G453" t="n">
-        <v>0.965509593486786</v>
+        <v>0.965509653091431</v>
       </c>
       <c r="H453" t="n">
         <v>68000</v>
@@ -13535,7 +13535,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G454" t="n">
-        <v>0.983034074306488</v>
+        <v>0.983034133911133</v>
       </c>
       <c r="H454" t="n">
         <v>96800</v>
@@ -13593,7 +13593,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G456" t="n">
-        <v>0.994717061519623</v>
+        <v>0.994717121124268</v>
       </c>
       <c r="H456" t="n">
         <v>119200</v>
@@ -13651,7 +13651,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>1.0264276266098</v>
+        <v>1.02642786502838</v>
       </c>
       <c r="H458" t="n">
         <v>73200</v>
@@ -13680,7 +13680,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G459" t="n">
-        <v>1.03477275371552</v>
+        <v>1.0347728729248</v>
       </c>
       <c r="H459" t="n">
         <v>89200</v>
@@ -13738,7 +13738,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>1.21836161613464</v>
+        <v>1.21836149692535</v>
       </c>
       <c r="H461" t="n">
         <v>412400</v>
@@ -13941,7 +13941,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.27677607536316</v>
+        <v>1.27677595615387</v>
       </c>
       <c r="H468" t="n">
         <v>47600</v>
@@ -13970,7 +13970,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G469" t="n">
-        <v>1.36106014251709</v>
+        <v>1.3610600233078</v>
       </c>
       <c r="H469" t="n">
         <v>74800</v>
@@ -14115,7 +14115,7 @@
         <v>1.58399999141693</v>
       </c>
       <c r="G474" t="n">
-        <v>1.32183861732483</v>
+        <v>1.32183873653412</v>
       </c>
       <c r="H474" t="n">
         <v>58400</v>
@@ -14144,7 +14144,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G475" t="n">
-        <v>1.31850075721741</v>
+        <v>1.3185008764267</v>
       </c>
       <c r="H475" t="n">
         <v>29200</v>
@@ -14173,7 +14173,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G476" t="n">
-        <v>1.30181074142456</v>
+        <v>1.30181086063385</v>
       </c>
       <c r="H476" t="n">
         <v>16400</v>
@@ -14202,7 +14202,7 @@
         <v>1.5</v>
       </c>
       <c r="G477" t="n">
-        <v>1.25174117088318</v>
+        <v>1.25174129009247</v>
       </c>
       <c r="H477" t="n">
         <v>84000</v>
@@ -14231,7 +14231,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G478" t="n">
-        <v>1.23171317577362</v>
+        <v>1.23171329498291</v>
       </c>
       <c r="H478" t="n">
         <v>88000</v>
@@ -14260,7 +14260,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G479" t="n">
-        <v>1.20834743976593</v>
+        <v>1.20834755897522</v>
       </c>
       <c r="H479" t="n">
         <v>42800</v>
@@ -14289,7 +14289,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>1.16912627220154</v>
+        <v>1.16912639141083</v>
       </c>
       <c r="H480" t="n">
         <v>12000</v>
@@ -14318,7 +14318,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G481" t="n">
-        <v>1.1432569026947</v>
+        <v>1.14325702190399</v>
       </c>
       <c r="H481" t="n">
         <v>42400</v>
@@ -14347,7 +14347,7 @@
         <v>1.39699995517731</v>
       </c>
       <c r="G482" t="n">
-        <v>1.16578829288483</v>
+        <v>1.16578817367554</v>
       </c>
       <c r="H482" t="n">
         <v>11600</v>
@@ -14434,7 +14434,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>1.16411924362183</v>
+        <v>1.16411936283112</v>
       </c>
       <c r="H485" t="n">
         <v>13600</v>
@@ -14463,7 +14463,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G486" t="n">
-        <v>1.15994691848755</v>
+        <v>1.15994679927826</v>
       </c>
       <c r="H486" t="n">
         <v>10000</v>
@@ -14492,7 +14492,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.17246413230896</v>
+        <v>1.17246425151825</v>
       </c>
       <c r="H487" t="n">
         <v>8800</v>
@@ -14579,7 +14579,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G490" t="n">
-        <v>1.18247818946838</v>
+        <v>1.18247830867767</v>
       </c>
       <c r="H490" t="n">
         <v>800</v>
@@ -14608,7 +14608,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G491" t="n">
-        <v>1.15994691848755</v>
+        <v>1.15994679927826</v>
       </c>
       <c r="H491" t="n">
         <v>11600</v>
@@ -14666,7 +14666,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G493" t="n">
-        <v>1.17580211162567</v>
+        <v>1.17580235004425</v>
       </c>
       <c r="H493" t="n">
         <v>1600</v>
@@ -14695,7 +14695,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G494" t="n">
-        <v>1.24339616298676</v>
+        <v>1.24339640140533</v>
       </c>
       <c r="H494" t="n">
         <v>29600</v>
@@ -14840,7 +14840,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G499" t="n">
-        <v>1.17580211162567</v>
+        <v>1.17580235004425</v>
       </c>
       <c r="H499" t="n">
         <v>2800</v>
@@ -14869,7 +14869,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G500" t="n">
-        <v>1.17663681507111</v>
+        <v>1.17663669586182</v>
       </c>
       <c r="H500" t="n">
         <v>1200</v>
@@ -14898,7 +14898,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G501" t="n">
-        <v>1.16745746135712</v>
+        <v>1.16745734214783</v>
       </c>
       <c r="H501" t="n">
         <v>23600</v>
@@ -14927,7 +14927,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>1.16411924362183</v>
+        <v>1.16411936283112</v>
       </c>
       <c r="H502" t="n">
         <v>4800</v>
@@ -14985,7 +14985,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.15577447414398</v>
+        <v>1.15577435493469</v>
       </c>
       <c r="H504" t="n">
         <v>4800</v>
@@ -15014,7 +15014,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G505" t="n">
-        <v>1.15577447414398</v>
+        <v>1.15577435493469</v>
       </c>
       <c r="H505" t="n">
         <v>12800</v>
@@ -15043,7 +15043,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G506" t="n">
-        <v>1.09652531147003</v>
+        <v>1.09652519226074</v>
       </c>
       <c r="H506" t="n">
         <v>207600</v>
@@ -15275,7 +15275,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G514" t="n">
-        <v>1.10570466518402</v>
+        <v>1.10570478439331</v>
       </c>
       <c r="H514" t="n">
         <v>15200</v>
@@ -15304,7 +15304,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>1.11404979228973</v>
+        <v>1.11404967308044</v>
       </c>
       <c r="H515" t="n">
         <v>5600</v>
@@ -15333,7 +15333,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>1.11404979228973</v>
+        <v>1.11404967308044</v>
       </c>
       <c r="H516" t="n">
         <v>18000</v>
@@ -15391,7 +15391,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.1182222366333</v>
+        <v>1.11822211742401</v>
       </c>
       <c r="H518" t="n">
         <v>30400</v>
@@ -15420,7 +15420,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.1182222366333</v>
+        <v>1.11822211742401</v>
       </c>
       <c r="H519" t="n">
         <v>25600</v>
@@ -15594,7 +15594,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G525" t="n">
-        <v>1.1432569026947</v>
+        <v>1.14325702190399</v>
       </c>
       <c r="H525" t="n">
         <v>14800</v>
@@ -15681,7 +15681,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>1.11404979228973</v>
+        <v>1.11404967308044</v>
       </c>
       <c r="H528" t="n">
         <v>3200</v>
@@ -15710,7 +15710,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G529" t="n">
-        <v>1.11404979228973</v>
+        <v>1.11404967308044</v>
       </c>
       <c r="H529" t="n">
         <v>18400</v>
@@ -15739,7 +15739,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>1.11404979228973</v>
+        <v>1.11404967308044</v>
       </c>
       <c r="H530" t="n">
         <v>34800</v>
@@ -15768,7 +15768,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G531" t="n">
-        <v>1.1182222366333</v>
+        <v>1.11822211742401</v>
       </c>
       <c r="H531" t="n">
         <v>2800</v>
@@ -15826,7 +15826,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>1.09735989570618</v>
+        <v>1.09735977649689</v>
       </c>
       <c r="H533" t="n">
         <v>12400</v>
@@ -15942,7 +15942,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G537" t="n">
-        <v>0.997220575809479</v>
+        <v>0.997220516204834</v>
       </c>
       <c r="H537" t="n">
         <v>70800</v>
@@ -15971,7 +15971,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G538" t="n">
-        <v>1.01808297634125</v>
+        <v>1.01808285713196</v>
       </c>
       <c r="H538" t="n">
         <v>4000</v>
@@ -16116,7 +16116,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G543" t="n">
-        <v>0.947150945663452</v>
+        <v>0.947150766849518</v>
       </c>
       <c r="H543" t="n">
         <v>27200</v>
@@ -16203,7 +16203,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G546" t="n">
-        <v>0.926288485527039</v>
+        <v>0.926288425922394</v>
       </c>
       <c r="H546" t="n">
         <v>20800</v>
@@ -16290,7 +16290,7 @@
         <v>1.125</v>
       </c>
       <c r="G549" t="n">
-        <v>0.938805878162384</v>
+        <v>0.938805818557739</v>
       </c>
       <c r="H549" t="n">
         <v>43600</v>
@@ -16319,7 +16319,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G550" t="n">
-        <v>0.959668219089508</v>
+        <v>0.959668159484863</v>
       </c>
       <c r="H550" t="n">
         <v>41200</v>
@@ -16348,7 +16348,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G551" t="n">
-        <v>0.947150945663452</v>
+        <v>0.947150766849518</v>
       </c>
       <c r="H551" t="n">
         <v>61600</v>
@@ -16406,7 +16406,7 @@
         <v>1.125</v>
       </c>
       <c r="G553" t="n">
-        <v>0.938805878162384</v>
+        <v>0.938805818557739</v>
       </c>
       <c r="H553" t="n">
         <v>2000</v>
@@ -16435,7 +16435,7 @@
         <v>1.125</v>
       </c>
       <c r="G554" t="n">
-        <v>0.938805878162384</v>
+        <v>0.938805818557739</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G555" t="n">
-        <v>0.926288485527039</v>
+        <v>0.926288425922394</v>
       </c>
       <c r="H555" t="n">
         <v>32800</v>
@@ -16493,7 +16493,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>0.922116100788116</v>
+        <v>0.922116041183472</v>
       </c>
       <c r="H556" t="n">
         <v>47200</v>
@@ -16522,7 +16522,7 @@
         <v>1.125</v>
       </c>
       <c r="G557" t="n">
-        <v>0.938805878162384</v>
+        <v>0.938805818557739</v>
       </c>
       <c r="H557" t="n">
         <v>17600</v>
@@ -16551,7 +16551,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G558" t="n">
-        <v>0.922116100788116</v>
+        <v>0.922116041183472</v>
       </c>
       <c r="H558" t="n">
         <v>7600</v>
@@ -16580,7 +16580,7 @@
         <v>1.125</v>
       </c>
       <c r="G559" t="n">
-        <v>0.938805878162384</v>
+        <v>0.938805818557739</v>
       </c>
       <c r="H559" t="n">
         <v>40000</v>
@@ -16609,7 +16609,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>0.922116100788116</v>
+        <v>0.922116041183472</v>
       </c>
       <c r="H560" t="n">
         <v>1600</v>
@@ -16696,7 +16696,7 @@
         <v>1.125</v>
       </c>
       <c r="G563" t="n">
-        <v>0.938805878162384</v>
+        <v>0.938805818557739</v>
       </c>
       <c r="H563" t="n">
         <v>800</v>
@@ -16812,7 +16812,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>0.955495715141296</v>
+        <v>0.955495834350586</v>
       </c>
       <c r="H567" t="n">
         <v>5200</v>
@@ -16899,7 +16899,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.01808297634125</v>
+        <v>1.01808285713196</v>
       </c>
       <c r="H570" t="n">
         <v>12000</v>
@@ -16928,7 +16928,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G571" t="n">
-        <v>1.03060030937195</v>
+        <v>1.03060019016266</v>
       </c>
       <c r="H571" t="n">
         <v>4000</v>
@@ -17015,7 +17015,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.06397998332977</v>
+        <v>1.06398010253906</v>
       </c>
       <c r="H574" t="n">
         <v>18800</v>
@@ -17044,7 +17044,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G575" t="n">
-        <v>1.0264276266098</v>
+        <v>1.02642786502838</v>
       </c>
       <c r="H575" t="n">
         <v>16800</v>
@@ -17073,7 +17073,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H576" t="n">
         <v>56800</v>
@@ -17102,7 +17102,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G577" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H577" t="n">
         <v>11600</v>
@@ -17131,7 +17131,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>0.980530560016632</v>
+        <v>0.980530619621277</v>
       </c>
       <c r="H579" t="n">
         <v>3200</v>
@@ -17189,7 +17189,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H580" t="n">
         <v>4000</v>
@@ -17218,7 +17218,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G581" t="n">
-        <v>0.993048071861267</v>
+        <v>0.993048131465912</v>
       </c>
       <c r="H581" t="n">
         <v>1600</v>
@@ -17334,7 +17334,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G585" t="n">
-        <v>1.1432569026947</v>
+        <v>1.14325702190399</v>
       </c>
       <c r="H585" t="n">
         <v>101600</v>
@@ -17363,7 +17363,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>1.21836161613464</v>
+        <v>1.21836149692535</v>
       </c>
       <c r="H586" t="n">
         <v>274800</v>
@@ -17450,7 +17450,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G589" t="n">
-        <v>1.21001648902893</v>
+        <v>1.21001672744751</v>
       </c>
       <c r="H589" t="n">
         <v>34400</v>
@@ -17479,7 +17479,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G590" t="n">
-        <v>1.19332647323608</v>
+        <v>1.19332659244537</v>
       </c>
       <c r="H590" t="n">
         <v>18400</v>
@@ -17537,7 +17537,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G592" t="n">
-        <v>1.17663681507111</v>
+        <v>1.17663669586182</v>
       </c>
       <c r="H592" t="n">
         <v>2800</v>
@@ -17566,7 +17566,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G593" t="n">
-        <v>1.19332647323608</v>
+        <v>1.19332659244537</v>
       </c>
       <c r="H593" t="n">
         <v>14800</v>
@@ -17624,7 +17624,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G595" t="n">
-        <v>1.18080925941467</v>
+        <v>1.18080914020538</v>
       </c>
       <c r="H595" t="n">
         <v>60400</v>
@@ -17653,7 +17653,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>1.28512096405029</v>
+        <v>1.285120844841</v>
       </c>
       <c r="H596" t="n">
         <v>419200</v>
@@ -17682,7 +17682,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.31015586853027</v>
+        <v>1.31015574932098</v>
       </c>
       <c r="H597" t="n">
         <v>117200</v>
@@ -17711,7 +17711,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G598" t="n">
-        <v>1.33548247814178</v>
+        <v>1.3354823589325</v>
       </c>
       <c r="H598" t="n">
         <v>36400</v>
@@ -17798,7 +17798,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G601" t="n">
-        <v>1.27929723262787</v>
+        <v>1.27929711341858</v>
       </c>
       <c r="H601" t="n">
         <v>14000</v>
@@ -17885,7 +17885,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.27929723262787</v>
+        <v>1.27929711341858</v>
       </c>
       <c r="H604" t="n">
         <v>20000</v>
@@ -18204,7 +18204,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G615" t="n">
-        <v>1.21014595031738</v>
+        <v>1.21014606952667</v>
       </c>
       <c r="H615" t="n">
         <v>69200</v>
@@ -18291,7 +18291,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>1.33116042613983</v>
+        <v>1.33116054534912</v>
       </c>
       <c r="H618" t="n">
         <v>26000</v>
@@ -18320,7 +18320,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G619" t="n">
-        <v>1.33548247814178</v>
+        <v>1.3354823589325</v>
       </c>
       <c r="H619" t="n">
         <v>46400</v>
@@ -18378,7 +18378,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>1.33116042613983</v>
+        <v>1.33116054534912</v>
       </c>
       <c r="H621" t="n">
         <v>10400</v>
@@ -18494,7 +18494,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>1.32251667976379</v>
+        <v>1.3225165605545</v>
       </c>
       <c r="H625" t="n">
         <v>19600</v>
@@ -18581,7 +18581,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>1.27929723262787</v>
+        <v>1.27929711341858</v>
       </c>
       <c r="H628" t="n">
         <v>12000</v>
@@ -18639,7 +18639,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G630" t="n">
-        <v>1.32251667976379</v>
+        <v>1.3225165605545</v>
       </c>
       <c r="H630" t="n">
         <v>42400</v>
@@ -18755,7 +18755,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.4132776260376</v>
+        <v>1.41327750682831</v>
       </c>
       <c r="H634" t="n">
         <v>123200</v>
@@ -18784,7 +18784,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G635" t="n">
-        <v>1.40895557403564</v>
+        <v>1.40895569324493</v>
       </c>
       <c r="H635" t="n">
         <v>83600</v>
@@ -19016,7 +19016,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G643" t="n">
-        <v>1.49971652030945</v>
+        <v>1.49971663951874</v>
       </c>
       <c r="H643" t="n">
         <v>56800</v>
@@ -19132,7 +19132,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G647" t="n">
-        <v>1.4132776260376</v>
+        <v>1.41327750682831</v>
       </c>
       <c r="H647" t="n">
         <v>15200</v>
@@ -19248,7 +19248,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>1.60344350337982</v>
+        <v>1.60344338417053</v>
       </c>
       <c r="H651" t="n">
         <v>191600</v>
@@ -19335,7 +19335,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>1.71149206161499</v>
+        <v>1.71149218082428</v>
       </c>
       <c r="H654" t="n">
         <v>197600</v>
@@ -19422,7 +19422,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>1.98809683322906</v>
+        <v>1.98809695243835</v>
       </c>
       <c r="H657" t="n">
         <v>588000</v>
@@ -19451,7 +19451,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>2.01402831077576</v>
+        <v>2.01402854919434</v>
       </c>
       <c r="H658" t="n">
         <v>342800</v>
@@ -19480,7 +19480,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>1.96216535568237</v>
+        <v>1.96216511726379</v>
       </c>
       <c r="H659" t="n">
         <v>80000</v>
@@ -19596,7 +19596,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G663" t="n">
-        <v>1.91894567012787</v>
+        <v>1.91894578933716</v>
       </c>
       <c r="H663" t="n">
         <v>15600</v>
@@ -19683,7 +19683,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G666" t="n">
-        <v>1.91894567012787</v>
+        <v>1.91894578933716</v>
       </c>
       <c r="H666" t="n">
         <v>10400</v>
@@ -19712,7 +19712,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>1.92758965492249</v>
+        <v>1.9275895357132</v>
       </c>
       <c r="H667" t="n">
         <v>50000</v>
@@ -19741,7 +19741,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>1.97945284843445</v>
+        <v>1.97945296764374</v>
       </c>
       <c r="H668" t="n">
         <v>50400</v>
@@ -19770,7 +19770,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G669" t="n">
-        <v>1.98809683322906</v>
+        <v>1.98809695243835</v>
       </c>
       <c r="H669" t="n">
         <v>24800</v>
@@ -19799,7 +19799,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.98809683322906</v>
+        <v>1.98809695243835</v>
       </c>
       <c r="H670" t="n">
         <v>18400</v>
@@ -19828,7 +19828,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>2.01402831077576</v>
+        <v>2.01402854919434</v>
       </c>
       <c r="H671" t="n">
         <v>7600</v>
@@ -19857,7 +19857,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G672" t="n">
-        <v>1.96216535568237</v>
+        <v>1.96216511726379</v>
       </c>
       <c r="H672" t="n">
         <v>52000</v>
@@ -19886,7 +19886,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>1.97945284843445</v>
+        <v>1.97945296764374</v>
       </c>
       <c r="H673" t="n">
         <v>17200</v>
@@ -19915,7 +19915,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.96216535568237</v>
+        <v>1.96216511726379</v>
       </c>
       <c r="H674" t="n">
         <v>15200</v>
@@ -19973,7 +19973,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>1.97945284843445</v>
+        <v>1.97945296764374</v>
       </c>
       <c r="H676" t="n">
         <v>10000</v>
@@ -20002,7 +20002,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>1.91894567012787</v>
+        <v>1.91894578933716</v>
       </c>
       <c r="H677" t="n">
         <v>38000</v>
@@ -20118,7 +20118,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G681" t="n">
-        <v>1.97945284843445</v>
+        <v>1.97945296764374</v>
       </c>
       <c r="H681" t="n">
         <v>18000</v>
@@ -20147,7 +20147,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>1.98809683322906</v>
+        <v>1.98809695243835</v>
       </c>
       <c r="H682" t="n">
         <v>10000</v>
@@ -20176,7 +20176,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.97945284843445</v>
+        <v>1.97945296764374</v>
       </c>
       <c r="H683" t="n">
         <v>16000</v>
@@ -20205,7 +20205,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>1.99674081802368</v>
+        <v>1.99674069881439</v>
       </c>
       <c r="H684" t="n">
         <v>23600</v>
@@ -20263,7 +20263,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>2.117755651474</v>
+        <v>2.11775541305542</v>
       </c>
       <c r="H686" t="n">
         <v>130800</v>
@@ -20292,7 +20292,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17826271057129</v>
+        <v>2.17826247215271</v>
       </c>
       <c r="H687" t="n">
         <v>109200</v>
@@ -20321,7 +20321,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>2.16961860656738</v>
+        <v>2.16961884498596</v>
       </c>
       <c r="H688" t="n">
         <v>52000</v>
@@ -20379,7 +20379,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G690" t="n">
-        <v>2.26470160484314</v>
+        <v>2.26470184326172</v>
       </c>
       <c r="H690" t="n">
         <v>39200</v>
@@ -20408,7 +20408,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G691" t="n">
-        <v>2.40300416946411</v>
+        <v>2.40300393104553</v>
       </c>
       <c r="H691" t="n">
         <v>131200</v>
@@ -20524,7 +20524,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G695" t="n">
-        <v>2.42029190063477</v>
+        <v>2.42029213905334</v>
       </c>
       <c r="H695" t="n">
         <v>59200</v>
@@ -20582,7 +20582,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>2.50673079490662</v>
+        <v>2.5067310333252</v>
       </c>
       <c r="H697" t="n">
         <v>142400</v>
@@ -20611,7 +20611,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G698" t="n">
-        <v>2.42029190063477</v>
+        <v>2.42029213905334</v>
       </c>
       <c r="H698" t="n">
         <v>497600</v>
@@ -20640,7 +20640,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>2.42029190063477</v>
+        <v>2.42029213905334</v>
       </c>
       <c r="H699" t="n">
         <v>70400</v>
@@ -20669,7 +20669,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.41164779663086</v>
+        <v>2.41164803504944</v>
       </c>
       <c r="H700" t="n">
         <v>22000</v>
@@ -20698,7 +20698,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>2.3597846031189</v>
+        <v>2.35978436470032</v>
       </c>
       <c r="H701" t="n">
         <v>76400</v>
@@ -20727,7 +20727,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>2.3597846031189</v>
+        <v>2.35978436470032</v>
       </c>
       <c r="H702" t="n">
         <v>28000</v>
@@ -20756,7 +20756,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G703" t="n">
-        <v>2.24741387367249</v>
+        <v>2.24741363525391</v>
       </c>
       <c r="H703" t="n">
         <v>97600</v>
@@ -20785,7 +20785,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>2.24741387367249</v>
+        <v>2.24741363525391</v>
       </c>
       <c r="H704" t="n">
         <v>55200</v>
@@ -20959,7 +20959,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G710" t="n">
-        <v>2.26470160484314</v>
+        <v>2.26470184326172</v>
       </c>
       <c r="H710" t="n">
         <v>29600</v>
@@ -20988,7 +20988,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>2.27334570884705</v>
+        <v>2.27334547042847</v>
       </c>
       <c r="H711" t="n">
         <v>11200</v>
@@ -21017,7 +21017,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G712" t="n">
-        <v>2.27334570884705</v>
+        <v>2.27334547042847</v>
       </c>
       <c r="H712" t="n">
         <v>31600</v>
@@ -21046,7 +21046,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G713" t="n">
-        <v>2.27334570884705</v>
+        <v>2.27334547042847</v>
       </c>
       <c r="H713" t="n">
         <v>18400</v>
@@ -21104,7 +21104,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G715" t="n">
-        <v>2.51537489891052</v>
+        <v>2.51537466049194</v>
       </c>
       <c r="H715" t="n">
         <v>298000</v>
@@ -21481,7 +21481,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G728" t="n">
-        <v>3.05129671096802</v>
+        <v>3.05129647254944</v>
       </c>
       <c r="H728" t="n">
         <v>77200</v>
@@ -21568,7 +21568,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.18959879875183</v>
+        <v>3.18959903717041</v>
       </c>
       <c r="H731" t="n">
         <v>43600</v>
@@ -22177,7 +22177,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G752" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H752" t="n">
         <v>13600</v>
@@ -22235,7 +22235,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G754" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H754" t="n">
         <v>5200</v>
@@ -22264,7 +22264,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G755" t="n">
-        <v>2.76604795455933</v>
+        <v>2.76604771614075</v>
       </c>
       <c r="H755" t="n">
         <v>3200</v>
@@ -22293,7 +22293,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G756" t="n">
-        <v>2.76604795455933</v>
+        <v>2.76604771614075</v>
       </c>
       <c r="H756" t="n">
         <v>4800</v>
@@ -22409,7 +22409,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G760" t="n">
-        <v>2.76604795455933</v>
+        <v>2.76604771614075</v>
       </c>
       <c r="H760" t="n">
         <v>24000</v>
@@ -22496,7 +22496,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G763" t="n">
-        <v>2.76604795455933</v>
+        <v>2.76604771614075</v>
       </c>
       <c r="H763" t="n">
         <v>53600</v>
@@ -22525,7 +22525,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G764" t="n">
-        <v>2.67096495628357</v>
+        <v>2.67096471786499</v>
       </c>
       <c r="H764" t="n">
         <v>14000</v>
@@ -22757,7 +22757,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>2.61910128593445</v>
+        <v>2.61910152435303</v>
       </c>
       <c r="H772" t="n">
         <v>5600</v>
@@ -22815,7 +22815,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G774" t="n">
-        <v>2.77469158172607</v>
+        <v>2.77469182014465</v>
       </c>
       <c r="H774" t="n">
         <v>17600</v>
@@ -22844,7 +22844,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>2.77469158172607</v>
+        <v>2.77469182014465</v>
       </c>
       <c r="H775" t="n">
         <v>12000</v>
@@ -23221,7 +23221,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G788" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H788" t="n">
         <v>2800</v>
@@ -23424,7 +23424,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G795" t="n">
-        <v>2.76604795455933</v>
+        <v>2.76604771614075</v>
       </c>
       <c r="H795" t="n">
         <v>23600</v>
@@ -23540,7 +23540,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>2.55859446525574</v>
+        <v>2.55859422683716</v>
       </c>
       <c r="H799" t="n">
         <v>34400</v>
@@ -23569,7 +23569,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G800" t="n">
-        <v>2.51537489891052</v>
+        <v>2.51537466049194</v>
       </c>
       <c r="H800" t="n">
         <v>28800</v>
@@ -23598,7 +23598,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.51537489891052</v>
+        <v>2.51537466049194</v>
       </c>
       <c r="H801" t="n">
         <v>12800</v>
@@ -23627,7 +23627,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>2.51537489891052</v>
+        <v>2.51537466049194</v>
       </c>
       <c r="H802" t="n">
         <v>119200</v>
@@ -23743,7 +23743,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>2.41164779663086</v>
+        <v>2.41164803504944</v>
       </c>
       <c r="H806" t="n">
         <v>12400</v>
@@ -23830,7 +23830,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>2.42029190063477</v>
+        <v>2.42029213905334</v>
       </c>
       <c r="H809" t="n">
         <v>7200</v>
@@ -23859,7 +23859,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40300416946411</v>
+        <v>2.40300393104553</v>
       </c>
       <c r="H810" t="n">
         <v>3600</v>
@@ -23917,7 +23917,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>2.41164779663086</v>
+        <v>2.41164803504944</v>
       </c>
       <c r="H812" t="n">
         <v>5200</v>
@@ -24207,7 +24207,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G822" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H822" t="n">
         <v>44800</v>
@@ -24294,7 +24294,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G825" t="n">
-        <v>2.61910128593445</v>
+        <v>2.61910152435303</v>
       </c>
       <c r="H825" t="n">
         <v>10000</v>
@@ -24410,7 +24410,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>2.69689631462097</v>
+        <v>2.69689655303955</v>
       </c>
       <c r="H829" t="n">
         <v>4800</v>
@@ -24584,7 +24584,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G835" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H835" t="n">
         <v>1600</v>
@@ -24671,7 +24671,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.66232085227966</v>
+        <v>2.66232109069824</v>
       </c>
       <c r="H838" t="n">
         <v>12800</v>
@@ -24729,7 +24729,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>2.61910128593445</v>
+        <v>2.61910152435303</v>
       </c>
       <c r="H840" t="n">
         <v>12800</v>
@@ -79980,6 +79980,35 @@
         <v>400</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>1.52042245864868</v>
+        <v>1.52042269706726</v>
       </c>
       <c r="H3" t="n">
         <v>2400</v>
@@ -485,7 +485,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>1.54427242279053</v>
+        <v>1.54427230358124</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -514,7 +514,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G5" t="n">
-        <v>1.43918418884277</v>
+        <v>1.43918442726135</v>
       </c>
       <c r="H5" t="n">
         <v>10800</v>
@@ -572,7 +572,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G7" t="n">
-        <v>1.39968311786652</v>
+        <v>1.39968323707581</v>
       </c>
       <c r="H7" t="n">
         <v>3600</v>
@@ -601,7 +601,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39968311786652</v>
+        <v>1.39968323707581</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G9" t="n">
-        <v>1.39372074604034</v>
+        <v>1.39372062683105</v>
       </c>
       <c r="H9" t="n">
         <v>1600</v>
@@ -659,7 +659,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G10" t="n">
-        <v>1.39372074604034</v>
+        <v>1.39372062683105</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G11" t="n">
-        <v>1.39968311786652</v>
+        <v>1.39968323707581</v>
       </c>
       <c r="H11" t="n">
         <v>2400</v>
@@ -717,7 +717,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39968311786652</v>
+        <v>1.39968323707581</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G13" t="n">
-        <v>1.39968311786652</v>
+        <v>1.39968323707581</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G14" t="n">
-        <v>1.33931350708008</v>
+        <v>1.33931362628937</v>
       </c>
       <c r="H14" t="n">
         <v>2800</v>
@@ -804,7 +804,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G15" t="n">
-        <v>1.31919026374817</v>
+        <v>1.31919014453888</v>
       </c>
       <c r="H15" t="n">
         <v>4000</v>
@@ -833,7 +833,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G16" t="n">
-        <v>1.33856821060181</v>
+        <v>1.33856809139252</v>
       </c>
       <c r="H16" t="n">
         <v>1600</v>
@@ -862,7 +862,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>1.28937804698944</v>
+        <v>1.28937816619873</v>
       </c>
       <c r="H17" t="n">
         <v>4000</v>
@@ -949,7 +949,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.26701867580414</v>
+        <v>1.26701891422272</v>
       </c>
       <c r="H20" t="n">
         <v>5600</v>
@@ -978,7 +978,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>1.29981219768524</v>
+        <v>1.29981231689453</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.27447199821472</v>
+        <v>1.27447187900543</v>
       </c>
       <c r="H22" t="n">
         <v>1200</v>
@@ -1036,7 +1036,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G23" t="n">
-        <v>1.22379100322723</v>
+        <v>1.22379112243652</v>
       </c>
       <c r="H23" t="n">
         <v>5600</v>
@@ -1065,7 +1065,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G24" t="n">
-        <v>1.22379100322723</v>
+        <v>1.22379112243652</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G25" t="n">
-        <v>1.19099771976471</v>
+        <v>1.190997838974</v>
       </c>
       <c r="H25" t="n">
         <v>2800</v>
@@ -1181,7 +1181,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G28" t="n">
-        <v>0.991256058216095</v>
+        <v>0.99125599861145</v>
       </c>
       <c r="H28" t="n">
         <v>4000</v>
@@ -1239,7 +1239,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>0.961443603038788</v>
+        <v>0.961443722248077</v>
       </c>
       <c r="H30" t="n">
         <v>2400</v>
@@ -1268,7 +1268,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>0.976349890232086</v>
+        <v>0.976349771022797</v>
       </c>
       <c r="H31" t="n">
         <v>4800</v>
@@ -1413,7 +1413,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G36" t="n">
-        <v>0.995727837085724</v>
+        <v>0.995727717876434</v>
       </c>
       <c r="H36" t="n">
         <v>2000</v>
@@ -1442,7 +1442,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G37" t="n">
-        <v>1.01212441921234</v>
+        <v>1.01212453842163</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1471,7 +1471,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G38" t="n">
-        <v>1.02106821537018</v>
+        <v>1.02106809616089</v>
       </c>
       <c r="H38" t="n">
         <v>400</v>
@@ -1500,7 +1500,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G39" t="n">
-        <v>1.02106821537018</v>
+        <v>1.02106809616089</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1529,7 +1529,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G40" t="n">
-        <v>1.02106821537018</v>
+        <v>1.02106809616089</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G41" t="n">
-        <v>1.02106821537018</v>
+        <v>1.02106809616089</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G44" t="n">
-        <v>0.983802855014801</v>
+        <v>0.983802914619446</v>
       </c>
       <c r="H44" t="n">
         <v>7200</v>
@@ -1674,7 +1674,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>0.976349890232086</v>
+        <v>0.976349771022797</v>
       </c>
       <c r="H45" t="n">
         <v>3600</v>
@@ -1703,7 +1703,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G46" t="n">
-        <v>0.983802855014801</v>
+        <v>0.983802914619446</v>
       </c>
       <c r="H46" t="n">
         <v>5600</v>
@@ -1732,7 +1732,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>0.976349890232086</v>
+        <v>0.976349771022797</v>
       </c>
       <c r="H47" t="n">
         <v>400</v>
@@ -1761,7 +1761,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G48" t="n">
-        <v>0.976349890232086</v>
+        <v>0.976349771022797</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G49" t="n">
-        <v>0.994237184524536</v>
+        <v>0.994237124919891</v>
       </c>
       <c r="H49" t="n">
         <v>2400</v>
@@ -1848,7 +1848,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>0.953990757465363</v>
+        <v>0.953990697860718</v>
       </c>
       <c r="H51" t="n">
         <v>8400</v>
@@ -1877,7 +1877,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G52" t="n">
-        <v>0.953990757465363</v>
+        <v>0.953990697860718</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>0.961443603038788</v>
+        <v>0.961443722248077</v>
       </c>
       <c r="H53" t="n">
         <v>18800</v>
@@ -1935,7 +1935,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G54" t="n">
-        <v>0.967406153678894</v>
+        <v>0.967406094074249</v>
       </c>
       <c r="H54" t="n">
         <v>7200</v>
@@ -2051,7 +2051,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G58" t="n">
-        <v>0.950264096260071</v>
+        <v>0.950264155864716</v>
       </c>
       <c r="H58" t="n">
         <v>400</v>
@@ -2080,7 +2080,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>0.946537435054779</v>
+        <v>0.946537554264069</v>
       </c>
       <c r="H59" t="n">
         <v>400</v>
@@ -2109,7 +2109,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>0.961443603038788</v>
+        <v>0.961443722248077</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2254,7 +2254,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G65" t="n">
-        <v>0.991256058216095</v>
+        <v>0.99125599861145</v>
       </c>
       <c r="H65" t="n">
         <v>7200</v>
@@ -2283,7 +2283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.991256058216095</v>
+        <v>0.99125599861145</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G70" t="n">
-        <v>0.958462536334991</v>
+        <v>0.958462357521057</v>
       </c>
       <c r="H70" t="n">
         <v>8400</v>
@@ -2428,7 +2428,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>0.961443603038788</v>
+        <v>0.961443722248077</v>
       </c>
       <c r="H71" t="n">
         <v>24800</v>
@@ -2486,7 +2486,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G73" t="n">
-        <v>0.940575242042542</v>
+        <v>0.940575063228607</v>
       </c>
       <c r="H73" t="n">
         <v>2400</v>
@@ -2544,7 +2544,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>0.946537435054779</v>
+        <v>0.946537554264069</v>
       </c>
       <c r="H75" t="n">
         <v>17200</v>
@@ -2573,7 +2573,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G76" t="n">
-        <v>0.932376801967621</v>
+        <v>0.93237692117691</v>
       </c>
       <c r="H76" t="n">
         <v>13200</v>
@@ -2602,7 +2602,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9241783618927</v>
+        <v>0.92417848110199</v>
       </c>
       <c r="H77" t="n">
         <v>4800</v>
@@ -2776,7 +2776,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>0.912998795509338</v>
+        <v>0.912998914718628</v>
       </c>
       <c r="H83" t="n">
         <v>15600</v>
@@ -2805,7 +2805,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G84" t="n">
-        <v>0.983802855014801</v>
+        <v>0.983802914619446</v>
       </c>
       <c r="H84" t="n">
         <v>51600</v>
@@ -2834,7 +2834,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G85" t="n">
-        <v>0.99870902299881</v>
+        <v>0.998708963394165</v>
       </c>
       <c r="H85" t="n">
         <v>12000</v>
@@ -2892,7 +2892,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G87" t="n">
-        <v>1.02852118015289</v>
+        <v>1.02852129936218</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G88" t="n">
-        <v>1.02852118015289</v>
+        <v>1.02852129936218</v>
       </c>
       <c r="H88" t="n">
         <v>20800</v>
@@ -2950,7 +2950,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G89" t="n">
-        <v>0.991256058216095</v>
+        <v>0.99125599861145</v>
       </c>
       <c r="H89" t="n">
         <v>30000</v>
@@ -2979,7 +2979,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>0.983325839042664</v>
+        <v>0.983325779438019</v>
       </c>
       <c r="H90" t="n">
         <v>14400</v>
@@ -3008,7 +3008,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G91" t="n">
-        <v>0.996014058589935</v>
+        <v>0.996013998985291</v>
       </c>
       <c r="H91" t="n">
         <v>8400</v>
@@ -3124,7 +3124,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G95" t="n">
-        <v>1.01028800010681</v>
+        <v>1.0102881193161</v>
       </c>
       <c r="H95" t="n">
         <v>10400</v>
@@ -3182,7 +3182,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G97" t="n">
-        <v>1.011873960495</v>
+        <v>1.01187407970428</v>
       </c>
       <c r="H97" t="n">
         <v>400</v>
@@ -3211,7 +3211,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G98" t="n">
-        <v>1.011873960495</v>
+        <v>1.01187407970428</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>0.97698187828064</v>
+        <v>0.976981937885284</v>
       </c>
       <c r="H99" t="n">
         <v>11200</v>
@@ -3269,7 +3269,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G100" t="n">
-        <v>0.990462839603424</v>
+        <v>0.990462899208069</v>
       </c>
       <c r="H100" t="n">
         <v>13200</v>
@@ -3414,7 +3414,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G105" t="n">
-        <v>0.935745537281036</v>
+        <v>0.935745477676392</v>
       </c>
       <c r="H105" t="n">
         <v>4400</v>
@@ -3675,7 +3675,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G114" t="n">
-        <v>0.903232395648956</v>
+        <v>0.903232455253601</v>
       </c>
       <c r="H114" t="n">
         <v>19200</v>
@@ -3704,7 +3704,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G115" t="n">
-        <v>0.904025435447693</v>
+        <v>0.904025375843048</v>
       </c>
       <c r="H115" t="n">
         <v>800</v>
@@ -3733,7 +3733,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G116" t="n">
-        <v>0.911955535411835</v>
+        <v>0.911955416202545</v>
       </c>
       <c r="H116" t="n">
         <v>4400</v>
@@ -3762,7 +3762,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G117" t="n">
-        <v>0.911955535411835</v>
+        <v>0.911955416202545</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G118" t="n">
-        <v>0.884993314743042</v>
+        <v>0.884993255138397</v>
       </c>
       <c r="H118" t="n">
         <v>4800</v>
@@ -3907,7 +3907,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G122" t="n">
-        <v>0.864375233650208</v>
+        <v>0.864375174045563</v>
       </c>
       <c r="H122" t="n">
         <v>59600</v>
@@ -3965,7 +3965,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>0.824724972248077</v>
+        <v>0.824724912643433</v>
       </c>
       <c r="H124" t="n">
         <v>2800</v>
@@ -4023,7 +4023,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>0.796969711780548</v>
+        <v>0.796969771385193</v>
       </c>
       <c r="H126" t="n">
         <v>42400</v>
@@ -4052,7 +4052,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G127" t="n">
-        <v>0.800934791564941</v>
+        <v>0.800934851169586</v>
       </c>
       <c r="H127" t="n">
         <v>400</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.800934791564941</v>
+        <v>0.800934851169586</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G131" t="n">
-        <v>0.745424449443817</v>
+        <v>0.745424509048462</v>
       </c>
       <c r="H131" t="n">
         <v>5200</v>
@@ -4197,7 +4197,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G132" t="n">
-        <v>0.729564428329468</v>
+        <v>0.729564309120178</v>
       </c>
       <c r="H132" t="n">
         <v>2000</v>
@@ -4429,7 +4429,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G140" t="n">
-        <v>0.828689932823181</v>
+        <v>0.828689873218536</v>
       </c>
       <c r="H140" t="n">
         <v>8000</v>
@@ -4458,7 +4458,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G141" t="n">
-        <v>0.831862032413483</v>
+        <v>0.831861972808838</v>
       </c>
       <c r="H141" t="n">
         <v>4800</v>
@@ -4487,7 +4487,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>0.832655012607574</v>
+        <v>0.83265495300293</v>
       </c>
       <c r="H142" t="n">
         <v>2000</v>
@@ -4516,7 +4516,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G143" t="n">
-        <v>0.839792013168335</v>
+        <v>0.83979195356369</v>
       </c>
       <c r="H143" t="n">
         <v>90800</v>
@@ -4545,7 +4545,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G144" t="n">
-        <v>0.835034072399139</v>
+        <v>0.835034012794495</v>
       </c>
       <c r="H144" t="n">
         <v>11600</v>
@@ -4574,7 +4574,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G145" t="n">
-        <v>0.835034072399139</v>
+        <v>0.835034012794495</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G146" t="n">
-        <v>0.835034072399139</v>
+        <v>0.835034012794495</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>0.835034072399139</v>
+        <v>0.835034012794495</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>0.840584993362427</v>
+        <v>0.840584933757782</v>
       </c>
       <c r="H149" t="n">
         <v>12400</v>
@@ -4748,7 +4748,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G151" t="n">
-        <v>0.808864772319794</v>
+        <v>0.808864831924438</v>
       </c>
       <c r="H151" t="n">
         <v>5600</v>
@@ -4777,7 +4777,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>0.808864772319794</v>
+        <v>0.808864831924438</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G153" t="n">
-        <v>0.808864772319794</v>
+        <v>0.808864831924438</v>
       </c>
       <c r="H153" t="n">
         <v>2000</v>
@@ -4835,7 +4835,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>0.808864772319794</v>
+        <v>0.808864831924438</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>0.824724972248077</v>
+        <v>0.824724912643433</v>
       </c>
       <c r="H155" t="n">
         <v>5600</v>
@@ -4893,7 +4893,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>0.824724972248077</v>
+        <v>0.824724912643433</v>
       </c>
       <c r="H156" t="n">
         <v>2400</v>
@@ -4980,7 +4980,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G159" t="n">
-        <v>0.805692851543427</v>
+        <v>0.805692791938782</v>
       </c>
       <c r="H159" t="n">
         <v>3600</v>
@@ -5009,7 +5009,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G160" t="n">
-        <v>0.779127180576324</v>
+        <v>0.779127240180969</v>
       </c>
       <c r="H160" t="n">
         <v>5200</v>
@@ -5154,7 +5154,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G165" t="n">
-        <v>0.761284589767456</v>
+        <v>0.761284530162811</v>
       </c>
       <c r="H165" t="n">
         <v>2800</v>
@@ -5183,7 +5183,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G166" t="n">
-        <v>0.758112490177155</v>
+        <v>0.758112549781799</v>
       </c>
       <c r="H166" t="n">
         <v>800</v>
@@ -5212,7 +5212,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G167" t="n">
-        <v>0.779127180576324</v>
+        <v>0.779127240180969</v>
       </c>
       <c r="H167" t="n">
         <v>400</v>
@@ -5299,7 +5299,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G170" t="n">
-        <v>0.751768469810486</v>
+        <v>0.751768529415131</v>
       </c>
       <c r="H170" t="n">
         <v>13600</v>
@@ -5502,7 +5502,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G177" t="n">
-        <v>0.794590711593628</v>
+        <v>0.794590771198273</v>
       </c>
       <c r="H177" t="n">
         <v>28400</v>
@@ -5589,7 +5589,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G180" t="n">
-        <v>0.773179650306702</v>
+        <v>0.773179590702057</v>
       </c>
       <c r="H180" t="n">
         <v>17600</v>
@@ -5618,7 +5618,7 @@
         <v>0.975000023841858</v>
       </c>
       <c r="G181" t="n">
-        <v>0.773179650306702</v>
+        <v>0.773179590702057</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G185" t="n">
-        <v>0.761284589767456</v>
+        <v>0.761284530162811</v>
       </c>
       <c r="H185" t="n">
         <v>4800</v>
@@ -5792,7 +5792,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>0.766835570335388</v>
+        <v>0.766835629940033</v>
       </c>
       <c r="H187" t="n">
         <v>41200</v>
@@ -5821,7 +5821,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G188" t="n">
-        <v>0.713704228401184</v>
+        <v>0.713704288005829</v>
       </c>
       <c r="H188" t="n">
         <v>86400</v>
@@ -5850,7 +5850,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>0.689914166927338</v>
+        <v>0.689914107322693</v>
       </c>
       <c r="H189" t="n">
         <v>35200</v>
@@ -5879,7 +5879,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G190" t="n">
-        <v>0.689121186733246</v>
+        <v>0.689121127128601</v>
       </c>
       <c r="H190" t="n">
         <v>10000</v>
@@ -5908,7 +5908,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G191" t="n">
-        <v>0.689121186733246</v>
+        <v>0.689121127128601</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G192" t="n">
-        <v>0.681984066963196</v>
+        <v>0.681984126567841</v>
       </c>
       <c r="H192" t="n">
         <v>24800</v>
@@ -5966,7 +5966,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G193" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H193" t="n">
         <v>27600</v>
@@ -6024,7 +6024,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G195" t="n">
-        <v>0.634403884410858</v>
+        <v>0.634403765201569</v>
       </c>
       <c r="H195" t="n">
         <v>15200</v>
@@ -6053,7 +6053,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G196" t="n">
-        <v>0.628852784633636</v>
+        <v>0.628852725028992</v>
       </c>
       <c r="H196" t="n">
         <v>64400</v>
@@ -6227,7 +6227,7 @@
         <v>0.72299998998642</v>
       </c>
       <c r="G202" t="n">
-        <v>0.573342442512512</v>
+        <v>0.573342382907867</v>
       </c>
       <c r="H202" t="n">
         <v>28400</v>
@@ -6285,7 +6285,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>0.555499792098999</v>
+        <v>0.555499851703644</v>
       </c>
       <c r="H204" t="n">
         <v>38000</v>
@@ -6604,7 +6604,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G215" t="n">
-        <v>0.569377362728119</v>
+        <v>0.569377481937408</v>
       </c>
       <c r="H215" t="n">
         <v>22400</v>
@@ -6633,7 +6633,7 @@
         <v>0.695500016212463</v>
       </c>
       <c r="G216" t="n">
-        <v>0.551534831523895</v>
+        <v>0.55153477191925</v>
       </c>
       <c r="H216" t="n">
         <v>67200</v>
@@ -6749,7 +6749,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G220" t="n">
-        <v>0.539243280887604</v>
+        <v>0.539243221282959</v>
       </c>
       <c r="H220" t="n">
         <v>26400</v>
@@ -6923,7 +6923,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G226" t="n">
-        <v>0.515453040599823</v>
+        <v>0.515453100204468</v>
       </c>
       <c r="H226" t="n">
         <v>62800</v>
@@ -6981,7 +6981,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>0.513867080211639</v>
+        <v>0.513867139816284</v>
       </c>
       <c r="H228" t="n">
         <v>34800</v>
@@ -7010,7 +7010,7 @@
         <v>0.625500023365021</v>
       </c>
       <c r="G229" t="n">
-        <v>0.496024459600449</v>
+        <v>0.496024489402771</v>
       </c>
       <c r="H229" t="n">
         <v>18000</v>
@@ -7068,7 +7068,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G231" t="n">
-        <v>0.551138341426849</v>
+        <v>0.551138281822205</v>
       </c>
       <c r="H231" t="n">
         <v>14800</v>
@@ -7126,7 +7126,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G233" t="n">
-        <v>0.539243280887604</v>
+        <v>0.539243221282959</v>
       </c>
       <c r="H233" t="n">
         <v>20800</v>
@@ -7155,7 +7155,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G234" t="n">
-        <v>0.531313240528107</v>
+        <v>0.531313180923462</v>
       </c>
       <c r="H234" t="n">
         <v>4800</v>
@@ -7184,7 +7184,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G235" t="n">
-        <v>0.531313240528107</v>
+        <v>0.531313180923462</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G237" t="n">
-        <v>0.551138341426849</v>
+        <v>0.551138281822205</v>
       </c>
       <c r="H237" t="n">
         <v>2800</v>
@@ -7271,7 +7271,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G238" t="n">
-        <v>0.527348220348358</v>
+        <v>0.527348160743713</v>
       </c>
       <c r="H238" t="n">
         <v>9200</v>
@@ -7329,7 +7329,7 @@
         <v>0.694500029087067</v>
       </c>
       <c r="G240" t="n">
-        <v>0.550741791725159</v>
+        <v>0.550741851329803</v>
       </c>
       <c r="H240" t="n">
         <v>16400</v>
@@ -7358,7 +7358,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G241" t="n">
-        <v>0.539243280887604</v>
+        <v>0.539243221282959</v>
       </c>
       <c r="H241" t="n">
         <v>13200</v>
@@ -7387,7 +7387,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G242" t="n">
-        <v>0.539243280887604</v>
+        <v>0.539243221282959</v>
       </c>
       <c r="H242" t="n">
         <v>8000</v>
@@ -7706,7 +7706,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G253" t="n">
-        <v>0.615371704101562</v>
+        <v>0.615371763706207</v>
       </c>
       <c r="H253" t="n">
         <v>42000</v>
@@ -7735,7 +7735,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G254" t="n">
-        <v>0.626473784446716</v>
+        <v>0.626473724842072</v>
       </c>
       <c r="H254" t="n">
         <v>97200</v>
@@ -7764,7 +7764,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G255" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H255" t="n">
         <v>39600</v>
@@ -7793,7 +7793,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G256" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H256" t="n">
         <v>27200</v>
@@ -7822,7 +7822,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G257" t="n">
-        <v>0.66533100605011</v>
+        <v>0.665330946445465</v>
       </c>
       <c r="H257" t="n">
         <v>88400</v>
@@ -7880,7 +7880,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>0.77714467048645</v>
+        <v>0.777144730091095</v>
       </c>
       <c r="H259" t="n">
         <v>194400</v>
@@ -8025,7 +8025,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>0.796969711780548</v>
+        <v>0.796969771385193</v>
       </c>
       <c r="H264" t="n">
         <v>3600</v>
@@ -8054,7 +8054,7 @@
         <v>1.00699996948242</v>
       </c>
       <c r="G265" t="n">
-        <v>0.798555672168732</v>
+        <v>0.798555791378021</v>
       </c>
       <c r="H265" t="n">
         <v>2000</v>
@@ -8083,7 +8083,7 @@
         <v>1.00699996948242</v>
       </c>
       <c r="G266" t="n">
-        <v>0.798555672168732</v>
+        <v>0.798555791378021</v>
       </c>
       <c r="H266" t="n">
         <v>6000</v>
@@ -8112,7 +8112,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G267" t="n">
-        <v>0.800934791564941</v>
+        <v>0.800934851169586</v>
       </c>
       <c r="H267" t="n">
         <v>14000</v>
@@ -8141,7 +8141,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G268" t="n">
-        <v>0.778334140777588</v>
+        <v>0.778334200382233</v>
       </c>
       <c r="H268" t="n">
         <v>4400</v>
@@ -8228,7 +8228,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>0.77714467048645</v>
+        <v>0.777144730091095</v>
       </c>
       <c r="H271" t="n">
         <v>4800</v>
@@ -8344,7 +8344,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>0.77714467048645</v>
+        <v>0.777144730091095</v>
       </c>
       <c r="H275" t="n">
         <v>7200</v>
@@ -8431,7 +8431,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G278" t="n">
-        <v>0.761284589767456</v>
+        <v>0.761284530162811</v>
       </c>
       <c r="H278" t="n">
         <v>13200</v>
@@ -8634,7 +8634,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G285" t="n">
-        <v>0.721634387969971</v>
+        <v>0.721634328365326</v>
       </c>
       <c r="H285" t="n">
         <v>38400</v>
@@ -8692,7 +8692,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G287" t="n">
-        <v>0.666123986244202</v>
+        <v>0.666123926639557</v>
       </c>
       <c r="H287" t="n">
         <v>27200</v>
@@ -8750,7 +8750,7 @@
         <v>0.800499975681305</v>
       </c>
       <c r="G289" t="n">
-        <v>0.634800314903259</v>
+        <v>0.634800255298615</v>
       </c>
       <c r="H289" t="n">
         <v>12800</v>
@@ -8779,7 +8779,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G290" t="n">
-        <v>0.64233386516571</v>
+        <v>0.642333805561066</v>
       </c>
       <c r="H290" t="n">
         <v>23200</v>
@@ -8808,7 +8808,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G291" t="n">
-        <v>0.653435885906219</v>
+        <v>0.653435945510864</v>
       </c>
       <c r="H291" t="n">
         <v>9200</v>
@@ -8837,7 +8837,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G292" t="n">
-        <v>0.662158906459808</v>
+        <v>0.662158966064453</v>
       </c>
       <c r="H292" t="n">
         <v>8000</v>
@@ -8866,7 +8866,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G293" t="n">
-        <v>0.664537966251373</v>
+        <v>0.664538025856018</v>
       </c>
       <c r="H293" t="n">
         <v>14400</v>
@@ -8895,7 +8895,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G294" t="n">
-        <v>0.646298885345459</v>
+        <v>0.646298825740814</v>
       </c>
       <c r="H294" t="n">
         <v>14800</v>
@@ -8953,7 +8953,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G296" t="n">
-        <v>0.658193945884705</v>
+        <v>0.65819388628006</v>
       </c>
       <c r="H296" t="n">
         <v>19200</v>
@@ -9040,7 +9040,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G299" t="n">
-        <v>0.674053966999054</v>
+        <v>0.674054086208344</v>
       </c>
       <c r="H299" t="n">
         <v>47200</v>
@@ -9069,7 +9069,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>0.689914166927338</v>
+        <v>0.689914107322693</v>
       </c>
       <c r="H300" t="n">
         <v>30800</v>
@@ -9098,7 +9098,7 @@
         <v>0.856500029563904</v>
       </c>
       <c r="G301" t="n">
-        <v>0.679208636283875</v>
+        <v>0.67920857667923</v>
       </c>
       <c r="H301" t="n">
         <v>12800</v>
@@ -9127,7 +9127,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G302" t="n">
-        <v>0.67246800661087</v>
+        <v>0.672468066215515</v>
       </c>
       <c r="H302" t="n">
         <v>10000</v>
@@ -9156,7 +9156,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G303" t="n">
-        <v>0.674053966999054</v>
+        <v>0.674054086208344</v>
       </c>
       <c r="H303" t="n">
         <v>6000</v>
@@ -9185,7 +9185,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G304" t="n">
-        <v>0.696258187294006</v>
+        <v>0.696258246898651</v>
       </c>
       <c r="H304" t="n">
         <v>16800</v>
@@ -9214,7 +9214,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>0.678019106388092</v>
+        <v>0.678019046783447</v>
       </c>
       <c r="H305" t="n">
         <v>33600</v>
@@ -9243,7 +9243,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G306" t="n">
-        <v>0.658193945884705</v>
+        <v>0.65819388628006</v>
       </c>
       <c r="H306" t="n">
         <v>12800</v>
@@ -9301,7 +9301,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G308" t="n">
-        <v>0.672864496707916</v>
+        <v>0.672864556312561</v>
       </c>
       <c r="H308" t="n">
         <v>2800</v>
@@ -9330,7 +9330,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G309" t="n">
-        <v>0.672864496707916</v>
+        <v>0.672864556312561</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G310" t="n">
-        <v>0.674053966999054</v>
+        <v>0.674054086208344</v>
       </c>
       <c r="H310" t="n">
         <v>10400</v>
@@ -9388,7 +9388,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G311" t="n">
-        <v>0.662158906459808</v>
+        <v>0.662158966064453</v>
       </c>
       <c r="H311" t="n">
         <v>50000</v>
@@ -9446,7 +9446,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G313" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H313" t="n">
         <v>40800</v>
@@ -9504,7 +9504,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G315" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H315" t="n">
         <v>88400</v>
@@ -9562,7 +9562,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>0.649470865726471</v>
+        <v>0.649470925331116</v>
       </c>
       <c r="H317" t="n">
         <v>30000</v>
@@ -9620,7 +9620,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G319" t="n">
-        <v>0.698637127876282</v>
+        <v>0.698637187480927</v>
       </c>
       <c r="H319" t="n">
         <v>65200</v>
@@ -9649,7 +9649,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G320" t="n">
-        <v>0.689121186733246</v>
+        <v>0.689121127128601</v>
       </c>
       <c r="H320" t="n">
         <v>149200</v>
@@ -9678,7 +9678,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>0.689914166927338</v>
+        <v>0.689914107322693</v>
       </c>
       <c r="H321" t="n">
         <v>191200</v>
@@ -9765,7 +9765,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G324" t="n">
-        <v>0.718462347984314</v>
+        <v>0.718462288379669</v>
       </c>
       <c r="H324" t="n">
         <v>52400</v>
@@ -9794,7 +9794,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G325" t="n">
-        <v>0.722427308559418</v>
+        <v>0.722427368164062</v>
       </c>
       <c r="H325" t="n">
         <v>19600</v>
@@ -9968,7 +9968,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G331" t="n">
-        <v>0.816794872283936</v>
+        <v>0.816794812679291</v>
       </c>
       <c r="H331" t="n">
         <v>171600</v>
@@ -10084,7 +10084,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G335" t="n">
-        <v>0.850101053714752</v>
+        <v>0.850101113319397</v>
       </c>
       <c r="H335" t="n">
         <v>56000</v>
@@ -10200,7 +10200,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G339" t="n">
-        <v>0.840584993362427</v>
+        <v>0.840584933757782</v>
       </c>
       <c r="H339" t="n">
         <v>91600</v>
@@ -10287,7 +10287,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G342" t="n">
-        <v>0.847011506557465</v>
+        <v>0.847011566162109</v>
       </c>
       <c r="H342" t="n">
         <v>92000</v>
@@ -10316,7 +10316,7 @@
         <v>1.0110000371933</v>
       </c>
       <c r="G343" t="n">
-        <v>0.843673586845398</v>
+        <v>0.843673646450043</v>
       </c>
       <c r="H343" t="n">
         <v>36400</v>
@@ -10345,7 +10345,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G344" t="n">
-        <v>0.842839062213898</v>
+        <v>0.842839002609253</v>
       </c>
       <c r="H344" t="n">
         <v>42800</v>
@@ -10403,7 +10403,7 @@
         <v>1.00899994373322</v>
       </c>
       <c r="G346" t="n">
-        <v>0.842004537582397</v>
+        <v>0.842004597187042</v>
       </c>
       <c r="H346" t="n">
         <v>32400</v>
@@ -10432,7 +10432,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G347" t="n">
-        <v>0.838666617870331</v>
+        <v>0.838666677474976</v>
       </c>
       <c r="H347" t="n">
         <v>16000</v>
@@ -10490,7 +10490,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G349" t="n">
-        <v>0.824897468090057</v>
+        <v>0.824897527694702</v>
       </c>
       <c r="H349" t="n">
         <v>400</v>
@@ -10635,7 +10635,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G354" t="n">
-        <v>0.867039382457733</v>
+        <v>0.867039442062378</v>
       </c>
       <c r="H354" t="n">
         <v>297600</v>
@@ -10780,7 +10780,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G359" t="n">
-        <v>1.11071157455444</v>
+        <v>1.11071169376373</v>
       </c>
       <c r="H359" t="n">
         <v>314400</v>
@@ -10925,7 +10925,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G364" t="n">
-        <v>1.01391053199768</v>
+        <v>1.01391041278839</v>
       </c>
       <c r="H364" t="n">
         <v>24400</v>
@@ -10954,7 +10954,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G365" t="n">
-        <v>0.973854660987854</v>
+        <v>0.973854720592499</v>
       </c>
       <c r="H365" t="n">
         <v>172400</v>
@@ -11012,7 +11012,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G367" t="n">
-        <v>0.997220516204834</v>
+        <v>0.997220575809479</v>
       </c>
       <c r="H367" t="n">
         <v>41200</v>
@@ -11070,7 +11070,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G369" t="n">
-        <v>1.04812479019165</v>
+        <v>1.04812467098236</v>
       </c>
       <c r="H369" t="n">
         <v>56400</v>
@@ -11099,7 +11099,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G370" t="n">
-        <v>1.04562127590179</v>
+        <v>1.0456211566925</v>
       </c>
       <c r="H370" t="n">
         <v>85200</v>
@@ -11128,7 +11128,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G371" t="n">
-        <v>1.1006977558136</v>
+        <v>1.10069787502289</v>
       </c>
       <c r="H371" t="n">
         <v>264800</v>
@@ -11215,7 +11215,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G374" t="n">
-        <v>1.04812479019165</v>
+        <v>1.04812467098236</v>
       </c>
       <c r="H374" t="n">
         <v>59600</v>
@@ -11302,7 +11302,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G377" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H377" t="n">
         <v>12000</v>
@@ -11360,7 +11360,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>0.982199728488922</v>
+        <v>0.982199609279633</v>
       </c>
       <c r="H379" t="n">
         <v>12400</v>
@@ -11389,7 +11389,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G380" t="n">
-        <v>0.991379022598267</v>
+        <v>0.991379082202911</v>
       </c>
       <c r="H380" t="n">
         <v>3600</v>
@@ -11447,7 +11447,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G382" t="n">
-        <v>0.97635817527771</v>
+        <v>0.976358115673065</v>
       </c>
       <c r="H382" t="n">
         <v>22800</v>
@@ -11476,7 +11476,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G383" t="n">
-        <v>0.979696154594421</v>
+        <v>0.979696094989777</v>
       </c>
       <c r="H383" t="n">
         <v>25200</v>
@@ -11505,7 +11505,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G384" t="n">
-        <v>0.961337149143219</v>
+        <v>0.961337268352509</v>
       </c>
       <c r="H384" t="n">
         <v>13200</v>
@@ -11563,7 +11563,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>0.954661309719086</v>
+        <v>0.95466148853302</v>
       </c>
       <c r="H386" t="n">
         <v>22000</v>
@@ -11592,7 +11592,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G387" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H387" t="n">
         <v>65200</v>
@@ -11621,7 +11621,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G388" t="n">
-        <v>0.997220516204834</v>
+        <v>0.997220575809479</v>
       </c>
       <c r="H388" t="n">
         <v>8000</v>
@@ -11650,7 +11650,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G389" t="n">
-        <v>0.978027164936066</v>
+        <v>0.97802722454071</v>
       </c>
       <c r="H389" t="n">
         <v>7200</v>
@@ -11708,7 +11708,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G391" t="n">
-        <v>0.971351206302643</v>
+        <v>0.971351325511932</v>
       </c>
       <c r="H391" t="n">
         <v>7600</v>
@@ -11737,7 +11737,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G392" t="n">
-        <v>0.971351206302643</v>
+        <v>0.971351325511932</v>
       </c>
       <c r="H392" t="n">
         <v>2400</v>
@@ -11853,7 +11853,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G396" t="n">
-        <v>0.97552365064621</v>
+        <v>0.975523710250854</v>
       </c>
       <c r="H396" t="n">
         <v>20400</v>
@@ -11940,7 +11940,7 @@
         <v>1.125</v>
       </c>
       <c r="G399" t="n">
-        <v>0.938805818557739</v>
+        <v>0.938805878162384</v>
       </c>
       <c r="H399" t="n">
         <v>400</v>
@@ -12027,7 +12027,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G402" t="n">
-        <v>1.04144871234894</v>
+        <v>1.04144883155823</v>
       </c>
       <c r="H402" t="n">
         <v>101200</v>
@@ -12056,7 +12056,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G403" t="n">
-        <v>1.0347728729248</v>
+        <v>1.03477275371552</v>
       </c>
       <c r="H403" t="n">
         <v>32400</v>
@@ -12085,7 +12085,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G404" t="n">
-        <v>1.0347728729248</v>
+        <v>1.03477275371552</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G405" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H405" t="n">
         <v>6000</v>
@@ -12143,7 +12143,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G406" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H406" t="n">
         <v>36800</v>
@@ -12172,7 +12172,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.07232487201691</v>
+        <v>1.0723249912262</v>
       </c>
       <c r="H407" t="n">
         <v>139600</v>
@@ -12259,7 +12259,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G410" t="n">
-        <v>1.0347728729248</v>
+        <v>1.03477275371552</v>
       </c>
       <c r="H410" t="n">
         <v>7600</v>
@@ -12288,7 +12288,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G411" t="n">
-        <v>1.02893137931824</v>
+        <v>1.02893126010895</v>
       </c>
       <c r="H411" t="n">
         <v>37200</v>
@@ -12317,7 +12317,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H412" t="n">
         <v>53200</v>
@@ -12346,7 +12346,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G413" t="n">
-        <v>0.986372113227844</v>
+        <v>0.986372053623199</v>
       </c>
       <c r="H413" t="n">
         <v>21200</v>
@@ -12404,7 +12404,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G415" t="n">
-        <v>0.971351206302643</v>
+        <v>0.971351325511932</v>
       </c>
       <c r="H415" t="n">
         <v>30800</v>
@@ -12462,7 +12462,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G417" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H417" t="n">
         <v>60000</v>
@@ -12520,7 +12520,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G419" t="n">
-        <v>0.982199728488922</v>
+        <v>0.982199609279633</v>
       </c>
       <c r="H419" t="n">
         <v>50000</v>
@@ -12549,7 +12549,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G420" t="n">
-        <v>0.982199728488922</v>
+        <v>0.982199609279633</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G422" t="n">
-        <v>0.97635817527771</v>
+        <v>0.976358115673065</v>
       </c>
       <c r="H422" t="n">
         <v>11200</v>
@@ -12636,7 +12636,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G423" t="n">
-        <v>0.994717121124268</v>
+        <v>0.994717061519623</v>
       </c>
       <c r="H423" t="n">
         <v>400</v>
@@ -12665,7 +12665,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G424" t="n">
-        <v>0.979696154594421</v>
+        <v>0.979696094989777</v>
       </c>
       <c r="H424" t="n">
         <v>9200</v>
@@ -12694,7 +12694,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G425" t="n">
-        <v>0.979696154594421</v>
+        <v>0.979696094989777</v>
       </c>
       <c r="H425" t="n">
         <v>400</v>
@@ -12752,7 +12752,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G427" t="n">
-        <v>0.978027164936066</v>
+        <v>0.97802722454071</v>
       </c>
       <c r="H427" t="n">
         <v>31600</v>
@@ -12810,7 +12810,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G429" t="n">
-        <v>0.988041043281555</v>
+        <v>0.9880411028862</v>
       </c>
       <c r="H429" t="n">
         <v>5200</v>
@@ -12868,7 +12868,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G431" t="n">
-        <v>0.981365144252777</v>
+        <v>0.981365084648132</v>
       </c>
       <c r="H431" t="n">
         <v>3600</v>
@@ -12926,7 +12926,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G433" t="n">
-        <v>0.962171792984009</v>
+        <v>0.962171673774719</v>
       </c>
       <c r="H433" t="n">
         <v>32800</v>
@@ -12955,7 +12955,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G434" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H434" t="n">
         <v>10000</v>
@@ -13071,7 +13071,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G438" t="n">
-        <v>0.91794365644455</v>
+        <v>0.91794353723526</v>
       </c>
       <c r="H438" t="n">
         <v>164800</v>
@@ -13100,7 +13100,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G439" t="n">
-        <v>0.957999169826508</v>
+        <v>0.957999289035797</v>
       </c>
       <c r="H439" t="n">
         <v>80000</v>
@@ -13129,7 +13129,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G440" t="n">
-        <v>0.91794365644455</v>
+        <v>0.91794353723526</v>
       </c>
       <c r="H440" t="n">
         <v>138000</v>
@@ -13216,7 +13216,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G443" t="n">
-        <v>0.900419116020203</v>
+        <v>0.900419235229492</v>
       </c>
       <c r="H443" t="n">
         <v>11600</v>
@@ -13245,7 +13245,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G444" t="n">
-        <v>0.932964384555817</v>
+        <v>0.932964503765106</v>
       </c>
       <c r="H444" t="n">
         <v>26400</v>
@@ -13274,7 +13274,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G445" t="n">
-        <v>0.935467958450317</v>
+        <v>0.935468018054962</v>
       </c>
       <c r="H445" t="n">
         <v>21600</v>
@@ -13332,7 +13332,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G447" t="n">
-        <v>0.967178761959076</v>
+        <v>0.967178702354431</v>
       </c>
       <c r="H447" t="n">
         <v>137200</v>
@@ -13390,7 +13390,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>0.949654400348663</v>
+        <v>0.949654340744019</v>
       </c>
       <c r="H449" t="n">
         <v>18400</v>
@@ -13419,7 +13419,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G450" t="n">
-        <v>0.954661309719086</v>
+        <v>0.95466148853302</v>
       </c>
       <c r="H450" t="n">
         <v>4800</v>
@@ -13477,7 +13477,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G452" t="n">
-        <v>0.949654400348663</v>
+        <v>0.949654340744019</v>
       </c>
       <c r="H452" t="n">
         <v>32800</v>
@@ -13535,7 +13535,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G454" t="n">
-        <v>0.983034133911133</v>
+        <v>0.983034074306488</v>
       </c>
       <c r="H454" t="n">
         <v>96800</v>
@@ -13593,7 +13593,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G456" t="n">
-        <v>0.994717121124268</v>
+        <v>0.994717061519623</v>
       </c>
       <c r="H456" t="n">
         <v>119200</v>
@@ -13622,7 +13622,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G457" t="n">
-        <v>1.00222742557526</v>
+        <v>1.00222754478455</v>
       </c>
       <c r="H457" t="n">
         <v>43200</v>
@@ -13651,7 +13651,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G458" t="n">
-        <v>1.02642786502838</v>
+        <v>1.02642774581909</v>
       </c>
       <c r="H458" t="n">
         <v>73200</v>
@@ -13680,7 +13680,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G459" t="n">
-        <v>1.0347728729248</v>
+        <v>1.03477275371552</v>
       </c>
       <c r="H459" t="n">
         <v>89200</v>
@@ -13796,7 +13796,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G463" t="n">
-        <v>1.26092064380646</v>
+        <v>1.26092052459717</v>
       </c>
       <c r="H463" t="n">
         <v>311600</v>
@@ -13854,7 +13854,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G465" t="n">
-        <v>1.28679001331329</v>
+        <v>1.28679013252258</v>
       </c>
       <c r="H465" t="n">
         <v>1049200</v>
@@ -13941,7 +13941,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.27677595615387</v>
+        <v>1.27677607536316</v>
       </c>
       <c r="H468" t="n">
         <v>47600</v>
@@ -14144,7 +14144,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G475" t="n">
-        <v>1.3185008764267</v>
+        <v>1.31850075721741</v>
       </c>
       <c r="H475" t="n">
         <v>29200</v>
@@ -14173,7 +14173,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G476" t="n">
-        <v>1.30181086063385</v>
+        <v>1.30181074142456</v>
       </c>
       <c r="H476" t="n">
         <v>16400</v>
@@ -14202,7 +14202,7 @@
         <v>1.5</v>
       </c>
       <c r="G477" t="n">
-        <v>1.25174129009247</v>
+        <v>1.25174117088318</v>
       </c>
       <c r="H477" t="n">
         <v>84000</v>
@@ -14260,7 +14260,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G479" t="n">
-        <v>1.20834755897522</v>
+        <v>1.20834743976593</v>
       </c>
       <c r="H479" t="n">
         <v>42800</v>
@@ -14289,7 +14289,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>1.16912639141083</v>
+        <v>1.16912627220154</v>
       </c>
       <c r="H480" t="n">
         <v>12000</v>
@@ -14318,7 +14318,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G481" t="n">
-        <v>1.14325702190399</v>
+        <v>1.1432569026947</v>
       </c>
       <c r="H481" t="n">
         <v>42400</v>
@@ -14347,7 +14347,7 @@
         <v>1.39699995517731</v>
       </c>
       <c r="G482" t="n">
-        <v>1.16578817367554</v>
+        <v>1.16578829288483</v>
       </c>
       <c r="H482" t="n">
         <v>11600</v>
@@ -14434,7 +14434,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>1.16411936283112</v>
+        <v>1.16411924362183</v>
       </c>
       <c r="H485" t="n">
         <v>13600</v>
@@ -14637,7 +14637,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G492" t="n">
-        <v>1.16829180717468</v>
+        <v>1.16829192638397</v>
       </c>
       <c r="H492" t="n">
         <v>17200</v>
@@ -14666,7 +14666,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G493" t="n">
-        <v>1.17580235004425</v>
+        <v>1.17580211162567</v>
       </c>
       <c r="H493" t="n">
         <v>1600</v>
@@ -14695,7 +14695,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G494" t="n">
-        <v>1.24339640140533</v>
+        <v>1.24339616298676</v>
       </c>
       <c r="H494" t="n">
         <v>29600</v>
@@ -14782,7 +14782,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G497" t="n">
-        <v>1.18331277370453</v>
+        <v>1.18331265449524</v>
       </c>
       <c r="H497" t="n">
         <v>35600</v>
@@ -14840,7 +14840,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G499" t="n">
-        <v>1.17580235004425</v>
+        <v>1.17580211162567</v>
       </c>
       <c r="H499" t="n">
         <v>2800</v>
@@ -14898,7 +14898,7 @@
         <v>1.39900004863739</v>
       </c>
       <c r="G501" t="n">
-        <v>1.16745734214783</v>
+        <v>1.16745746135712</v>
       </c>
       <c r="H501" t="n">
         <v>23600</v>
@@ -14927,7 +14927,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>1.16411936283112</v>
+        <v>1.16411924362183</v>
       </c>
       <c r="H502" t="n">
         <v>4800</v>
@@ -14985,7 +14985,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.15577435493469</v>
+        <v>1.15577447414398</v>
       </c>
       <c r="H504" t="n">
         <v>4800</v>
@@ -15014,7 +15014,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G505" t="n">
-        <v>1.15577435493469</v>
+        <v>1.15577447414398</v>
       </c>
       <c r="H505" t="n">
         <v>12800</v>
@@ -15043,7 +15043,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G506" t="n">
-        <v>1.09652519226074</v>
+        <v>1.09652531147003</v>
       </c>
       <c r="H506" t="n">
         <v>207600</v>
@@ -15072,7 +15072,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G507" t="n">
-        <v>1.12406361103058</v>
+        <v>1.12406373023987</v>
       </c>
       <c r="H507" t="n">
         <v>13600</v>
@@ -15101,7 +15101,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G508" t="n">
-        <v>1.09986329078674</v>
+        <v>1.09986317157745</v>
       </c>
       <c r="H508" t="n">
         <v>24400</v>
@@ -15188,7 +15188,7 @@
         <v>1.36300003528595</v>
       </c>
       <c r="G511" t="n">
-        <v>1.13741552829742</v>
+        <v>1.13741564750671</v>
       </c>
       <c r="H511" t="n">
         <v>19600</v>
@@ -15391,7 +15391,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.11822211742401</v>
+        <v>1.1182222366333</v>
       </c>
       <c r="H518" t="n">
         <v>30400</v>
@@ -15420,7 +15420,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.11822211742401</v>
+        <v>1.1182222366333</v>
       </c>
       <c r="H519" t="n">
         <v>25600</v>
@@ -15536,7 +15536,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G523" t="n">
-        <v>1.15160191059113</v>
+        <v>1.15160202980042</v>
       </c>
       <c r="H523" t="n">
         <v>36800</v>
@@ -15594,7 +15594,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G525" t="n">
-        <v>1.14325702190399</v>
+        <v>1.1432569026947</v>
       </c>
       <c r="H525" t="n">
         <v>14800</v>
@@ -15768,7 +15768,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G531" t="n">
-        <v>1.11822211742401</v>
+        <v>1.1182222366333</v>
       </c>
       <c r="H531" t="n">
         <v>2800</v>
@@ -15913,7 +15913,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>1.0598076581955</v>
+        <v>1.05980753898621</v>
       </c>
       <c r="H536" t="n">
         <v>30400</v>
@@ -15942,7 +15942,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G537" t="n">
-        <v>0.997220516204834</v>
+        <v>0.997220575809479</v>
       </c>
       <c r="H537" t="n">
         <v>70800</v>
@@ -15971,7 +15971,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G538" t="n">
-        <v>1.01808285713196</v>
+        <v>1.01808297634125</v>
       </c>
       <c r="H538" t="n">
         <v>4000</v>
@@ -16116,7 +16116,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G543" t="n">
-        <v>0.947150766849518</v>
+        <v>0.947150945663452</v>
       </c>
       <c r="H543" t="n">
         <v>27200</v>
@@ -16203,7 +16203,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G546" t="n">
-        <v>0.926288425922394</v>
+        <v>0.926288545131683</v>
       </c>
       <c r="H546" t="n">
         <v>20800</v>
@@ -16290,7 +16290,7 @@
         <v>1.125</v>
       </c>
       <c r="G549" t="n">
-        <v>0.938805818557739</v>
+        <v>0.938805878162384</v>
       </c>
       <c r="H549" t="n">
         <v>43600</v>
@@ -16348,7 +16348,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G551" t="n">
-        <v>0.947150766849518</v>
+        <v>0.947150945663452</v>
       </c>
       <c r="H551" t="n">
         <v>61600</v>
@@ -16406,7 +16406,7 @@
         <v>1.125</v>
       </c>
       <c r="G553" t="n">
-        <v>0.938805818557739</v>
+        <v>0.938805878162384</v>
       </c>
       <c r="H553" t="n">
         <v>2000</v>
@@ -16435,7 +16435,7 @@
         <v>1.125</v>
       </c>
       <c r="G554" t="n">
-        <v>0.938805818557739</v>
+        <v>0.938805878162384</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G555" t="n">
-        <v>0.926288425922394</v>
+        <v>0.926288545131683</v>
       </c>
       <c r="H555" t="n">
         <v>32800</v>
@@ -16522,7 +16522,7 @@
         <v>1.125</v>
       </c>
       <c r="G557" t="n">
-        <v>0.938805818557739</v>
+        <v>0.938805878162384</v>
       </c>
       <c r="H557" t="n">
         <v>17600</v>
@@ -16580,7 +16580,7 @@
         <v>1.125</v>
       </c>
       <c r="G559" t="n">
-        <v>0.938805818557739</v>
+        <v>0.938805878162384</v>
       </c>
       <c r="H559" t="n">
         <v>40000</v>
@@ -16696,7 +16696,7 @@
         <v>1.125</v>
       </c>
       <c r="G563" t="n">
-        <v>0.938805818557739</v>
+        <v>0.938805878162384</v>
       </c>
       <c r="H563" t="n">
         <v>800</v>
@@ -16812,7 +16812,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>0.955495834350586</v>
+        <v>0.955495715141296</v>
       </c>
       <c r="H567" t="n">
         <v>5200</v>
@@ -16899,7 +16899,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G570" t="n">
-        <v>1.01808285713196</v>
+        <v>1.01808297634125</v>
       </c>
       <c r="H570" t="n">
         <v>12000</v>
@@ -16928,7 +16928,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G571" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H571" t="n">
         <v>4000</v>
@@ -17015,7 +17015,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.06398010253906</v>
+        <v>1.06397998332977</v>
       </c>
       <c r="H574" t="n">
         <v>18800</v>
@@ -17044,7 +17044,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G575" t="n">
-        <v>1.02642786502838</v>
+        <v>1.02642774581909</v>
       </c>
       <c r="H575" t="n">
         <v>16800</v>
@@ -17073,7 +17073,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H576" t="n">
         <v>56800</v>
@@ -17102,7 +17102,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G577" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H577" t="n">
         <v>11600</v>
@@ -17131,7 +17131,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>0.980530619621277</v>
+        <v>0.980530560016632</v>
       </c>
       <c r="H579" t="n">
         <v>3200</v>
@@ -17189,7 +17189,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H580" t="n">
         <v>4000</v>
@@ -17218,7 +17218,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G581" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048071861267</v>
       </c>
       <c r="H581" t="n">
         <v>1600</v>
@@ -17247,7 +17247,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.0598076581955</v>
+        <v>1.05980753898621</v>
       </c>
       <c r="H582" t="n">
         <v>129600</v>
@@ -17334,7 +17334,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G585" t="n">
-        <v>1.14325702190399</v>
+        <v>1.1432569026947</v>
       </c>
       <c r="H585" t="n">
         <v>101600</v>
@@ -17392,7 +17392,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>1.19749915599823</v>
+        <v>1.19749903678894</v>
       </c>
       <c r="H587" t="n">
         <v>127600</v>
@@ -17450,7 +17450,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G589" t="n">
-        <v>1.21001672744751</v>
+        <v>1.21001648902893</v>
       </c>
       <c r="H589" t="n">
         <v>34400</v>
@@ -17479,7 +17479,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G590" t="n">
-        <v>1.19332659244537</v>
+        <v>1.19332647323608</v>
       </c>
       <c r="H590" t="n">
         <v>18400</v>
@@ -17508,7 +17508,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G591" t="n">
-        <v>1.16829180717468</v>
+        <v>1.16829192638397</v>
       </c>
       <c r="H591" t="n">
         <v>14000</v>
@@ -17566,7 +17566,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G593" t="n">
-        <v>1.19332659244537</v>
+        <v>1.19332647323608</v>
       </c>
       <c r="H593" t="n">
         <v>14800</v>
@@ -17653,7 +17653,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>1.285120844841</v>
+        <v>1.28512096405029</v>
       </c>
       <c r="H596" t="n">
         <v>419200</v>
@@ -17682,7 +17682,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.31015574932098</v>
+        <v>1.31015586853027</v>
       </c>
       <c r="H597" t="n">
         <v>117200</v>
@@ -17711,7 +17711,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G598" t="n">
-        <v>1.3354823589325</v>
+        <v>1.33548247814178</v>
       </c>
       <c r="H598" t="n">
         <v>36400</v>
@@ -17798,7 +17798,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G601" t="n">
-        <v>1.27929711341858</v>
+        <v>1.27929723262787</v>
       </c>
       <c r="H601" t="n">
         <v>14000</v>
@@ -17885,7 +17885,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G604" t="n">
-        <v>1.27929711341858</v>
+        <v>1.27929723262787</v>
       </c>
       <c r="H604" t="n">
         <v>20000</v>
@@ -18204,7 +18204,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G615" t="n">
-        <v>1.21014606952667</v>
+        <v>1.21014595031738</v>
       </c>
       <c r="H615" t="n">
         <v>69200</v>
@@ -18291,7 +18291,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>1.33116054534912</v>
+        <v>1.33116042613983</v>
       </c>
       <c r="H618" t="n">
         <v>26000</v>
@@ -18320,7 +18320,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G619" t="n">
-        <v>1.3354823589325</v>
+        <v>1.33548247814178</v>
       </c>
       <c r="H619" t="n">
         <v>46400</v>
@@ -18378,7 +18378,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>1.33116054534912</v>
+        <v>1.33116042613983</v>
       </c>
       <c r="H621" t="n">
         <v>10400</v>
@@ -18494,7 +18494,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G625" t="n">
-        <v>1.3225165605545</v>
+        <v>1.32251667976379</v>
       </c>
       <c r="H625" t="n">
         <v>19600</v>
@@ -18581,7 +18581,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>1.27929711341858</v>
+        <v>1.27929723262787</v>
       </c>
       <c r="H628" t="n">
         <v>12000</v>
@@ -18639,7 +18639,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G630" t="n">
-        <v>1.3225165605545</v>
+        <v>1.32251667976379</v>
       </c>
       <c r="H630" t="n">
         <v>42400</v>
@@ -18755,7 +18755,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.41327750682831</v>
+        <v>1.4132776260376</v>
       </c>
       <c r="H634" t="n">
         <v>123200</v>
@@ -18784,7 +18784,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G635" t="n">
-        <v>1.40895569324493</v>
+        <v>1.40895557403564</v>
       </c>
       <c r="H635" t="n">
         <v>83600</v>
@@ -19016,7 +19016,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G643" t="n">
-        <v>1.49971663951874</v>
+        <v>1.49971652030945</v>
       </c>
       <c r="H643" t="n">
         <v>56800</v>
@@ -19132,7 +19132,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G647" t="n">
-        <v>1.41327750682831</v>
+        <v>1.4132776260376</v>
       </c>
       <c r="H647" t="n">
         <v>15200</v>
@@ -19248,7 +19248,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G651" t="n">
-        <v>1.60344338417053</v>
+        <v>1.60344350337982</v>
       </c>
       <c r="H651" t="n">
         <v>191600</v>
@@ -19335,7 +19335,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>1.71149218082428</v>
+        <v>1.71149206161499</v>
       </c>
       <c r="H654" t="n">
         <v>197600</v>
@@ -19422,7 +19422,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>1.98809695243835</v>
+        <v>1.98809683322906</v>
       </c>
       <c r="H657" t="n">
         <v>588000</v>
@@ -19451,7 +19451,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>2.01402854919434</v>
+        <v>2.01402831077576</v>
       </c>
       <c r="H658" t="n">
         <v>342800</v>
@@ -19480,7 +19480,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>1.96216511726379</v>
+        <v>1.96216535568237</v>
       </c>
       <c r="H659" t="n">
         <v>80000</v>
@@ -19596,7 +19596,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G663" t="n">
-        <v>1.91894578933716</v>
+        <v>1.91894567012787</v>
       </c>
       <c r="H663" t="n">
         <v>15600</v>
@@ -19683,7 +19683,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G666" t="n">
-        <v>1.91894578933716</v>
+        <v>1.91894567012787</v>
       </c>
       <c r="H666" t="n">
         <v>10400</v>
@@ -19712,7 +19712,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>1.9275895357132</v>
+        <v>1.92758965492249</v>
       </c>
       <c r="H667" t="n">
         <v>50000</v>
@@ -19741,7 +19741,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945284843445</v>
       </c>
       <c r="H668" t="n">
         <v>50400</v>
@@ -19770,7 +19770,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G669" t="n">
-        <v>1.98809695243835</v>
+        <v>1.98809683322906</v>
       </c>
       <c r="H669" t="n">
         <v>24800</v>
@@ -19799,7 +19799,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.98809695243835</v>
+        <v>1.98809683322906</v>
       </c>
       <c r="H670" t="n">
         <v>18400</v>
@@ -19828,7 +19828,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G671" t="n">
-        <v>2.01402854919434</v>
+        <v>2.01402831077576</v>
       </c>
       <c r="H671" t="n">
         <v>7600</v>
@@ -19857,7 +19857,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G672" t="n">
-        <v>1.96216511726379</v>
+        <v>1.96216535568237</v>
       </c>
       <c r="H672" t="n">
         <v>52000</v>
@@ -19886,7 +19886,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945284843445</v>
       </c>
       <c r="H673" t="n">
         <v>17200</v>
@@ -19915,7 +19915,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.96216511726379</v>
+        <v>1.96216535568237</v>
       </c>
       <c r="H674" t="n">
         <v>15200</v>
@@ -19973,7 +19973,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945284843445</v>
       </c>
       <c r="H676" t="n">
         <v>10000</v>
@@ -20002,7 +20002,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>1.91894578933716</v>
+        <v>1.91894567012787</v>
       </c>
       <c r="H677" t="n">
         <v>38000</v>
@@ -20118,7 +20118,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G681" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945284843445</v>
       </c>
       <c r="H681" t="n">
         <v>18000</v>
@@ -20147,7 +20147,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>1.98809695243835</v>
+        <v>1.98809683322906</v>
       </c>
       <c r="H682" t="n">
         <v>10000</v>
@@ -20176,7 +20176,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945284843445</v>
       </c>
       <c r="H683" t="n">
         <v>16000</v>
@@ -20205,7 +20205,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>1.99674069881439</v>
+        <v>1.99674081802368</v>
       </c>
       <c r="H684" t="n">
         <v>23600</v>
@@ -20263,7 +20263,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>2.11775541305542</v>
+        <v>2.117755651474</v>
       </c>
       <c r="H686" t="n">
         <v>130800</v>
@@ -20292,7 +20292,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G687" t="n">
-        <v>2.17826247215271</v>
+        <v>2.17826271057129</v>
       </c>
       <c r="H687" t="n">
         <v>109200</v>
@@ -20321,7 +20321,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G688" t="n">
-        <v>2.16961884498596</v>
+        <v>2.16961860656738</v>
       </c>
       <c r="H688" t="n">
         <v>52000</v>
@@ -20379,7 +20379,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G690" t="n">
-        <v>2.26470184326172</v>
+        <v>2.26470160484314</v>
       </c>
       <c r="H690" t="n">
         <v>39200</v>
@@ -20408,7 +20408,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G691" t="n">
-        <v>2.40300393104553</v>
+        <v>2.40300416946411</v>
       </c>
       <c r="H691" t="n">
         <v>131200</v>
@@ -20524,7 +20524,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G695" t="n">
-        <v>2.42029213905334</v>
+        <v>2.42029190063477</v>
       </c>
       <c r="H695" t="n">
         <v>59200</v>
@@ -20582,7 +20582,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>2.5067310333252</v>
+        <v>2.50673079490662</v>
       </c>
       <c r="H697" t="n">
         <v>142400</v>
@@ -20611,7 +20611,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G698" t="n">
-        <v>2.42029213905334</v>
+        <v>2.42029190063477</v>
       </c>
       <c r="H698" t="n">
         <v>497600</v>
@@ -20640,7 +20640,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>2.42029213905334</v>
+        <v>2.42029190063477</v>
       </c>
       <c r="H699" t="n">
         <v>70400</v>
@@ -20669,7 +20669,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>2.41164803504944</v>
+        <v>2.41164779663086</v>
       </c>
       <c r="H700" t="n">
         <v>22000</v>
@@ -20698,7 +20698,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>2.35978436470032</v>
+        <v>2.3597846031189</v>
       </c>
       <c r="H701" t="n">
         <v>76400</v>
@@ -20727,7 +20727,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>2.35978436470032</v>
+        <v>2.3597846031189</v>
       </c>
       <c r="H702" t="n">
         <v>28000</v>
@@ -20756,7 +20756,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G703" t="n">
-        <v>2.24741363525391</v>
+        <v>2.24741387367249</v>
       </c>
       <c r="H703" t="n">
         <v>97600</v>
@@ -20785,7 +20785,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>2.24741363525391</v>
+        <v>2.24741387367249</v>
       </c>
       <c r="H704" t="n">
         <v>55200</v>
@@ -20959,7 +20959,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G710" t="n">
-        <v>2.26470184326172</v>
+        <v>2.26470160484314</v>
       </c>
       <c r="H710" t="n">
         <v>29600</v>
@@ -20988,7 +20988,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>2.27334547042847</v>
+        <v>2.27334570884705</v>
       </c>
       <c r="H711" t="n">
         <v>11200</v>
@@ -21017,7 +21017,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G712" t="n">
-        <v>2.27334547042847</v>
+        <v>2.27334570884705</v>
       </c>
       <c r="H712" t="n">
         <v>31600</v>
@@ -21046,7 +21046,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G713" t="n">
-        <v>2.27334547042847</v>
+        <v>2.27334570884705</v>
       </c>
       <c r="H713" t="n">
         <v>18400</v>
@@ -21104,7 +21104,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G715" t="n">
-        <v>2.51537466049194</v>
+        <v>2.51537489891052</v>
       </c>
       <c r="H715" t="n">
         <v>298000</v>
@@ -21481,7 +21481,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G728" t="n">
-        <v>3.05129647254944</v>
+        <v>3.05129671096802</v>
       </c>
       <c r="H728" t="n">
         <v>77200</v>
@@ -21568,7 +21568,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G731" t="n">
-        <v>3.18959903717041</v>
+        <v>3.18959879875183</v>
       </c>
       <c r="H731" t="n">
         <v>43600</v>
@@ -22177,7 +22177,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G752" t="n">
-        <v>2.73147225379944</v>
+        <v>2.73147249221802</v>
       </c>
       <c r="H752" t="n">
         <v>13600</v>
@@ -22235,7 +22235,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G754" t="n">
-        <v>2.73147225379944</v>
+        <v>2.73147249221802</v>
       </c>
       <c r="H754" t="n">
         <v>5200</v>
@@ -22264,7 +22264,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G755" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H755" t="n">
         <v>3200</v>
@@ -22293,7 +22293,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G756" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H756" t="n">
         <v>4800</v>
@@ -22409,7 +22409,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G760" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H760" t="n">
         <v>24000</v>
@@ -22496,7 +22496,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G763" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H763" t="n">
         <v>53600</v>
@@ -22525,7 +22525,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G764" t="n">
-        <v>2.67096471786499</v>
+        <v>2.67096495628357</v>
       </c>
       <c r="H764" t="n">
         <v>14000</v>
@@ -22757,7 +22757,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>2.61910152435303</v>
+        <v>2.61910128593445</v>
       </c>
       <c r="H772" t="n">
         <v>5600</v>
@@ -22815,7 +22815,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G774" t="n">
-        <v>2.77469182014465</v>
+        <v>2.77469158172607</v>
       </c>
       <c r="H774" t="n">
         <v>17600</v>
@@ -22844,7 +22844,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>2.77469182014465</v>
+        <v>2.77469158172607</v>
       </c>
       <c r="H775" t="n">
         <v>12000</v>
@@ -23221,7 +23221,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G788" t="n">
-        <v>2.73147225379944</v>
+        <v>2.73147249221802</v>
       </c>
       <c r="H788" t="n">
         <v>2800</v>
@@ -23424,7 +23424,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G795" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H795" t="n">
         <v>23600</v>
@@ -23540,7 +23540,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>2.55859422683716</v>
+        <v>2.55859446525574</v>
       </c>
       <c r="H799" t="n">
         <v>34400</v>
@@ -23569,7 +23569,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G800" t="n">
-        <v>2.51537466049194</v>
+        <v>2.51537489891052</v>
       </c>
       <c r="H800" t="n">
         <v>28800</v>
@@ -23598,7 +23598,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.51537466049194</v>
+        <v>2.51537489891052</v>
       </c>
       <c r="H801" t="n">
         <v>12800</v>
@@ -23627,7 +23627,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>2.51537466049194</v>
+        <v>2.51537489891052</v>
       </c>
       <c r="H802" t="n">
         <v>119200</v>
@@ -23743,7 +23743,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>2.41164803504944</v>
+        <v>2.41164779663086</v>
       </c>
       <c r="H806" t="n">
         <v>12400</v>
@@ -23830,7 +23830,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>2.42029213905334</v>
+        <v>2.42029190063477</v>
       </c>
       <c r="H809" t="n">
         <v>7200</v>
@@ -23859,7 +23859,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40300393104553</v>
+        <v>2.40300416946411</v>
       </c>
       <c r="H810" t="n">
         <v>3600</v>
@@ -23917,7 +23917,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>2.41164803504944</v>
+        <v>2.41164779663086</v>
       </c>
       <c r="H812" t="n">
         <v>5200</v>
@@ -24207,7 +24207,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G822" t="n">
-        <v>2.73147225379944</v>
+        <v>2.73147249221802</v>
       </c>
       <c r="H822" t="n">
         <v>44800</v>
@@ -24294,7 +24294,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G825" t="n">
-        <v>2.61910152435303</v>
+        <v>2.61910128593445</v>
       </c>
       <c r="H825" t="n">
         <v>10000</v>
@@ -24410,7 +24410,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>2.69689655303955</v>
+        <v>2.69689631462097</v>
       </c>
       <c r="H829" t="n">
         <v>4800</v>
@@ -24584,7 +24584,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G835" t="n">
-        <v>2.73147225379944</v>
+        <v>2.73147249221802</v>
       </c>
       <c r="H835" t="n">
         <v>1600</v>
@@ -24671,7 +24671,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.66232109069824</v>
+        <v>2.66232085227966</v>
       </c>
       <c r="H838" t="n">
         <v>12800</v>
@@ -24729,7 +24729,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>2.61910152435303</v>
+        <v>2.61910128593445</v>
       </c>
       <c r="H840" t="n">
         <v>12800</v>
@@ -80009,6 +80009,35 @@
         <v>0</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>1.54427242279053</v>
+        <v>1.54427254199982</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -514,7 +514,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G5" t="n">
-        <v>1.43918430805206</v>
+        <v>1.43918442726135</v>
       </c>
       <c r="H5" t="n">
         <v>10800</v>
@@ -543,7 +543,7 @@
         <v>1.92900002002716</v>
       </c>
       <c r="G6" t="n">
-        <v>1.43769383430481</v>
+        <v>1.43769371509552</v>
       </c>
       <c r="H6" t="n">
         <v>400</v>
@@ -775,7 +775,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G14" t="n">
-        <v>1.33931338787079</v>
+        <v>1.33931350708008</v>
       </c>
       <c r="H14" t="n">
         <v>2800</v>
@@ -891,7 +891,7 @@
         <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30428409576416</v>
+        <v>1.30428397655487</v>
       </c>
       <c r="H18" t="n">
         <v>8800</v>
@@ -920,7 +920,7 @@
         <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.30428409576416</v>
+        <v>1.30428397655487</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G20" t="n">
-        <v>1.26701879501343</v>
+        <v>1.26701891422272</v>
       </c>
       <c r="H20" t="n">
         <v>5600</v>
@@ -978,7 +978,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>1.29981231689453</v>
+        <v>1.29981219768524</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.27447211742401</v>
+        <v>1.27447199821472</v>
       </c>
       <c r="H22" t="n">
         <v>1200</v>
@@ -1268,7 +1268,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>0.976349771022797</v>
+        <v>0.976349711418152</v>
       </c>
       <c r="H31" t="n">
         <v>4800</v>
@@ -1326,7 +1326,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G33" t="n">
-        <v>1.01734149456024</v>
+        <v>1.01734161376953</v>
       </c>
       <c r="H33" t="n">
         <v>4000</v>
@@ -1471,7 +1471,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G38" t="n">
-        <v>1.02106821537018</v>
+        <v>1.02106809616089</v>
       </c>
       <c r="H38" t="n">
         <v>400</v>
@@ -1500,7 +1500,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G39" t="n">
-        <v>1.02106821537018</v>
+        <v>1.02106809616089</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1529,7 +1529,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G40" t="n">
-        <v>1.02106821537018</v>
+        <v>1.02106809616089</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G41" t="n">
-        <v>1.02106821537018</v>
+        <v>1.02106809616089</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G42" t="n">
-        <v>1.02032268047333</v>
+        <v>1.02032279968262</v>
       </c>
       <c r="H42" t="n">
         <v>400</v>
@@ -1616,7 +1616,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G43" t="n">
-        <v>1.02032268047333</v>
+        <v>1.02032279968262</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G44" t="n">
-        <v>0.983802855014801</v>
+        <v>0.983802914619446</v>
       </c>
       <c r="H44" t="n">
         <v>7200</v>
@@ -1674,7 +1674,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>0.976349771022797</v>
+        <v>0.976349711418152</v>
       </c>
       <c r="H45" t="n">
         <v>3600</v>
@@ -1703,7 +1703,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G46" t="n">
-        <v>0.983802855014801</v>
+        <v>0.983802914619446</v>
       </c>
       <c r="H46" t="n">
         <v>5600</v>
@@ -1732,7 +1732,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>0.976349771022797</v>
+        <v>0.976349711418152</v>
       </c>
       <c r="H47" t="n">
         <v>400</v>
@@ -1761,7 +1761,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G48" t="n">
-        <v>0.976349771022797</v>
+        <v>0.976349711418152</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G49" t="n">
-        <v>0.994237065315247</v>
+        <v>0.994237124919891</v>
       </c>
       <c r="H49" t="n">
         <v>2400</v>
@@ -1819,7 +1819,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G50" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H50" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>0.953990757465363</v>
+        <v>0.953990638256073</v>
       </c>
       <c r="H51" t="n">
         <v>8400</v>
@@ -1877,7 +1877,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G52" t="n">
-        <v>0.953990757465363</v>
+        <v>0.953990638256073</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H55" t="n">
         <v>800</v>
@@ -1993,7 +1993,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9681516289711</v>
+        <v>0.968151450157166</v>
       </c>
       <c r="H56" t="n">
         <v>1200</v>
@@ -2022,7 +2022,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9681516289711</v>
+        <v>0.968151450157166</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G58" t="n">
-        <v>0.950264096260071</v>
+        <v>0.950264155864716</v>
       </c>
       <c r="H58" t="n">
         <v>400</v>
@@ -2080,7 +2080,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>0.946537554264069</v>
+        <v>0.946537673473358</v>
       </c>
       <c r="H59" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G61" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H61" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H62" t="n">
         <v>2400</v>
@@ -2312,7 +2312,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H67" t="n">
         <v>6000</v>
@@ -2341,7 +2341,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H68" t="n">
         <v>4800</v>
@@ -2370,7 +2370,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G69" t="n">
-        <v>0.969641923904419</v>
+        <v>0.969642043113708</v>
       </c>
       <c r="H69" t="n">
         <v>6400</v>
@@ -2457,7 +2457,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H72" t="n">
         <v>6000</v>
@@ -2486,7 +2486,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G73" t="n">
-        <v>0.940575242042542</v>
+        <v>0.940575182437897</v>
       </c>
       <c r="H73" t="n">
         <v>2400</v>
@@ -2515,7 +2515,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H74" t="n">
         <v>8000</v>
@@ -2544,7 +2544,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>0.946537554264069</v>
+        <v>0.946537673473358</v>
       </c>
       <c r="H75" t="n">
         <v>17200</v>
@@ -2660,7 +2660,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G79" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H79" t="n">
         <v>27200</v>
@@ -2689,7 +2689,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G80" t="n">
-        <v>0.978585660457611</v>
+        <v>0.978585600852966</v>
       </c>
       <c r="H80" t="n">
         <v>15200</v>
@@ -2718,7 +2718,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G81" t="n">
-        <v>0.978585660457611</v>
+        <v>0.978585600852966</v>
       </c>
       <c r="H81" t="n">
         <v>22000</v>
@@ -2805,7 +2805,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G84" t="n">
-        <v>0.983802855014801</v>
+        <v>0.983802914619446</v>
       </c>
       <c r="H84" t="n">
         <v>51600</v>
@@ -2834,7 +2834,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G85" t="n">
-        <v>0.998709142208099</v>
+        <v>0.99870902299881</v>
       </c>
       <c r="H85" t="n">
         <v>12000</v>
@@ -2892,7 +2892,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G87" t="n">
-        <v>1.02852118015289</v>
+        <v>1.0285210609436</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G88" t="n">
-        <v>1.02852118015289</v>
+        <v>1.0285210609436</v>
       </c>
       <c r="H88" t="n">
         <v>20800</v>
@@ -2979,7 +2979,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>0.983325839042664</v>
+        <v>0.983325779438019</v>
       </c>
       <c r="H90" t="n">
         <v>14400</v>
@@ -3008,7 +3008,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G91" t="n">
-        <v>0.996013939380646</v>
+        <v>0.996014058589935</v>
       </c>
       <c r="H91" t="n">
         <v>8400</v>
@@ -3124,7 +3124,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G95" t="n">
-        <v>1.01028800010681</v>
+        <v>1.0102881193161</v>
       </c>
       <c r="H95" t="n">
         <v>10400</v>
@@ -3153,7 +3153,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G96" t="n">
-        <v>1.01821827888489</v>
+        <v>1.0182181596756</v>
       </c>
       <c r="H96" t="n">
         <v>1600</v>
@@ -3240,7 +3240,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>0.976981997489929</v>
+        <v>0.97698187828064</v>
       </c>
       <c r="H99" t="n">
         <v>11200</v>
@@ -3269,7 +3269,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G100" t="n">
-        <v>0.990462839603424</v>
+        <v>0.990462899208069</v>
       </c>
       <c r="H100" t="n">
         <v>13200</v>
@@ -3298,7 +3298,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G101" t="n">
-        <v>0.957156777381897</v>
+        <v>0.957156836986542</v>
       </c>
       <c r="H101" t="n">
         <v>43600</v>
@@ -3327,7 +3327,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G102" t="n">
-        <v>0.947640657424927</v>
+        <v>0.947640717029572</v>
       </c>
       <c r="H102" t="n">
         <v>25200</v>
@@ -3356,7 +3356,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G103" t="n">
-        <v>0.947640657424927</v>
+        <v>0.947640717029572</v>
       </c>
       <c r="H103" t="n">
         <v>400</v>
@@ -3385,7 +3385,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G104" t="n">
-        <v>0.947640657424927</v>
+        <v>0.947640717029572</v>
       </c>
       <c r="H104" t="n">
         <v>6400</v>
@@ -3675,7 +3675,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G114" t="n">
-        <v>0.903232455253601</v>
+        <v>0.903232514858246</v>
       </c>
       <c r="H114" t="n">
         <v>19200</v>
@@ -3791,7 +3791,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G118" t="n">
-        <v>0.884993374347687</v>
+        <v>0.884993314743042</v>
       </c>
       <c r="H118" t="n">
         <v>4800</v>
@@ -3936,7 +3936,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G123" t="n">
-        <v>0.841378033161163</v>
+        <v>0.841377973556519</v>
       </c>
       <c r="H123" t="n">
         <v>72000</v>
@@ -4110,7 +4110,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.734322428703308</v>
+        <v>0.734322369098663</v>
       </c>
       <c r="H129" t="n">
         <v>11600</v>
@@ -4197,7 +4197,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G132" t="n">
-        <v>0.729564368724823</v>
+        <v>0.729564309120178</v>
       </c>
       <c r="H132" t="n">
         <v>2000</v>
@@ -4255,7 +4255,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G134" t="n">
-        <v>0.80252069234848</v>
+        <v>0.802520751953125</v>
       </c>
       <c r="H134" t="n">
         <v>18000</v>
@@ -4284,7 +4284,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G135" t="n">
-        <v>0.780713200569153</v>
+        <v>0.780713140964508</v>
       </c>
       <c r="H135" t="n">
         <v>7600</v>
@@ -4342,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H137" t="n">
         <v>13200</v>
@@ -4371,7 +4371,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>0.823931992053986</v>
+        <v>0.823931932449341</v>
       </c>
       <c r="H138" t="n">
         <v>2400</v>
@@ -4400,7 +4400,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G139" t="n">
-        <v>0.823931992053986</v>
+        <v>0.823931932449341</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G141" t="n">
-        <v>0.831862032413483</v>
+        <v>0.831862092018127</v>
       </c>
       <c r="H141" t="n">
         <v>4800</v>
@@ -4487,7 +4487,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>0.832655012607574</v>
+        <v>0.83265495300293</v>
       </c>
       <c r="H142" t="n">
         <v>2000</v>
@@ -4951,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H158" t="n">
         <v>6000</v>
@@ -4980,7 +4980,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G159" t="n">
-        <v>0.805692791938782</v>
+        <v>0.805692851543427</v>
       </c>
       <c r="H159" t="n">
         <v>3600</v>
@@ -5009,7 +5009,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G160" t="n">
-        <v>0.77912712097168</v>
+        <v>0.779127180576324</v>
       </c>
       <c r="H160" t="n">
         <v>5200</v>
@@ -5038,7 +5038,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G161" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H161" t="n">
         <v>12400</v>
@@ -5067,7 +5067,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G162" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G163" t="n">
-        <v>0.747010469436646</v>
+        <v>0.747010409832001</v>
       </c>
       <c r="H163" t="n">
         <v>2000</v>
@@ -5125,7 +5125,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G164" t="n">
-        <v>0.747010469436646</v>
+        <v>0.747010409832001</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G165" t="n">
-        <v>0.761284470558167</v>
+        <v>0.761284530162811</v>
       </c>
       <c r="H165" t="n">
         <v>2800</v>
@@ -5212,7 +5212,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G167" t="n">
-        <v>0.77912712097168</v>
+        <v>0.779127180576324</v>
       </c>
       <c r="H167" t="n">
         <v>400</v>
@@ -5270,7 +5270,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G169" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H169" t="n">
         <v>2400</v>
@@ -5328,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H171" t="n">
         <v>3200</v>
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H172" t="n">
         <v>3600</v>
@@ -5386,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>0.785074710845947</v>
+        <v>0.785074651241302</v>
       </c>
       <c r="H175" t="n">
         <v>5200</v>
@@ -5473,7 +5473,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>0.785074710845947</v>
+        <v>0.785074651241302</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="G178" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H178" t="n">
         <v>32400</v>
@@ -5560,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H179" t="n">
         <v>23600</v>
@@ -5705,7 +5705,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G184" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H184" t="n">
         <v>31600</v>
@@ -5734,7 +5734,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G185" t="n">
-        <v>0.761284470558167</v>
+        <v>0.761284530162811</v>
       </c>
       <c r="H185" t="n">
         <v>4800</v>
@@ -5763,7 +5763,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G186" t="n">
-        <v>0.717669248580933</v>
+        <v>0.717669367790222</v>
       </c>
       <c r="H186" t="n">
         <v>10800</v>
@@ -5966,7 +5966,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G193" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H193" t="n">
         <v>27600</v>
@@ -6111,7 +6111,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G198" t="n">
-        <v>0.607441604137421</v>
+        <v>0.607441663742065</v>
       </c>
       <c r="H198" t="n">
         <v>14400</v>
@@ -6372,7 +6372,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G207" t="n">
-        <v>0.547173261642456</v>
+        <v>0.547173202037811</v>
       </c>
       <c r="H207" t="n">
         <v>53600</v>
@@ -6459,7 +6459,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G210" t="n">
-        <v>0.555103302001953</v>
+        <v>0.555103361606598</v>
       </c>
       <c r="H210" t="n">
         <v>25200</v>
@@ -6488,7 +6488,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G211" t="n">
-        <v>0.559068262577057</v>
+        <v>0.559068381786346</v>
       </c>
       <c r="H211" t="n">
         <v>28000</v>
@@ -6517,7 +6517,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G212" t="n">
-        <v>0.592374563217163</v>
+        <v>0.592374503612518</v>
       </c>
       <c r="H212" t="n">
         <v>158000</v>
@@ -6604,7 +6604,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G215" t="n">
-        <v>0.569377362728119</v>
+        <v>0.569377422332764</v>
       </c>
       <c r="H215" t="n">
         <v>22400</v>
@@ -6662,7 +6662,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G217" t="n">
-        <v>0.547173261642456</v>
+        <v>0.547173202037811</v>
       </c>
       <c r="H217" t="n">
         <v>24400</v>
@@ -6720,7 +6720,7 @@
         <v>0.715499997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>0.567394852638245</v>
+        <v>0.567394912242889</v>
       </c>
       <c r="H219" t="n">
         <v>18000</v>
@@ -6749,7 +6749,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G220" t="n">
-        <v>0.539243221282959</v>
+        <v>0.539243280887604</v>
       </c>
       <c r="H220" t="n">
         <v>26400</v>
@@ -6778,7 +6778,7 @@
         <v>0.672500014305115</v>
       </c>
       <c r="G221" t="n">
-        <v>0.533295750617981</v>
+        <v>0.533295691013336</v>
       </c>
       <c r="H221" t="n">
         <v>6800</v>
@@ -6836,7 +6836,7 @@
         <v>0.689499974250793</v>
       </c>
       <c r="G223" t="n">
-        <v>0.546776711940765</v>
+        <v>0.54677677154541</v>
       </c>
       <c r="H223" t="n">
         <v>800</v>
@@ -6865,7 +6865,7 @@
         <v>0.672500014305115</v>
       </c>
       <c r="G224" t="n">
-        <v>0.533295750617981</v>
+        <v>0.533295691013336</v>
       </c>
       <c r="H224" t="n">
         <v>12400</v>
@@ -6923,7 +6923,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G226" t="n">
-        <v>0.515453040599823</v>
+        <v>0.515453100204468</v>
       </c>
       <c r="H226" t="n">
         <v>62800</v>
@@ -6952,7 +6952,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G227" t="n">
-        <v>0.507523059844971</v>
+        <v>0.507523000240326</v>
       </c>
       <c r="H227" t="n">
         <v>52000</v>
@@ -7010,7 +7010,7 @@
         <v>0.625500023365021</v>
       </c>
       <c r="G229" t="n">
-        <v>0.496024519205093</v>
+        <v>0.496024489402771</v>
       </c>
       <c r="H229" t="n">
         <v>18000</v>
@@ -7068,7 +7068,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G231" t="n">
-        <v>0.551138341426849</v>
+        <v>0.55113822221756</v>
       </c>
       <c r="H231" t="n">
         <v>14800</v>
@@ -7097,7 +7097,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G232" t="n">
-        <v>0.559068262577057</v>
+        <v>0.559068381786346</v>
       </c>
       <c r="H232" t="n">
         <v>400</v>
@@ -7126,7 +7126,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G233" t="n">
-        <v>0.539243221282959</v>
+        <v>0.539243280887604</v>
       </c>
       <c r="H233" t="n">
         <v>20800</v>
@@ -7155,7 +7155,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G234" t="n">
-        <v>0.531313240528107</v>
+        <v>0.531313180923462</v>
       </c>
       <c r="H234" t="n">
         <v>4800</v>
@@ -7184,7 +7184,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G235" t="n">
-        <v>0.531313240528107</v>
+        <v>0.531313180923462</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>0.727500021457672</v>
       </c>
       <c r="G236" t="n">
-        <v>0.576910972595215</v>
+        <v>0.57691103219986</v>
       </c>
       <c r="H236" t="n">
         <v>186000</v>
@@ -7242,7 +7242,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G237" t="n">
-        <v>0.551138341426849</v>
+        <v>0.55113822221756</v>
       </c>
       <c r="H237" t="n">
         <v>2800</v>
@@ -7271,7 +7271,7 @@
         <v>0.665000021457672</v>
       </c>
       <c r="G238" t="n">
-        <v>0.527348220348358</v>
+        <v>0.527348160743713</v>
       </c>
       <c r="H238" t="n">
         <v>9200</v>
@@ -7300,7 +7300,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>0.521797060966492</v>
+        <v>0.521797180175781</v>
       </c>
       <c r="H239" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G241" t="n">
-        <v>0.539243221282959</v>
+        <v>0.539243280887604</v>
       </c>
       <c r="H241" t="n">
         <v>13200</v>
@@ -7387,7 +7387,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G242" t="n">
-        <v>0.539243221282959</v>
+        <v>0.539243280887604</v>
       </c>
       <c r="H242" t="n">
         <v>8000</v>
@@ -7532,7 +7532,7 @@
         <v>0.71450001001358</v>
       </c>
       <c r="G247" t="n">
-        <v>0.566601872444153</v>
+        <v>0.566601932048798</v>
       </c>
       <c r="H247" t="n">
         <v>102400</v>
@@ -7648,7 +7648,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G251" t="n">
-        <v>0.566205322742462</v>
+        <v>0.566205382347107</v>
       </c>
       <c r="H251" t="n">
         <v>59600</v>
@@ -7706,7 +7706,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G253" t="n">
-        <v>0.615371704101562</v>
+        <v>0.615371644496918</v>
       </c>
       <c r="H253" t="n">
         <v>42000</v>
@@ -7764,7 +7764,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G255" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H255" t="n">
         <v>39600</v>
@@ -7793,7 +7793,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G256" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H256" t="n">
         <v>27200</v>
@@ -7851,7 +7851,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G258" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H258" t="n">
         <v>111600</v>
@@ -7909,7 +7909,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>0.785074710845947</v>
+        <v>0.785074651241302</v>
       </c>
       <c r="H260" t="n">
         <v>67200</v>
@@ -7938,7 +7938,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H261" t="n">
         <v>81600</v>
@@ -7967,7 +7967,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H262" t="n">
         <v>25200</v>
@@ -8141,7 +8141,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G268" t="n">
-        <v>0.778334140777588</v>
+        <v>0.778334200382233</v>
       </c>
       <c r="H268" t="n">
         <v>4400</v>
@@ -8170,7 +8170,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G269" t="n">
-        <v>0.78626424074173</v>
+        <v>0.786264181137085</v>
       </c>
       <c r="H269" t="n">
         <v>13600</v>
@@ -8199,7 +8199,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G270" t="n">
-        <v>0.780713200569153</v>
+        <v>0.780713140964508</v>
       </c>
       <c r="H270" t="n">
         <v>8400</v>
@@ -8257,7 +8257,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>0.785074710845947</v>
+        <v>0.785074651241302</v>
       </c>
       <c r="H272" t="n">
         <v>34400</v>
@@ -8286,7 +8286,7 @@
         <v>0.992500007152557</v>
       </c>
       <c r="G273" t="n">
-        <v>0.787057280540466</v>
+        <v>0.787057220935822</v>
       </c>
       <c r="H273" t="n">
         <v>6400</v>
@@ -8315,7 +8315,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G274" t="n">
-        <v>0.785074710845947</v>
+        <v>0.785074651241302</v>
       </c>
       <c r="H274" t="n">
         <v>2400</v>
@@ -8373,7 +8373,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G276" t="n">
-        <v>0.765249609947205</v>
+        <v>0.76524955034256</v>
       </c>
       <c r="H276" t="n">
         <v>8400</v>
@@ -8431,7 +8431,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G278" t="n">
-        <v>0.761284470558167</v>
+        <v>0.761284530162811</v>
       </c>
       <c r="H278" t="n">
         <v>13200</v>
@@ -8460,7 +8460,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G279" t="n">
-        <v>0.788246810436249</v>
+        <v>0.788246691226959</v>
       </c>
       <c r="H279" t="n">
         <v>8800</v>
@@ -8489,7 +8489,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G280" t="n">
-        <v>0.788246810436249</v>
+        <v>0.788246691226959</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>0.785074710845947</v>
+        <v>0.785074651241302</v>
       </c>
       <c r="H281" t="n">
         <v>35600</v>
@@ -8576,7 +8576,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G283" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H283" t="n">
         <v>3200</v>
@@ -8605,7 +8605,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G284" t="n">
-        <v>0.754147469997406</v>
+        <v>0.754147529602051</v>
       </c>
       <c r="H284" t="n">
         <v>17600</v>
@@ -8750,7 +8750,7 @@
         <v>0.800499975681305</v>
       </c>
       <c r="G289" t="n">
-        <v>0.634800314903259</v>
+        <v>0.634800255298615</v>
       </c>
       <c r="H289" t="n">
         <v>12800</v>
@@ -8779,7 +8779,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G290" t="n">
-        <v>0.642333924770355</v>
+        <v>0.64233386516571</v>
       </c>
       <c r="H290" t="n">
         <v>23200</v>
@@ -8808,7 +8808,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G291" t="n">
-        <v>0.653435885906219</v>
+        <v>0.653436005115509</v>
       </c>
       <c r="H291" t="n">
         <v>9200</v>
@@ -8837,7 +8837,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G292" t="n">
-        <v>0.662158906459808</v>
+        <v>0.662158966064453</v>
       </c>
       <c r="H292" t="n">
         <v>8000</v>
@@ -8924,7 +8924,7 @@
         <v>0.782999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>0.620922684669495</v>
+        <v>0.620922744274139</v>
       </c>
       <c r="H295" t="n">
         <v>40800</v>
@@ -9040,7 +9040,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G299" t="n">
-        <v>0.674054026603699</v>
+        <v>0.674054086208344</v>
       </c>
       <c r="H299" t="n">
         <v>47200</v>
@@ -9098,7 +9098,7 @@
         <v>0.856500029563904</v>
       </c>
       <c r="G301" t="n">
-        <v>0.679208636283875</v>
+        <v>0.67920857667923</v>
       </c>
       <c r="H301" t="n">
         <v>12800</v>
@@ -9127,7 +9127,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G302" t="n">
-        <v>0.67246800661087</v>
+        <v>0.672468066215515</v>
       </c>
       <c r="H302" t="n">
         <v>10000</v>
@@ -9156,7 +9156,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G303" t="n">
-        <v>0.674054026603699</v>
+        <v>0.674054086208344</v>
       </c>
       <c r="H303" t="n">
         <v>6000</v>
@@ -9185,7 +9185,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G304" t="n">
-        <v>0.696258187294006</v>
+        <v>0.696258246898651</v>
       </c>
       <c r="H304" t="n">
         <v>16800</v>
@@ -9214,7 +9214,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>0.678019106388092</v>
+        <v>0.678019046783447</v>
       </c>
       <c r="H305" t="n">
         <v>33600</v>
@@ -9359,7 +9359,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G310" t="n">
-        <v>0.674054026603699</v>
+        <v>0.674054086208344</v>
       </c>
       <c r="H310" t="n">
         <v>10400</v>
@@ -9388,7 +9388,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G311" t="n">
-        <v>0.662158906459808</v>
+        <v>0.662158966064453</v>
       </c>
       <c r="H311" t="n">
         <v>50000</v>
@@ -9446,7 +9446,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G313" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H313" t="n">
         <v>40800</v>
@@ -9475,7 +9475,7 @@
         <v>0.826499998569489</v>
       </c>
       <c r="G314" t="n">
-        <v>0.655418455600739</v>
+        <v>0.655418395996094</v>
       </c>
       <c r="H314" t="n">
         <v>190000</v>
@@ -9504,7 +9504,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G315" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H315" t="n">
         <v>88400</v>
@@ -9533,7 +9533,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G316" t="n">
-        <v>0.654228925704956</v>
+        <v>0.654228866100311</v>
       </c>
       <c r="H316" t="n">
         <v>20400</v>
@@ -9591,7 +9591,7 @@
         <v>0.862500011920929</v>
       </c>
       <c r="G318" t="n">
-        <v>0.683966636657715</v>
+        <v>0.68396657705307</v>
       </c>
       <c r="H318" t="n">
         <v>142000</v>
@@ -9620,7 +9620,7 @@
         <v>0.880999982357025</v>
       </c>
       <c r="G319" t="n">
-        <v>0.698637127876282</v>
+        <v>0.698637187480927</v>
       </c>
       <c r="H319" t="n">
         <v>65200</v>
@@ -9794,7 +9794,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G325" t="n">
-        <v>0.722427368164062</v>
+        <v>0.722427308559418</v>
       </c>
       <c r="H325" t="n">
         <v>19600</v>
@@ -9823,7 +9823,7 @@
         <v>0.952499985694885</v>
       </c>
       <c r="G326" t="n">
-        <v>0.755336940288544</v>
+        <v>0.755337059497833</v>
       </c>
       <c r="H326" t="n">
         <v>210000</v>
@@ -9939,7 +9939,7 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0.793004751205444</v>
+        <v>0.793004810810089</v>
       </c>
       <c r="H330" t="n">
         <v>268000</v>
@@ -10084,7 +10084,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G335" t="n">
-        <v>0.850100994110107</v>
+        <v>0.850101053714752</v>
       </c>
       <c r="H335" t="n">
         <v>56000</v>
@@ -10113,7 +10113,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G336" t="n">
-        <v>0.854859054088593</v>
+        <v>0.854858994483948</v>
       </c>
       <c r="H336" t="n">
         <v>76400</v>
@@ -10171,7 +10171,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G338" t="n">
-        <v>0.855652093887329</v>
+        <v>0.855652153491974</v>
       </c>
       <c r="H338" t="n">
         <v>66000</v>
@@ -10229,7 +10229,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G340" t="n">
-        <v>0.843757092952728</v>
+        <v>0.843757033348083</v>
       </c>
       <c r="H340" t="n">
         <v>73600</v>
@@ -10258,7 +10258,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>0.855356514453888</v>
+        <v>0.855356454849243</v>
       </c>
       <c r="H341" t="n">
         <v>45200</v>
@@ -10461,7 +10461,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G348" t="n">
-        <v>0.809459328651428</v>
+        <v>0.809459388256073</v>
       </c>
       <c r="H348" t="n">
         <v>34000</v>
@@ -10548,7 +10548,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G351" t="n">
-        <v>0.805286824703217</v>
+        <v>0.805286884307861</v>
       </c>
       <c r="H351" t="n">
         <v>7200</v>
@@ -10722,7 +10722,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G357" t="n">
-        <v>1.14075362682343</v>
+        <v>1.14075350761414</v>
       </c>
       <c r="H357" t="n">
         <v>584400</v>
@@ -10751,7 +10751,7 @@
         <v>1.38699996471405</v>
       </c>
       <c r="G358" t="n">
-        <v>1.15744340419769</v>
+        <v>1.1574432849884</v>
       </c>
       <c r="H358" t="n">
         <v>1138800</v>
@@ -10983,7 +10983,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>0.988875567913055</v>
+        <v>0.988875508308411</v>
       </c>
       <c r="H366" t="n">
         <v>155200</v>
@@ -11128,7 +11128,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G371" t="n">
-        <v>1.1006977558136</v>
+        <v>1.10069787502289</v>
       </c>
       <c r="H371" t="n">
         <v>264800</v>
@@ -11244,7 +11244,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G375" t="n">
-        <v>1.03894519805908</v>
+        <v>1.03894531726837</v>
       </c>
       <c r="H375" t="n">
         <v>6400</v>
@@ -11302,7 +11302,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G377" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H377" t="n">
         <v>12000</v>
@@ -11331,7 +11331,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G378" t="n">
-        <v>0.990544676780701</v>
+        <v>0.990544557571411</v>
       </c>
       <c r="H378" t="n">
         <v>12800</v>
@@ -11360,7 +11360,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>0.982199609279633</v>
+        <v>0.982199549674988</v>
       </c>
       <c r="H379" t="n">
         <v>12400</v>
@@ -11389,7 +11389,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G380" t="n">
-        <v>0.991379022598267</v>
+        <v>0.991379082202911</v>
       </c>
       <c r="H380" t="n">
         <v>3600</v>
@@ -11418,7 +11418,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G381" t="n">
-        <v>0.974689185619354</v>
+        <v>0.974689126014709</v>
       </c>
       <c r="H381" t="n">
         <v>11200</v>
@@ -11447,7 +11447,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G382" t="n">
-        <v>0.97635805606842</v>
+        <v>0.976357996463776</v>
       </c>
       <c r="H382" t="n">
         <v>22800</v>
@@ -11476,7 +11476,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G383" t="n">
-        <v>0.979696035385132</v>
+        <v>0.979696094989777</v>
       </c>
       <c r="H383" t="n">
         <v>25200</v>
@@ -11563,7 +11563,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>0.954661309719086</v>
+        <v>0.95466136932373</v>
       </c>
       <c r="H386" t="n">
         <v>22000</v>
@@ -11592,7 +11592,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G387" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H387" t="n">
         <v>65200</v>
@@ -11650,7 +11650,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G389" t="n">
-        <v>0.978027164936066</v>
+        <v>0.97802722454071</v>
       </c>
       <c r="H389" t="n">
         <v>7200</v>
@@ -11708,7 +11708,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G391" t="n">
-        <v>0.971351087093353</v>
+        <v>0.971351146697998</v>
       </c>
       <c r="H391" t="n">
         <v>7600</v>
@@ -11737,7 +11737,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G392" t="n">
-        <v>0.971351087093353</v>
+        <v>0.971351146697998</v>
       </c>
       <c r="H392" t="n">
         <v>2400</v>
@@ -11766,7 +11766,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G393" t="n">
-        <v>0.973020195960999</v>
+        <v>0.973020136356354</v>
       </c>
       <c r="H393" t="n">
         <v>97600</v>
@@ -11969,7 +11969,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>0.963840782642365</v>
+        <v>0.96384072303772</v>
       </c>
       <c r="H400" t="n">
         <v>50000</v>
@@ -12114,7 +12114,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G405" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H405" t="n">
         <v>6000</v>
@@ -12143,7 +12143,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G406" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H406" t="n">
         <v>36800</v>
@@ -12172,7 +12172,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.0723249912262</v>
+        <v>1.07232487201691</v>
       </c>
       <c r="H407" t="n">
         <v>139600</v>
@@ -12201,7 +12201,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>1.05396616458893</v>
+        <v>1.05396628379822</v>
       </c>
       <c r="H408" t="n">
         <v>126800</v>
@@ -12230,7 +12230,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G409" t="n">
-        <v>1.03894519805908</v>
+        <v>1.03894531726837</v>
       </c>
       <c r="H409" t="n">
         <v>22400</v>
@@ -12317,7 +12317,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H412" t="n">
         <v>53200</v>
@@ -12375,7 +12375,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G414" t="n">
-        <v>0.974689185619354</v>
+        <v>0.974689126014709</v>
       </c>
       <c r="H414" t="n">
         <v>14000</v>
@@ -12404,7 +12404,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G415" t="n">
-        <v>0.971351087093353</v>
+        <v>0.971351146697998</v>
       </c>
       <c r="H415" t="n">
         <v>30800</v>
@@ -12433,7 +12433,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G416" t="n">
-        <v>1.01140689849854</v>
+        <v>1.01140701770782</v>
       </c>
       <c r="H416" t="n">
         <v>13600</v>
@@ -12462,7 +12462,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G417" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H417" t="n">
         <v>60000</v>
@@ -12520,7 +12520,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G419" t="n">
-        <v>0.982199609279633</v>
+        <v>0.982199549674988</v>
       </c>
       <c r="H419" t="n">
         <v>50000</v>
@@ -12549,7 +12549,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G420" t="n">
-        <v>0.982199609279633</v>
+        <v>0.982199549674988</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G422" t="n">
-        <v>0.97635805606842</v>
+        <v>0.976357996463776</v>
       </c>
       <c r="H422" t="n">
         <v>11200</v>
@@ -12636,7 +12636,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G423" t="n">
-        <v>0.994717001914978</v>
+        <v>0.994717061519623</v>
       </c>
       <c r="H423" t="n">
         <v>400</v>
@@ -12665,7 +12665,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G424" t="n">
-        <v>0.979696035385132</v>
+        <v>0.979696094989777</v>
       </c>
       <c r="H424" t="n">
         <v>9200</v>
@@ -12694,7 +12694,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G425" t="n">
-        <v>0.979696035385132</v>
+        <v>0.979696094989777</v>
       </c>
       <c r="H425" t="n">
         <v>400</v>
@@ -12723,7 +12723,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G426" t="n">
-        <v>0.98720645904541</v>
+        <v>0.987206518650055</v>
       </c>
       <c r="H426" t="n">
         <v>800</v>
@@ -12752,7 +12752,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G427" t="n">
-        <v>0.978027164936066</v>
+        <v>0.97802722454071</v>
       </c>
       <c r="H427" t="n">
         <v>31600</v>
@@ -12810,7 +12810,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G429" t="n">
-        <v>0.988041043281555</v>
+        <v>0.9880411028862</v>
       </c>
       <c r="H429" t="n">
         <v>5200</v>
@@ -12868,7 +12868,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G431" t="n">
-        <v>0.981365144252777</v>
+        <v>0.981365084648132</v>
       </c>
       <c r="H431" t="n">
         <v>3600</v>
@@ -12897,7 +12897,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G432" t="n">
-        <v>0.963840782642365</v>
+        <v>0.96384072303772</v>
       </c>
       <c r="H432" t="n">
         <v>3200</v>
@@ -12926,7 +12926,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G433" t="n">
-        <v>0.962171792984009</v>
+        <v>0.962171852588654</v>
       </c>
       <c r="H433" t="n">
         <v>32800</v>
@@ -12955,7 +12955,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G434" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H434" t="n">
         <v>10000</v>
@@ -12984,7 +12984,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G435" t="n">
-        <v>0.98720645904541</v>
+        <v>0.987206518650055</v>
       </c>
       <c r="H435" t="n">
         <v>21600</v>
@@ -13013,7 +13013,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>0.963840782642365</v>
+        <v>0.96384072303772</v>
       </c>
       <c r="H436" t="n">
         <v>32400</v>
@@ -13042,7 +13042,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G437" t="n">
-        <v>0.963840782642365</v>
+        <v>0.96384072303772</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G438" t="n">
-        <v>0.917943596839905</v>
+        <v>0.91794365644455</v>
       </c>
       <c r="H438" t="n">
         <v>164800</v>
@@ -13129,7 +13129,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G440" t="n">
-        <v>0.917943596839905</v>
+        <v>0.91794365644455</v>
       </c>
       <c r="H440" t="n">
         <v>138000</v>
@@ -13274,7 +13274,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G445" t="n">
-        <v>0.935467958450317</v>
+        <v>0.935468018054962</v>
       </c>
       <c r="H445" t="n">
         <v>21600</v>
@@ -13361,7 +13361,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G448" t="n">
-        <v>0.947985410690308</v>
+        <v>0.947985291481018</v>
       </c>
       <c r="H448" t="n">
         <v>54000</v>
@@ -13390,7 +13390,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>0.949654400348663</v>
+        <v>0.949654340744019</v>
       </c>
       <c r="H449" t="n">
         <v>18400</v>
@@ -13419,7 +13419,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G450" t="n">
-        <v>0.954661309719086</v>
+        <v>0.95466136932373</v>
       </c>
       <c r="H450" t="n">
         <v>4800</v>
@@ -13448,7 +13448,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G451" t="n">
-        <v>0.941309452056885</v>
+        <v>0.94130939245224</v>
       </c>
       <c r="H451" t="n">
         <v>49600</v>
@@ -13477,7 +13477,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G452" t="n">
-        <v>0.949654400348663</v>
+        <v>0.949654340744019</v>
       </c>
       <c r="H452" t="n">
         <v>32800</v>
@@ -13506,7 +13506,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G453" t="n">
-        <v>0.96550977230072</v>
+        <v>0.965509712696075</v>
       </c>
       <c r="H453" t="n">
         <v>68000</v>
@@ -13535,7 +13535,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G454" t="n">
-        <v>0.983034133911133</v>
+        <v>0.983034074306488</v>
       </c>
       <c r="H454" t="n">
         <v>96800</v>
@@ -13593,7 +13593,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G456" t="n">
-        <v>0.994717001914978</v>
+        <v>0.994717061519623</v>
       </c>
       <c r="H456" t="n">
         <v>119200</v>
@@ -13709,7 +13709,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G460" t="n">
-        <v>1.05730414390564</v>
+        <v>1.05730402469635</v>
       </c>
       <c r="H460" t="n">
         <v>49200</v>
@@ -13767,7 +13767,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G462" t="n">
-        <v>1.13491201400757</v>
+        <v>1.13491213321686</v>
       </c>
       <c r="H462" t="n">
         <v>400800</v>
@@ -13825,7 +13825,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G464" t="n">
-        <v>1.45619225502014</v>
+        <v>1.45619237422943</v>
       </c>
       <c r="H464" t="n">
         <v>674400</v>
@@ -13941,7 +13941,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G468" t="n">
-        <v>1.27677607536316</v>
+        <v>1.27677595615387</v>
       </c>
       <c r="H468" t="n">
         <v>47600</v>
@@ -14057,7 +14057,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G472" t="n">
-        <v>1.3310182094574</v>
+        <v>1.33101809024811</v>
       </c>
       <c r="H472" t="n">
         <v>70000</v>
@@ -14086,7 +14086,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G473" t="n">
-        <v>1.31599736213684</v>
+        <v>1.31599724292755</v>
       </c>
       <c r="H473" t="n">
         <v>56400</v>
@@ -14434,7 +14434,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>1.16411936283112</v>
+        <v>1.16411924362183</v>
       </c>
       <c r="H485" t="n">
         <v>13600</v>
@@ -14695,7 +14695,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G494" t="n">
-        <v>1.24339628219604</v>
+        <v>1.24339640140533</v>
       </c>
       <c r="H494" t="n">
         <v>29600</v>
@@ -14753,7 +14753,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G496" t="n">
-        <v>1.16328477859497</v>
+        <v>1.16328489780426</v>
       </c>
       <c r="H496" t="n">
         <v>68800</v>
@@ -14811,7 +14811,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G498" t="n">
-        <v>1.16996073722839</v>
+        <v>1.16996085643768</v>
       </c>
       <c r="H498" t="n">
         <v>8800</v>
@@ -14927,7 +14927,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>1.16411936283112</v>
+        <v>1.16411924362183</v>
       </c>
       <c r="H502" t="n">
         <v>4800</v>
@@ -15043,7 +15043,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G506" t="n">
-        <v>1.09652531147003</v>
+        <v>1.09652543067932</v>
       </c>
       <c r="H506" t="n">
         <v>207600</v>
@@ -15101,7 +15101,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G508" t="n">
-        <v>1.09986329078674</v>
+        <v>1.09986317157745</v>
       </c>
       <c r="H508" t="n">
         <v>24400</v>
@@ -15217,7 +15217,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G512" t="n">
-        <v>1.12656712532043</v>
+        <v>1.12656700611115</v>
       </c>
       <c r="H512" t="n">
         <v>10400</v>
@@ -15275,7 +15275,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G514" t="n">
-        <v>1.10570478439331</v>
+        <v>1.10570466518402</v>
       </c>
       <c r="H514" t="n">
         <v>15200</v>
@@ -15362,7 +15362,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G517" t="n">
-        <v>1.12656712532043</v>
+        <v>1.12656700611115</v>
       </c>
       <c r="H517" t="n">
         <v>12400</v>
@@ -15449,7 +15449,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G520" t="n">
-        <v>1.12656712532043</v>
+        <v>1.12656700611115</v>
       </c>
       <c r="H520" t="n">
         <v>14000</v>
@@ -15478,7 +15478,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.12656712532043</v>
+        <v>1.12656700611115</v>
       </c>
       <c r="H521" t="n">
         <v>12400</v>
@@ -15507,7 +15507,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G522" t="n">
-        <v>1.12656712532043</v>
+        <v>1.12656700611115</v>
       </c>
       <c r="H522" t="n">
         <v>8800</v>
@@ -15565,7 +15565,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G524" t="n">
-        <v>1.13491201400757</v>
+        <v>1.13491213321686</v>
       </c>
       <c r="H524" t="n">
         <v>34800</v>
@@ -15623,7 +15623,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G526" t="n">
-        <v>1.12656712532043</v>
+        <v>1.12656700611115</v>
       </c>
       <c r="H526" t="n">
         <v>42000</v>
@@ -15826,7 +15826,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>1.09735977649689</v>
+        <v>1.09735989570618</v>
       </c>
       <c r="H533" t="n">
         <v>12400</v>
@@ -15855,7 +15855,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.07649743556976</v>
+        <v>1.07649731636047</v>
       </c>
       <c r="H534" t="n">
         <v>32000</v>
@@ -15884,7 +15884,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>1.07649743556976</v>
+        <v>1.07649731636047</v>
       </c>
       <c r="H535" t="n">
         <v>4000</v>
@@ -16116,7 +16116,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G543" t="n">
-        <v>0.947150886058807</v>
+        <v>0.947150826454163</v>
       </c>
       <c r="H543" t="n">
         <v>27200</v>
@@ -16174,7 +16174,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G545" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H545" t="n">
         <v>107200</v>
@@ -16232,7 +16232,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G547" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H547" t="n">
         <v>5600</v>
@@ -16261,7 +16261,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G548" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H548" t="n">
         <v>3200</v>
@@ -16348,7 +16348,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G551" t="n">
-        <v>0.947150886058807</v>
+        <v>0.947150826454163</v>
       </c>
       <c r="H551" t="n">
         <v>61600</v>
@@ -16377,7 +16377,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G552" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H552" t="n">
         <v>15600</v>
@@ -16638,7 +16638,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>0.93046098947525</v>
+        <v>0.930460929870605</v>
       </c>
       <c r="H561" t="n">
         <v>6000</v>
@@ -16725,7 +16725,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G564" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H564" t="n">
         <v>2400</v>
@@ -16812,7 +16812,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>0.955495834350586</v>
+        <v>0.955495774745941</v>
       </c>
       <c r="H567" t="n">
         <v>5200</v>
@@ -16928,7 +16928,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G571" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H571" t="n">
         <v>4000</v>
@@ -17015,7 +17015,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.06397998332977</v>
+        <v>1.06397986412048</v>
       </c>
       <c r="H574" t="n">
         <v>18800</v>
@@ -17073,7 +17073,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G576" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H576" t="n">
         <v>56800</v>
@@ -17102,7 +17102,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G577" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H577" t="n">
         <v>11600</v>
@@ -17131,7 +17131,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>0.980530619621277</v>
+        <v>0.980530560016632</v>
       </c>
       <c r="H579" t="n">
         <v>3200</v>
@@ -17189,7 +17189,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H580" t="n">
         <v>4000</v>
@@ -17218,7 +17218,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G581" t="n">
-        <v>0.993048131465912</v>
+        <v>0.993048191070557</v>
       </c>
       <c r="H581" t="n">
         <v>1600</v>
@@ -17305,7 +17305,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G584" t="n">
-        <v>1.13491201400757</v>
+        <v>1.13491213321686</v>
       </c>
       <c r="H584" t="n">
         <v>77200</v>
@@ -80096,6 +80096,64 @@
         <v>0</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>1.52042257785797</v>
+        <v>1.52042269706726</v>
       </c>
       <c r="H3" t="n">
         <v>2400</v>
@@ -485,7 +485,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G4" t="n">
-        <v>1.54427254199982</v>
+        <v>1.54427230358124</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -514,7 +514,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G5" t="n">
-        <v>1.43918442726135</v>
+        <v>1.43918430805206</v>
       </c>
       <c r="H5" t="n">
         <v>10800</v>
@@ -572,7 +572,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G7" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H7" t="n">
         <v>3600</v>
@@ -601,7 +601,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G11" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H11" t="n">
         <v>2400</v>
@@ -717,7 +717,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G13" t="n">
-        <v>1.39968323707581</v>
+        <v>1.39968311786652</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>1.28937792778015</v>
+        <v>1.28937804698944</v>
       </c>
       <c r="H17" t="n">
         <v>4000</v>
@@ -891,7 +891,7 @@
         <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30428397655487</v>
+        <v>1.30428409576416</v>
       </c>
       <c r="H18" t="n">
         <v>8800</v>
@@ -920,7 +920,7 @@
         <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.30428397655487</v>
+        <v>1.30428409576416</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G23" t="n">
-        <v>1.22379112243652</v>
+        <v>1.22379100322723</v>
       </c>
       <c r="H23" t="n">
         <v>5600</v>
@@ -1065,7 +1065,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G24" t="n">
-        <v>1.22379112243652</v>
+        <v>1.22379100322723</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G26" t="n">
-        <v>1.17012917995453</v>
+        <v>1.17012929916382</v>
       </c>
       <c r="H26" t="n">
         <v>400</v>
@@ -1152,7 +1152,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.08069264888763</v>
+        <v>1.08069276809692</v>
       </c>
       <c r="H27" t="n">
         <v>3600</v>
@@ -1181,7 +1181,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G28" t="n">
-        <v>0.991255939006805</v>
+        <v>0.991255879402161</v>
       </c>
       <c r="H28" t="n">
         <v>4000</v>
@@ -1210,7 +1210,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G29" t="n">
-        <v>1.02703058719635</v>
+        <v>1.02703070640564</v>
       </c>
       <c r="H29" t="n">
         <v>3600</v>
@@ -1239,7 +1239,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>0.961443722248077</v>
+        <v>0.961443603038788</v>
       </c>
       <c r="H30" t="n">
         <v>2400</v>
@@ -1268,7 +1268,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G31" t="n">
-        <v>0.976349711418152</v>
+        <v>0.976349830627441</v>
       </c>
       <c r="H31" t="n">
         <v>4800</v>
@@ -1297,7 +1297,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G32" t="n">
-        <v>1.01883208751678</v>
+        <v>1.01883220672607</v>
       </c>
       <c r="H32" t="n">
         <v>6800</v>
@@ -1384,7 +1384,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G35" t="n">
-        <v>1.01510560512543</v>
+        <v>1.01510572433472</v>
       </c>
       <c r="H35" t="n">
         <v>4400</v>
@@ -1413,7 +1413,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G36" t="n">
-        <v>0.995727837085724</v>
+        <v>0.995727717876434</v>
       </c>
       <c r="H36" t="n">
         <v>2000</v>
@@ -1442,7 +1442,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G37" t="n">
-        <v>1.01212441921234</v>
+        <v>1.01212453842163</v>
       </c>
       <c r="H37" t="n">
         <v>3200</v>
@@ -1674,7 +1674,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>0.976349711418152</v>
+        <v>0.976349830627441</v>
       </c>
       <c r="H45" t="n">
         <v>3600</v>
@@ -1732,7 +1732,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G47" t="n">
-        <v>0.976349711418152</v>
+        <v>0.976349830627441</v>
       </c>
       <c r="H47" t="n">
         <v>400</v>
@@ -1761,7 +1761,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G48" t="n">
-        <v>0.976349711418152</v>
+        <v>0.976349830627441</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G49" t="n">
-        <v>0.994237124919891</v>
+        <v>0.994237065315247</v>
       </c>
       <c r="H49" t="n">
         <v>2400</v>
@@ -1819,7 +1819,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G50" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H50" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>0.953990638256073</v>
+        <v>0.953990519046783</v>
       </c>
       <c r="H51" t="n">
         <v>8400</v>
@@ -1877,7 +1877,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G52" t="n">
-        <v>0.953990638256073</v>
+        <v>0.953990519046783</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>0.961443722248077</v>
+        <v>0.961443603038788</v>
       </c>
       <c r="H53" t="n">
         <v>18800</v>
@@ -1935,7 +1935,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G54" t="n">
-        <v>0.967406153678894</v>
+        <v>0.967406213283539</v>
       </c>
       <c r="H54" t="n">
         <v>7200</v>
@@ -1964,7 +1964,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H55" t="n">
         <v>800</v>
@@ -1993,7 +1993,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G56" t="n">
-        <v>0.968151450157166</v>
+        <v>0.968151390552521</v>
       </c>
       <c r="H56" t="n">
         <v>1200</v>
@@ -2022,7 +2022,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G57" t="n">
-        <v>0.968151450157166</v>
+        <v>0.968151390552521</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>0.946537673473358</v>
+        <v>0.946537613868713</v>
       </c>
       <c r="H59" t="n">
         <v>400</v>
@@ -2109,7 +2109,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>0.961443722248077</v>
+        <v>0.961443603038788</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G61" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H61" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H62" t="n">
         <v>2400</v>
@@ -2225,7 +2225,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G64" t="n">
-        <v>1.02703058719635</v>
+        <v>1.02703070640564</v>
       </c>
       <c r="H64" t="n">
         <v>9600</v>
@@ -2254,7 +2254,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G65" t="n">
-        <v>0.991255939006805</v>
+        <v>0.991255879402161</v>
       </c>
       <c r="H65" t="n">
         <v>7200</v>
@@ -2283,7 +2283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.991255939006805</v>
+        <v>0.991255879402161</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H67" t="n">
         <v>6000</v>
@@ -2341,7 +2341,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H68" t="n">
         <v>4800</v>
@@ -2370,7 +2370,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G69" t="n">
-        <v>0.969642043113708</v>
+        <v>0.969642162322998</v>
       </c>
       <c r="H69" t="n">
         <v>6400</v>
@@ -2428,7 +2428,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>0.961443722248077</v>
+        <v>0.961443603038788</v>
       </c>
       <c r="H71" t="n">
         <v>24800</v>
@@ -2457,7 +2457,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H72" t="n">
         <v>6000</v>
@@ -2515,7 +2515,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H74" t="n">
         <v>8000</v>
@@ -2544,7 +2544,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>0.946537673473358</v>
+        <v>0.946537613868713</v>
       </c>
       <c r="H75" t="n">
         <v>17200</v>
@@ -2573,7 +2573,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G76" t="n">
-        <v>0.93237692117691</v>
+        <v>0.932376980781555</v>
       </c>
       <c r="H76" t="n">
         <v>13200</v>
@@ -2631,7 +2631,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G78" t="n">
-        <v>0.949518918991089</v>
+        <v>0.949519038200378</v>
       </c>
       <c r="H78" t="n">
         <v>34400</v>
@@ -2660,7 +2660,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G79" t="n">
-        <v>0.968896746635437</v>
+        <v>0.968896687030792</v>
       </c>
       <c r="H79" t="n">
         <v>27200</v>
@@ -2689,7 +2689,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G80" t="n">
-        <v>0.978585600852966</v>
+        <v>0.978585720062256</v>
       </c>
       <c r="H80" t="n">
         <v>15200</v>
@@ -2718,7 +2718,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G81" t="n">
-        <v>0.978585600852966</v>
+        <v>0.978585720062256</v>
       </c>
       <c r="H81" t="n">
         <v>22000</v>
@@ -2747,7 +2747,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G82" t="n">
-        <v>0.943556487560272</v>
+        <v>0.943556427955627</v>
       </c>
       <c r="H82" t="n">
         <v>7200</v>
@@ -2776,7 +2776,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>0.912998974323273</v>
+        <v>0.912998914718628</v>
       </c>
       <c r="H83" t="n">
         <v>15600</v>
@@ -2834,7 +2834,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G85" t="n">
-        <v>0.99870902299881</v>
+        <v>0.998708963394165</v>
       </c>
       <c r="H85" t="n">
         <v>12000</v>
@@ -2863,7 +2863,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G86" t="n">
-        <v>0.985293447971344</v>
+        <v>0.985293507575989</v>
       </c>
       <c r="H86" t="n">
         <v>58000</v>
@@ -2892,7 +2892,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G87" t="n">
-        <v>1.0285210609436</v>
+        <v>1.02852118015289</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G88" t="n">
-        <v>1.0285210609436</v>
+        <v>1.02852118015289</v>
       </c>
       <c r="H88" t="n">
         <v>20800</v>
@@ -2950,7 +2950,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G89" t="n">
-        <v>0.991255939006805</v>
+        <v>0.991255879402161</v>
       </c>
       <c r="H89" t="n">
         <v>30000</v>
@@ -2979,7 +2979,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G90" t="n">
-        <v>0.983325779438019</v>
+        <v>0.983325898647308</v>
       </c>
       <c r="H90" t="n">
         <v>14400</v>
@@ -3008,7 +3008,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G91" t="n">
-        <v>0.996014058589935</v>
+        <v>0.99601411819458</v>
       </c>
       <c r="H91" t="n">
         <v>8400</v>
@@ -3037,7 +3037,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G92" t="n">
-        <v>1.03725016117096</v>
+        <v>1.03725028038025</v>
       </c>
       <c r="H92" t="n">
         <v>7600</v>
@@ -3066,7 +3066,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G93" t="n">
-        <v>1.03883612155914</v>
+        <v>1.03883624076843</v>
       </c>
       <c r="H93" t="n">
         <v>5200</v>
@@ -3095,7 +3095,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G94" t="n">
-        <v>1.04438722133636</v>
+        <v>1.04438734054565</v>
       </c>
       <c r="H94" t="n">
         <v>1200</v>
@@ -3182,7 +3182,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G97" t="n">
-        <v>1.011873960495</v>
+        <v>1.01187407970428</v>
       </c>
       <c r="H97" t="n">
         <v>400</v>
@@ -3211,7 +3211,7 @@
         <v>1.27600002288818</v>
       </c>
       <c r="G98" t="n">
-        <v>1.011873960495</v>
+        <v>1.01187407970428</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G105" t="n">
-        <v>0.935745537281036</v>
+        <v>0.935745596885681</v>
       </c>
       <c r="H105" t="n">
         <v>4400</v>
@@ -3675,7 +3675,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G114" t="n">
-        <v>0.903232514858246</v>
+        <v>0.903232395648956</v>
       </c>
       <c r="H114" t="n">
         <v>19200</v>
@@ -3704,7 +3704,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G115" t="n">
-        <v>0.904025375843048</v>
+        <v>0.904025495052338</v>
       </c>
       <c r="H115" t="n">
         <v>800</v>
@@ -3791,7 +3791,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G118" t="n">
-        <v>0.884993314743042</v>
+        <v>0.884993374347687</v>
       </c>
       <c r="H118" t="n">
         <v>4800</v>
@@ -3907,7 +3907,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G122" t="n">
-        <v>0.864375233650208</v>
+        <v>0.864375174045563</v>
       </c>
       <c r="H122" t="n">
         <v>59600</v>
@@ -3936,7 +3936,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G123" t="n">
-        <v>0.841377973556519</v>
+        <v>0.841378033161163</v>
       </c>
       <c r="H123" t="n">
         <v>72000</v>
@@ -3965,7 +3965,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>0.824724912643433</v>
+        <v>0.824724972248077</v>
       </c>
       <c r="H124" t="n">
         <v>2800</v>
@@ -4023,7 +4023,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>0.796969771385193</v>
+        <v>0.796969830989838</v>
       </c>
       <c r="H126" t="n">
         <v>42400</v>
@@ -4052,7 +4052,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G127" t="n">
-        <v>0.800934731960297</v>
+        <v>0.800934791564941</v>
       </c>
       <c r="H127" t="n">
         <v>400</v>
@@ -4081,7 +4081,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G128" t="n">
-        <v>0.800934731960297</v>
+        <v>0.800934791564941</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G129" t="n">
-        <v>0.734322369098663</v>
+        <v>0.734322428703308</v>
       </c>
       <c r="H129" t="n">
         <v>11600</v>
@@ -4197,7 +4197,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G132" t="n">
-        <v>0.729564309120178</v>
+        <v>0.729564368724823</v>
       </c>
       <c r="H132" t="n">
         <v>2000</v>
@@ -4226,7 +4226,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G133" t="n">
-        <v>0.733529448509216</v>
+        <v>0.733529388904572</v>
       </c>
       <c r="H133" t="n">
         <v>800</v>
@@ -4255,7 +4255,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G134" t="n">
-        <v>0.802520751953125</v>
+        <v>0.80252081155777</v>
       </c>
       <c r="H134" t="n">
         <v>18000</v>
@@ -4284,7 +4284,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G135" t="n">
-        <v>0.780713140964508</v>
+        <v>0.780713200569153</v>
       </c>
       <c r="H135" t="n">
         <v>7600</v>
@@ -4342,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H137" t="n">
         <v>13200</v>
@@ -4371,7 +4371,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G138" t="n">
-        <v>0.823931932449341</v>
+        <v>0.823931992053986</v>
       </c>
       <c r="H138" t="n">
         <v>2400</v>
@@ -4400,7 +4400,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G139" t="n">
-        <v>0.823931932449341</v>
+        <v>0.823931992053986</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G141" t="n">
-        <v>0.831862092018127</v>
+        <v>0.831862032413483</v>
       </c>
       <c r="H141" t="n">
         <v>4800</v>
@@ -4545,7 +4545,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G144" t="n">
-        <v>0.835034012794495</v>
+        <v>0.83503395318985</v>
       </c>
       <c r="H144" t="n">
         <v>11600</v>
@@ -4574,7 +4574,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G145" t="n">
-        <v>0.835034012794495</v>
+        <v>0.83503395318985</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G146" t="n">
-        <v>0.835034012794495</v>
+        <v>0.83503395318985</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G147" t="n">
-        <v>0.835034012794495</v>
+        <v>0.83503395318985</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G148" t="n">
-        <v>0.851687073707581</v>
+        <v>0.85168719291687</v>
       </c>
       <c r="H148" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G150" t="n">
-        <v>0.848515033721924</v>
+        <v>0.848515093326569</v>
       </c>
       <c r="H150" t="n">
         <v>400</v>
@@ -4748,7 +4748,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G151" t="n">
-        <v>0.808864831924438</v>
+        <v>0.808864772319794</v>
       </c>
       <c r="H151" t="n">
         <v>5600</v>
@@ -4777,7 +4777,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>0.808864831924438</v>
+        <v>0.808864772319794</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G153" t="n">
-        <v>0.808864831924438</v>
+        <v>0.808864772319794</v>
       </c>
       <c r="H153" t="n">
         <v>2000</v>
@@ -4835,7 +4835,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G154" t="n">
-        <v>0.808864831924438</v>
+        <v>0.808864772319794</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>0.824724912643433</v>
+        <v>0.824724972248077</v>
       </c>
       <c r="H155" t="n">
         <v>5600</v>
@@ -4893,7 +4893,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>0.824724912643433</v>
+        <v>0.824724972248077</v>
       </c>
       <c r="H156" t="n">
         <v>2400</v>
@@ -4951,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H158" t="n">
         <v>6000</v>
@@ -5009,7 +5009,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G160" t="n">
-        <v>0.779127180576324</v>
+        <v>0.779127240180969</v>
       </c>
       <c r="H160" t="n">
         <v>5200</v>
@@ -5038,7 +5038,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G161" t="n">
-        <v>0.769214630126953</v>
+        <v>0.769214689731598</v>
       </c>
       <c r="H161" t="n">
         <v>12400</v>
@@ -5067,7 +5067,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G162" t="n">
-        <v>0.769214630126953</v>
+        <v>0.769214689731598</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G163" t="n">
-        <v>0.747010409832001</v>
+        <v>0.747010469436646</v>
       </c>
       <c r="H163" t="n">
         <v>2000</v>
@@ -5125,7 +5125,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G164" t="n">
-        <v>0.747010409832001</v>
+        <v>0.747010469436646</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G166" t="n">
-        <v>0.758112490177155</v>
+        <v>0.758112549781799</v>
       </c>
       <c r="H166" t="n">
         <v>800</v>
@@ -5212,7 +5212,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G167" t="n">
-        <v>0.779127180576324</v>
+        <v>0.779127240180969</v>
       </c>
       <c r="H167" t="n">
         <v>400</v>
@@ -5270,7 +5270,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G169" t="n">
-        <v>0.769214630126953</v>
+        <v>0.769214689731598</v>
       </c>
       <c r="H169" t="n">
         <v>2400</v>
@@ -5299,7 +5299,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G170" t="n">
-        <v>0.751768469810486</v>
+        <v>0.751768529415131</v>
       </c>
       <c r="H170" t="n">
         <v>13600</v>
@@ -5328,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H171" t="n">
         <v>3200</v>
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H172" t="n">
         <v>3600</v>
@@ -5386,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G175" t="n">
-        <v>0.785074651241302</v>
+        <v>0.785074710845947</v>
       </c>
       <c r="H175" t="n">
         <v>5200</v>
@@ -5473,7 +5473,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>0.785074651241302</v>
+        <v>0.785074710845947</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G177" t="n">
-        <v>0.794590771198273</v>
+        <v>0.794590711593628</v>
       </c>
       <c r="H177" t="n">
         <v>28400</v>
@@ -5531,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="G178" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H178" t="n">
         <v>32400</v>
@@ -5560,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H179" t="n">
         <v>23600</v>
@@ -5705,7 +5705,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G184" t="n">
-        <v>0.769214630126953</v>
+        <v>0.769214689731598</v>
       </c>
       <c r="H184" t="n">
         <v>31600</v>
@@ -5763,7 +5763,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G186" t="n">
-        <v>0.717669367790222</v>
+        <v>0.717669308185577</v>
       </c>
       <c r="H186" t="n">
         <v>10800</v>
@@ -5792,7 +5792,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>0.766835570335388</v>
+        <v>0.766835629940033</v>
       </c>
       <c r="H187" t="n">
         <v>41200</v>
@@ -5850,7 +5850,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>0.689914166927338</v>
+        <v>0.689914107322693</v>
       </c>
       <c r="H189" t="n">
         <v>35200</v>
@@ -5937,7 +5937,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G192" t="n">
-        <v>0.681984066963196</v>
+        <v>0.681984126567841</v>
       </c>
       <c r="H192" t="n">
         <v>24800</v>
@@ -5966,7 +5966,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G193" t="n">
-        <v>0.650263905525208</v>
+        <v>0.650263845920563</v>
       </c>
       <c r="H193" t="n">
         <v>27600</v>
@@ -5995,7 +5995,7 @@
         <v>0.807500004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>0.640351295471191</v>
+        <v>0.640351355075836</v>
       </c>
       <c r="H194" t="n">
         <v>51200</v>
@@ -6024,7 +6024,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G195" t="n">
-        <v>0.634403765201569</v>
+        <v>0.634403884410858</v>
       </c>
       <c r="H195" t="n">
         <v>15200</v>
@@ -6053,7 +6053,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G196" t="n">
-        <v>0.628852784633636</v>
+        <v>0.628852725028992</v>
       </c>
       <c r="H196" t="n">
         <v>64400</v>
@@ -6111,7 +6111,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G198" t="n">
-        <v>0.607441663742065</v>
+        <v>0.607441544532776</v>
       </c>
       <c r="H198" t="n">
         <v>14400</v>
@@ -6285,7 +6285,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>0.555499851703644</v>
+        <v>0.555499792098999</v>
       </c>
       <c r="H204" t="n">
         <v>38000</v>
@@ -6314,7 +6314,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G205" t="n">
-        <v>0.56303334236145</v>
+        <v>0.563033401966095</v>
       </c>
       <c r="H205" t="n">
         <v>16800</v>
@@ -6401,7 +6401,7 @@
         <v>0.722500026226044</v>
       </c>
       <c r="G208" t="n">
-        <v>0.572945952415466</v>
+        <v>0.572946012020111</v>
       </c>
       <c r="H208" t="n">
         <v>74800</v>
@@ -6459,7 +6459,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G210" t="n">
-        <v>0.555103361606598</v>
+        <v>0.555103302001953</v>
       </c>
       <c r="H210" t="n">
         <v>25200</v>
@@ -6517,7 +6517,7 @@
         <v>0.746999979019165</v>
       </c>
       <c r="G212" t="n">
-        <v>0.592374503612518</v>
+        <v>0.592374563217163</v>
       </c>
       <c r="H212" t="n">
         <v>158000</v>
@@ -6575,7 +6575,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G214" t="n">
-        <v>0.56303334236145</v>
+        <v>0.563033401966095</v>
       </c>
       <c r="H214" t="n">
         <v>102400</v>
@@ -6691,7 +6691,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G218" t="n">
-        <v>0.56303334236145</v>
+        <v>0.563033401966095</v>
       </c>
       <c r="H218" t="n">
         <v>25600</v>
@@ -6749,7 +6749,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G220" t="n">
-        <v>0.539243280887604</v>
+        <v>0.539243221282959</v>
       </c>
       <c r="H220" t="n">
         <v>26400</v>
@@ -6807,7 +6807,7 @@
         <v>0.698499977588654</v>
       </c>
       <c r="G222" t="n">
-        <v>0.553913772106171</v>
+        <v>0.553913831710815</v>
       </c>
       <c r="H222" t="n">
         <v>52000</v>
@@ -6894,7 +6894,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G225" t="n">
-        <v>0.523383140563965</v>
+        <v>0.52338308095932</v>
       </c>
       <c r="H225" t="n">
         <v>7600</v>
@@ -6923,7 +6923,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G226" t="n">
-        <v>0.515453100204468</v>
+        <v>0.515453040599823</v>
       </c>
       <c r="H226" t="n">
         <v>62800</v>
@@ -6952,7 +6952,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G227" t="n">
-        <v>0.507523000240326</v>
+        <v>0.507523059844971</v>
       </c>
       <c r="H227" t="n">
         <v>52000</v>
@@ -6981,7 +6981,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>0.513867080211639</v>
+        <v>0.513867020606995</v>
       </c>
       <c r="H228" t="n">
         <v>34800</v>
@@ -7068,7 +7068,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G231" t="n">
-        <v>0.55113822221756</v>
+        <v>0.551138281822205</v>
       </c>
       <c r="H231" t="n">
         <v>14800</v>
@@ -7126,7 +7126,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G233" t="n">
-        <v>0.539243280887604</v>
+        <v>0.539243221282959</v>
       </c>
       <c r="H233" t="n">
         <v>20800</v>
@@ -7155,7 +7155,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G234" t="n">
-        <v>0.531313180923462</v>
+        <v>0.531313240528107</v>
       </c>
       <c r="H234" t="n">
         <v>4800</v>
@@ -7184,7 +7184,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G235" t="n">
-        <v>0.531313180923462</v>
+        <v>0.531313240528107</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>0.727500021457672</v>
       </c>
       <c r="G236" t="n">
-        <v>0.57691103219986</v>
+        <v>0.576910972595215</v>
       </c>
       <c r="H236" t="n">
         <v>186000</v>
@@ -7242,7 +7242,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G237" t="n">
-        <v>0.55113822221756</v>
+        <v>0.551138281822205</v>
       </c>
       <c r="H237" t="n">
         <v>2800</v>
@@ -7300,7 +7300,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>0.521797180175781</v>
+        <v>0.521797120571136</v>
       </c>
       <c r="H239" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G241" t="n">
-        <v>0.539243280887604</v>
+        <v>0.539243221282959</v>
       </c>
       <c r="H241" t="n">
         <v>13200</v>
@@ -7387,7 +7387,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G242" t="n">
-        <v>0.539243280887604</v>
+        <v>0.539243221282959</v>
       </c>
       <c r="H242" t="n">
         <v>8000</v>
@@ -7416,7 +7416,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G243" t="n">
-        <v>0.523383140563965</v>
+        <v>0.52338308095932</v>
       </c>
       <c r="H243" t="n">
         <v>8000</v>
@@ -7445,7 +7445,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G244" t="n">
-        <v>0.523383140563965</v>
+        <v>0.52338308095932</v>
       </c>
       <c r="H244" t="n">
         <v>10400</v>
@@ -7474,7 +7474,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G245" t="n">
-        <v>0.523383140563965</v>
+        <v>0.52338308095932</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G246" t="n">
-        <v>0.523383140563965</v>
+        <v>0.52338308095932</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>0.71450001001358</v>
       </c>
       <c r="G247" t="n">
-        <v>0.566601932048798</v>
+        <v>0.566601872444153</v>
       </c>
       <c r="H247" t="n">
         <v>102400</v>
@@ -7561,7 +7561,7 @@
         <v>0.720499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>0.571359872817993</v>
+        <v>0.571359932422638</v>
       </c>
       <c r="H248" t="n">
         <v>43200</v>
@@ -7590,7 +7590,7 @@
         <v>0.703499972820282</v>
       </c>
       <c r="G249" t="n">
-        <v>0.557878851890564</v>
+        <v>0.557878792285919</v>
       </c>
       <c r="H249" t="n">
         <v>17200</v>
@@ -7706,7 +7706,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G253" t="n">
-        <v>0.615371644496918</v>
+        <v>0.615371704101562</v>
       </c>
       <c r="H253" t="n">
         <v>42000</v>
@@ -7735,7 +7735,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G254" t="n">
-        <v>0.626473784446716</v>
+        <v>0.626473724842072</v>
       </c>
       <c r="H254" t="n">
         <v>97200</v>
@@ -7764,7 +7764,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G255" t="n">
-        <v>0.650263905525208</v>
+        <v>0.650263845920563</v>
       </c>
       <c r="H255" t="n">
         <v>39600</v>
@@ -7793,7 +7793,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G256" t="n">
-        <v>0.650263905525208</v>
+        <v>0.650263845920563</v>
       </c>
       <c r="H256" t="n">
         <v>27200</v>
@@ -7822,7 +7822,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G257" t="n">
-        <v>0.665330946445465</v>
+        <v>0.66533100605011</v>
       </c>
       <c r="H257" t="n">
         <v>88400</v>
@@ -7851,7 +7851,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G258" t="n">
-        <v>0.769214630126953</v>
+        <v>0.769214689731598</v>
       </c>
       <c r="H258" t="n">
         <v>111600</v>
@@ -7880,7 +7880,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>0.77714467048645</v>
+        <v>0.777144730091095</v>
       </c>
       <c r="H259" t="n">
         <v>194400</v>
@@ -7909,7 +7909,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G260" t="n">
-        <v>0.785074651241302</v>
+        <v>0.785074710845947</v>
       </c>
       <c r="H260" t="n">
         <v>67200</v>
@@ -7938,7 +7938,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H261" t="n">
         <v>81600</v>
@@ -7967,7 +7967,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H262" t="n">
         <v>25200</v>
@@ -7996,7 +7996,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G263" t="n">
-        <v>0.80727881193161</v>
+        <v>0.807278871536255</v>
       </c>
       <c r="H263" t="n">
         <v>35600</v>
@@ -8025,7 +8025,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>0.796969771385193</v>
+        <v>0.796969830989838</v>
       </c>
       <c r="H264" t="n">
         <v>3600</v>
@@ -8112,7 +8112,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G267" t="n">
-        <v>0.800934731960297</v>
+        <v>0.800934791564941</v>
       </c>
       <c r="H267" t="n">
         <v>14000</v>
@@ -8170,7 +8170,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G269" t="n">
-        <v>0.786264181137085</v>
+        <v>0.78626424074173</v>
       </c>
       <c r="H269" t="n">
         <v>13600</v>
@@ -8199,7 +8199,7 @@
         <v>0.984499990940094</v>
       </c>
       <c r="G270" t="n">
-        <v>0.780713140964508</v>
+        <v>0.780713200569153</v>
       </c>
       <c r="H270" t="n">
         <v>8400</v>
@@ -8228,7 +8228,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G271" t="n">
-        <v>0.77714467048645</v>
+        <v>0.777144730091095</v>
       </c>
       <c r="H271" t="n">
         <v>4800</v>
@@ -8257,7 +8257,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G272" t="n">
-        <v>0.785074651241302</v>
+        <v>0.785074710845947</v>
       </c>
       <c r="H272" t="n">
         <v>34400</v>
@@ -8315,7 +8315,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G274" t="n">
-        <v>0.785074651241302</v>
+        <v>0.785074710845947</v>
       </c>
       <c r="H274" t="n">
         <v>2400</v>
@@ -8344,7 +8344,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>0.77714467048645</v>
+        <v>0.777144730091095</v>
       </c>
       <c r="H275" t="n">
         <v>7200</v>
@@ -8518,7 +8518,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>0.785074651241302</v>
+        <v>0.785074710845947</v>
       </c>
       <c r="H281" t="n">
         <v>35600</v>
@@ -8576,7 +8576,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G283" t="n">
-        <v>0.769214630126953</v>
+        <v>0.769214689731598</v>
       </c>
       <c r="H283" t="n">
         <v>3200</v>
@@ -8605,7 +8605,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G284" t="n">
-        <v>0.754147529602051</v>
+        <v>0.754147469997406</v>
       </c>
       <c r="H284" t="n">
         <v>17600</v>
@@ -8692,7 +8692,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G287" t="n">
-        <v>0.666123986244202</v>
+        <v>0.666124045848846</v>
       </c>
       <c r="H287" t="n">
         <v>27200</v>
@@ -8721,7 +8721,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G288" t="n">
-        <v>0.647884905338287</v>
+        <v>0.647884845733643</v>
       </c>
       <c r="H288" t="n">
         <v>14800</v>
@@ -8750,7 +8750,7 @@
         <v>0.800499975681305</v>
       </c>
       <c r="G289" t="n">
-        <v>0.634800255298615</v>
+        <v>0.634800314903259</v>
       </c>
       <c r="H289" t="n">
         <v>12800</v>
@@ -8779,7 +8779,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G290" t="n">
-        <v>0.64233386516571</v>
+        <v>0.642333805561066</v>
       </c>
       <c r="H290" t="n">
         <v>23200</v>
@@ -8808,7 +8808,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G291" t="n">
-        <v>0.653436005115509</v>
+        <v>0.653435945510864</v>
       </c>
       <c r="H291" t="n">
         <v>9200</v>
@@ -8837,7 +8837,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G292" t="n">
-        <v>0.662158966064453</v>
+        <v>0.662159025669098</v>
       </c>
       <c r="H292" t="n">
         <v>8000</v>
@@ -8895,7 +8895,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G294" t="n">
-        <v>0.646298885345459</v>
+        <v>0.646298825740814</v>
       </c>
       <c r="H294" t="n">
         <v>14800</v>
@@ -9069,7 +9069,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>0.689914166927338</v>
+        <v>0.689914107322693</v>
       </c>
       <c r="H300" t="n">
         <v>30800</v>
@@ -9098,7 +9098,7 @@
         <v>0.856500029563904</v>
       </c>
       <c r="G301" t="n">
-        <v>0.67920857667923</v>
+        <v>0.679208517074585</v>
       </c>
       <c r="H301" t="n">
         <v>12800</v>
@@ -9127,7 +9127,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G302" t="n">
-        <v>0.672468066215515</v>
+        <v>0.67246800661087</v>
       </c>
       <c r="H302" t="n">
         <v>10000</v>
@@ -9185,7 +9185,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G304" t="n">
-        <v>0.696258246898651</v>
+        <v>0.696258187294006</v>
       </c>
       <c r="H304" t="n">
         <v>16800</v>
@@ -9301,7 +9301,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G308" t="n">
-        <v>0.672864556312561</v>
+        <v>0.672864496707916</v>
       </c>
       <c r="H308" t="n">
         <v>2800</v>
@@ -9330,7 +9330,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G309" t="n">
-        <v>0.672864556312561</v>
+        <v>0.672864496707916</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G311" t="n">
-        <v>0.662158966064453</v>
+        <v>0.662159025669098</v>
       </c>
       <c r="H311" t="n">
         <v>50000</v>
@@ -9446,7 +9446,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G313" t="n">
-        <v>0.650263905525208</v>
+        <v>0.650263845920563</v>
       </c>
       <c r="H313" t="n">
         <v>40800</v>
@@ -9475,7 +9475,7 @@
         <v>0.826499998569489</v>
       </c>
       <c r="G314" t="n">
-        <v>0.655418395996094</v>
+        <v>0.655418455600739</v>
       </c>
       <c r="H314" t="n">
         <v>190000</v>
@@ -9504,7 +9504,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G315" t="n">
-        <v>0.650263905525208</v>
+        <v>0.650263845920563</v>
       </c>
       <c r="H315" t="n">
         <v>88400</v>
@@ -9533,7 +9533,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G316" t="n">
-        <v>0.654228866100311</v>
+        <v>0.654228925704956</v>
       </c>
       <c r="H316" t="n">
         <v>20400</v>
@@ -9562,7 +9562,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>0.649470925331116</v>
+        <v>0.649470865726471</v>
       </c>
       <c r="H317" t="n">
         <v>30000</v>
@@ -9678,7 +9678,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>0.689914166927338</v>
+        <v>0.689914107322693</v>
       </c>
       <c r="H321" t="n">
         <v>191200</v>
@@ -9707,7 +9707,7 @@
         <v>0.903500020503998</v>
       </c>
       <c r="G322" t="n">
-        <v>0.71647983789444</v>
+        <v>0.716479778289795</v>
       </c>
       <c r="H322" t="n">
         <v>112000</v>
@@ -9765,7 +9765,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G324" t="n">
-        <v>0.718462288379669</v>
+        <v>0.718462347984314</v>
       </c>
       <c r="H324" t="n">
         <v>52400</v>
@@ -9823,7 +9823,7 @@
         <v>0.952499985694885</v>
       </c>
       <c r="G326" t="n">
-        <v>0.755337059497833</v>
+        <v>0.755336999893188</v>
       </c>
       <c r="H326" t="n">
         <v>210000</v>
@@ -9852,7 +9852,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G327" t="n">
-        <v>0.780316710472107</v>
+        <v>0.780316770076752</v>
       </c>
       <c r="H327" t="n">
         <v>180800</v>
@@ -9881,7 +9881,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G328" t="n">
-        <v>0.814415872097015</v>
+        <v>0.814415812492371</v>
       </c>
       <c r="H328" t="n">
         <v>216400</v>
@@ -9939,7 +9939,7 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0.793004810810089</v>
+        <v>0.793004751205444</v>
       </c>
       <c r="H330" t="n">
         <v>268000</v>
@@ -9997,7 +9997,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G332" t="n">
-        <v>0.836619913578033</v>
+        <v>0.836619973182678</v>
       </c>
       <c r="H332" t="n">
         <v>138000</v>
@@ -10026,7 +10026,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G333" t="n">
-        <v>0.836619913578033</v>
+        <v>0.836619973182678</v>
       </c>
       <c r="H333" t="n">
         <v>26800</v>
@@ -10055,7 +10055,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G334" t="n">
-        <v>0.836619913578033</v>
+        <v>0.836619973182678</v>
       </c>
       <c r="H334" t="n">
         <v>52400</v>
@@ -10084,7 +10084,7 @@
         <v>1.07200002670288</v>
       </c>
       <c r="G335" t="n">
-        <v>0.850101053714752</v>
+        <v>0.850101113319397</v>
       </c>
       <c r="H335" t="n">
         <v>56000</v>
@@ -10113,7 +10113,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G336" t="n">
-        <v>0.854858994483948</v>
+        <v>0.854859113693237</v>
       </c>
       <c r="H336" t="n">
         <v>76400</v>
@@ -10171,7 +10171,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G338" t="n">
-        <v>0.855652153491974</v>
+        <v>0.855652093887329</v>
       </c>
       <c r="H338" t="n">
         <v>66000</v>
@@ -10316,7 +10316,7 @@
         <v>1.0110000371933</v>
       </c>
       <c r="G343" t="n">
-        <v>0.843673646450043</v>
+        <v>0.843673586845398</v>
       </c>
       <c r="H343" t="n">
         <v>36400</v>
@@ -10345,7 +10345,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G344" t="n">
-        <v>0.842839121818542</v>
+        <v>0.842839062213898</v>
       </c>
       <c r="H344" t="n">
         <v>42800</v>
@@ -10374,7 +10374,7 @@
         <v>0.991500020027161</v>
       </c>
       <c r="G345" t="n">
-        <v>0.827400922775269</v>
+        <v>0.827400982379913</v>
       </c>
       <c r="H345" t="n">
         <v>18000</v>
@@ -10403,7 +10403,7 @@
         <v>1.00899994373322</v>
       </c>
       <c r="G346" t="n">
-        <v>0.842004597187042</v>
+        <v>0.842004537582397</v>
       </c>
       <c r="H346" t="n">
         <v>32400</v>
@@ -10432,7 +10432,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G347" t="n">
-        <v>0.838666617870331</v>
+        <v>0.838666677474976</v>
       </c>
       <c r="H347" t="n">
         <v>16000</v>
@@ -10490,7 +10490,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G349" t="n">
-        <v>0.824897468090057</v>
+        <v>0.824897527694702</v>
       </c>
       <c r="H349" t="n">
         <v>400</v>
@@ -10548,7 +10548,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G351" t="n">
-        <v>0.805286884307861</v>
+        <v>0.805286824703217</v>
       </c>
       <c r="H351" t="n">
         <v>7200</v>
@@ -10722,7 +10722,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G357" t="n">
-        <v>1.14075350761414</v>
+        <v>1.14075338840485</v>
       </c>
       <c r="H357" t="n">
         <v>584400</v>
@@ -10751,7 +10751,7 @@
         <v>1.38699996471405</v>
       </c>
       <c r="G358" t="n">
-        <v>1.1574432849884</v>
+        <v>1.15744340419769</v>
       </c>
       <c r="H358" t="n">
         <v>1138800</v>
@@ -10896,7 +10896,7 @@
         <v>1.25</v>
       </c>
       <c r="G363" t="n">
-        <v>1.04311776161194</v>
+        <v>1.04311764240265</v>
       </c>
       <c r="H363" t="n">
         <v>82400</v>
@@ -10954,7 +10954,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G365" t="n">
-        <v>0.973854660987854</v>
+        <v>0.973854720592499</v>
       </c>
       <c r="H365" t="n">
         <v>172400</v>
@@ -10983,7 +10983,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>0.988875508308411</v>
+        <v>0.988875448703766</v>
       </c>
       <c r="H366" t="n">
         <v>155200</v>
@@ -11012,7 +11012,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G367" t="n">
-        <v>0.997220516204834</v>
+        <v>0.997220575809479</v>
       </c>
       <c r="H367" t="n">
         <v>41200</v>
@@ -11070,7 +11070,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G369" t="n">
-        <v>1.04812467098236</v>
+        <v>1.04812479019165</v>
       </c>
       <c r="H369" t="n">
         <v>56400</v>
@@ -11128,7 +11128,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G371" t="n">
-        <v>1.10069787502289</v>
+        <v>1.1006977558136</v>
       </c>
       <c r="H371" t="n">
         <v>264800</v>
@@ -11157,7 +11157,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G372" t="n">
-        <v>1.06314551830292</v>
+        <v>1.06314563751221</v>
       </c>
       <c r="H372" t="n">
         <v>102400</v>
@@ -11186,7 +11186,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G373" t="n">
-        <v>1.0297657251358</v>
+        <v>1.02976584434509</v>
       </c>
       <c r="H373" t="n">
         <v>79200</v>
@@ -11215,7 +11215,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G374" t="n">
-        <v>1.04812467098236</v>
+        <v>1.04812479019165</v>
       </c>
       <c r="H374" t="n">
         <v>59600</v>
@@ -11244,7 +11244,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G375" t="n">
-        <v>1.03894531726837</v>
+        <v>1.03894519805908</v>
       </c>
       <c r="H375" t="n">
         <v>6400</v>
@@ -11360,7 +11360,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G379" t="n">
-        <v>0.982199549674988</v>
+        <v>0.982199728488922</v>
       </c>
       <c r="H379" t="n">
         <v>12400</v>
@@ -11389,7 +11389,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G380" t="n">
-        <v>0.991379082202911</v>
+        <v>0.991378962993622</v>
       </c>
       <c r="H380" t="n">
         <v>3600</v>
@@ -11418,7 +11418,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G381" t="n">
-        <v>0.974689126014709</v>
+        <v>0.974689066410065</v>
       </c>
       <c r="H381" t="n">
         <v>11200</v>
@@ -11447,7 +11447,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G382" t="n">
-        <v>0.976357996463776</v>
+        <v>0.976358115673065</v>
       </c>
       <c r="H382" t="n">
         <v>22800</v>
@@ -11476,7 +11476,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G383" t="n">
-        <v>0.979696094989777</v>
+        <v>0.979696214199066</v>
       </c>
       <c r="H383" t="n">
         <v>25200</v>
@@ -11505,7 +11505,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G384" t="n">
-        <v>0.961337268352509</v>
+        <v>0.961337089538574</v>
       </c>
       <c r="H384" t="n">
         <v>13200</v>
@@ -11534,7 +11534,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G385" t="n">
-        <v>0.950488865375519</v>
+        <v>0.950488805770874</v>
       </c>
       <c r="H385" t="n">
         <v>35600</v>
@@ -11621,7 +11621,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G388" t="n">
-        <v>0.997220516204834</v>
+        <v>0.997220575809479</v>
       </c>
       <c r="H388" t="n">
         <v>8000</v>
@@ -11708,7 +11708,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G391" t="n">
-        <v>0.971351146697998</v>
+        <v>0.971351206302643</v>
       </c>
       <c r="H391" t="n">
         <v>7600</v>
@@ -11737,7 +11737,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G392" t="n">
-        <v>0.971351146697998</v>
+        <v>0.971351206302643</v>
       </c>
       <c r="H392" t="n">
         <v>2400</v>
@@ -11766,7 +11766,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G393" t="n">
-        <v>0.973020136356354</v>
+        <v>0.973020195960999</v>
       </c>
       <c r="H393" t="n">
         <v>97600</v>
@@ -11795,7 +11795,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G394" t="n">
-        <v>0.951323330402374</v>
+        <v>0.951323390007019</v>
       </c>
       <c r="H394" t="n">
         <v>26000</v>
@@ -11853,7 +11853,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G396" t="n">
-        <v>0.97552365064621</v>
+        <v>0.975523591041565</v>
       </c>
       <c r="H396" t="n">
         <v>20400</v>
@@ -11882,7 +11882,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G397" t="n">
-        <v>0.951323330402374</v>
+        <v>0.951323390007019</v>
       </c>
       <c r="H397" t="n">
         <v>4800</v>
@@ -11911,7 +11911,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G398" t="n">
-        <v>0.951323330402374</v>
+        <v>0.951323390007019</v>
       </c>
       <c r="H398" t="n">
         <v>5600</v>
@@ -12027,7 +12027,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G402" t="n">
-        <v>1.04144871234894</v>
+        <v>1.04144883155823</v>
       </c>
       <c r="H402" t="n">
         <v>101200</v>
@@ -12114,7 +12114,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G405" t="n">
-        <v>1.03060030937195</v>
+        <v>1.03060019016266</v>
       </c>
       <c r="H405" t="n">
         <v>6000</v>
@@ -12143,7 +12143,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G406" t="n">
-        <v>1.03060030937195</v>
+        <v>1.03060019016266</v>
       </c>
       <c r="H406" t="n">
         <v>36800</v>
@@ -12172,7 +12172,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G407" t="n">
-        <v>1.07232487201691</v>
+        <v>1.0723249912262</v>
       </c>
       <c r="H407" t="n">
         <v>139600</v>
@@ -12201,7 +12201,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>1.05396628379822</v>
+        <v>1.05396616458893</v>
       </c>
       <c r="H408" t="n">
         <v>126800</v>
@@ -12230,7 +12230,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G409" t="n">
-        <v>1.03894531726837</v>
+        <v>1.03894519805908</v>
       </c>
       <c r="H409" t="n">
         <v>22400</v>
@@ -12346,7 +12346,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G413" t="n">
-        <v>0.986372113227844</v>
+        <v>0.986372172832489</v>
       </c>
       <c r="H413" t="n">
         <v>21200</v>
@@ -12375,7 +12375,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G414" t="n">
-        <v>0.974689126014709</v>
+        <v>0.974689066410065</v>
       </c>
       <c r="H414" t="n">
         <v>14000</v>
@@ -12404,7 +12404,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G415" t="n">
-        <v>0.971351146697998</v>
+        <v>0.971351206302643</v>
       </c>
       <c r="H415" t="n">
         <v>30800</v>
@@ -12433,7 +12433,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G416" t="n">
-        <v>1.01140701770782</v>
+        <v>1.01140689849854</v>
       </c>
       <c r="H416" t="n">
         <v>13600</v>
@@ -12520,7 +12520,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G419" t="n">
-        <v>0.982199549674988</v>
+        <v>0.982199728488922</v>
       </c>
       <c r="H419" t="n">
         <v>50000</v>
@@ -12549,7 +12549,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G420" t="n">
-        <v>0.982199549674988</v>
+        <v>0.982199728488922</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G422" t="n">
-        <v>0.976357996463776</v>
+        <v>0.976358115673065</v>
       </c>
       <c r="H422" t="n">
         <v>11200</v>
@@ -12665,7 +12665,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G424" t="n">
-        <v>0.979696094989777</v>
+        <v>0.979696214199066</v>
       </c>
       <c r="H424" t="n">
         <v>9200</v>
@@ -12694,7 +12694,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G425" t="n">
-        <v>0.979696094989777</v>
+        <v>0.979696214199066</v>
       </c>
       <c r="H425" t="n">
         <v>400</v>
@@ -12723,7 +12723,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G426" t="n">
-        <v>0.987206518650055</v>
+        <v>0.9872065782547</v>
       </c>
       <c r="H426" t="n">
         <v>800</v>
@@ -12781,7 +12781,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G428" t="n">
-        <v>1.00055849552155</v>
+        <v>1.00055861473083</v>
       </c>
       <c r="H428" t="n">
         <v>11200</v>
@@ -12810,7 +12810,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G429" t="n">
-        <v>0.9880411028862</v>
+        <v>0.98804098367691</v>
       </c>
       <c r="H429" t="n">
         <v>5200</v>
@@ -12839,7 +12839,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G430" t="n">
-        <v>1.00055849552155</v>
+        <v>1.00055861473083</v>
       </c>
       <c r="H430" t="n">
         <v>2800</v>
@@ -12926,7 +12926,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G433" t="n">
-        <v>0.962171852588654</v>
+        <v>0.962171733379364</v>
       </c>
       <c r="H433" t="n">
         <v>32800</v>
@@ -12984,7 +12984,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G435" t="n">
-        <v>0.987206518650055</v>
+        <v>0.9872065782547</v>
       </c>
       <c r="H435" t="n">
         <v>21600</v>
@@ -13071,7 +13071,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G438" t="n">
-        <v>0.91794365644455</v>
+        <v>0.91794353723526</v>
       </c>
       <c r="H438" t="n">
         <v>164800</v>
@@ -13129,7 +13129,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G440" t="n">
-        <v>0.91794365644455</v>
+        <v>0.91794353723526</v>
       </c>
       <c r="H440" t="n">
         <v>138000</v>
@@ -13187,7 +13187,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G442" t="n">
-        <v>0.932129859924316</v>
+        <v>0.932129919528961</v>
       </c>
       <c r="H442" t="n">
         <v>20400</v>
@@ -13332,7 +13332,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G447" t="n">
-        <v>0.967178821563721</v>
+        <v>0.967178761959076</v>
       </c>
       <c r="H447" t="n">
         <v>137200</v>
@@ -13361,7 +13361,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G448" t="n">
-        <v>0.947985291481018</v>
+        <v>0.947985351085663</v>
       </c>
       <c r="H448" t="n">
         <v>54000</v>
@@ -13448,7 +13448,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G451" t="n">
-        <v>0.94130939245224</v>
+        <v>0.94130951166153</v>
       </c>
       <c r="H451" t="n">
         <v>49600</v>
@@ -13506,7 +13506,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G453" t="n">
-        <v>0.965509712696075</v>
+        <v>0.965509653091431</v>
       </c>
       <c r="H453" t="n">
         <v>68000</v>
@@ -13622,7 +13622,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G457" t="n">
-        <v>1.00222742557526</v>
+        <v>1.00222730636597</v>
       </c>
       <c r="H457" t="n">
         <v>43200</v>
@@ -13767,7 +13767,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G462" t="n">
-        <v>1.13491213321686</v>
+        <v>1.13491201400757</v>
       </c>
       <c r="H462" t="n">
         <v>400800</v>
@@ -13825,7 +13825,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G464" t="n">
-        <v>1.45619237422943</v>
+        <v>1.45619225502014</v>
       </c>
       <c r="H464" t="n">
         <v>674400</v>
@@ -13999,7 +13999,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G470" t="n">
-        <v>1.37608087062836</v>
+        <v>1.37608098983765</v>
       </c>
       <c r="H470" t="n">
         <v>335600</v>
@@ -14144,7 +14144,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G475" t="n">
-        <v>1.3185008764267</v>
+        <v>1.31850075721741</v>
       </c>
       <c r="H475" t="n">
         <v>29200</v>
@@ -14173,7 +14173,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G476" t="n">
-        <v>1.30181086063385</v>
+        <v>1.30181074142456</v>
       </c>
       <c r="H476" t="n">
         <v>16400</v>
@@ -14202,7 +14202,7 @@
         <v>1.5</v>
       </c>
       <c r="G477" t="n">
-        <v>1.25174129009247</v>
+        <v>1.25174117088318</v>
       </c>
       <c r="H477" t="n">
         <v>84000</v>
@@ -14231,7 +14231,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G478" t="n">
-        <v>1.2317134141922</v>
+        <v>1.23171317577362</v>
       </c>
       <c r="H478" t="n">
         <v>88000</v>
@@ -14492,7 +14492,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.17246425151825</v>
+        <v>1.17246437072754</v>
       </c>
       <c r="H487" t="n">
         <v>8800</v>
@@ -14579,7 +14579,7 @@
         <v>1.41700005531311</v>
       </c>
       <c r="G490" t="n">
-        <v>1.18247830867767</v>
+        <v>1.18247818946838</v>
       </c>
       <c r="H490" t="n">
         <v>800</v>
@@ -14666,7 +14666,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G493" t="n">
-        <v>1.17580235004425</v>
+        <v>1.17580223083496</v>
       </c>
       <c r="H493" t="n">
         <v>1600</v>
@@ -14695,7 +14695,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G494" t="n">
-        <v>1.24339640140533</v>
+        <v>1.24339628219604</v>
       </c>
       <c r="H494" t="n">
         <v>29600</v>
@@ -14724,7 +14724,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>1.22670638561249</v>
+        <v>1.22670650482178</v>
       </c>
       <c r="H495" t="n">
         <v>4400</v>
@@ -14811,7 +14811,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G498" t="n">
-        <v>1.16996085643768</v>
+        <v>1.16996073722839</v>
       </c>
       <c r="H498" t="n">
         <v>8800</v>
@@ -14840,7 +14840,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G499" t="n">
-        <v>1.17580235004425</v>
+        <v>1.17580223083496</v>
       </c>
       <c r="H499" t="n">
         <v>2800</v>
@@ -14869,7 +14869,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G500" t="n">
-        <v>1.17663669586182</v>
+        <v>1.17663681507111</v>
       </c>
       <c r="H500" t="n">
         <v>1200</v>
@@ -14956,7 +14956,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G503" t="n">
-        <v>1.14909851551056</v>
+        <v>1.14909839630127</v>
       </c>
       <c r="H503" t="n">
         <v>13600</v>
@@ -15043,7 +15043,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G506" t="n">
-        <v>1.09652543067932</v>
+        <v>1.09652519226074</v>
       </c>
       <c r="H506" t="n">
         <v>207600</v>
@@ -15130,7 +15130,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G509" t="n">
-        <v>1.10153245925903</v>
+        <v>1.10153222084045</v>
       </c>
       <c r="H509" t="n">
         <v>2400</v>
@@ -15188,7 +15188,7 @@
         <v>1.36300003528595</v>
       </c>
       <c r="G511" t="n">
-        <v>1.13741552829742</v>
+        <v>1.13741540908813</v>
       </c>
       <c r="H511" t="n">
         <v>19600</v>
@@ -15217,7 +15217,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G512" t="n">
-        <v>1.12656700611115</v>
+        <v>1.12656712532043</v>
       </c>
       <c r="H512" t="n">
         <v>10400</v>
@@ -15275,7 +15275,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G514" t="n">
-        <v>1.10570466518402</v>
+        <v>1.10570478439331</v>
       </c>
       <c r="H514" t="n">
         <v>15200</v>
@@ -15362,7 +15362,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G517" t="n">
-        <v>1.12656700611115</v>
+        <v>1.12656712532043</v>
       </c>
       <c r="H517" t="n">
         <v>12400</v>
@@ -15391,7 +15391,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.11822211742401</v>
+        <v>1.1182222366333</v>
       </c>
       <c r="H518" t="n">
         <v>30400</v>
@@ -15420,7 +15420,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G519" t="n">
-        <v>1.11822211742401</v>
+        <v>1.1182222366333</v>
       </c>
       <c r="H519" t="n">
         <v>25600</v>
@@ -15449,7 +15449,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G520" t="n">
-        <v>1.12656700611115</v>
+        <v>1.12656712532043</v>
       </c>
       <c r="H520" t="n">
         <v>14000</v>
@@ -15478,7 +15478,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G521" t="n">
-        <v>1.12656700611115</v>
+        <v>1.12656712532043</v>
       </c>
       <c r="H521" t="n">
         <v>12400</v>
@@ -15507,7 +15507,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G522" t="n">
-        <v>1.12656700611115</v>
+        <v>1.12656712532043</v>
       </c>
       <c r="H522" t="n">
         <v>8800</v>
@@ -15536,7 +15536,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G523" t="n">
-        <v>1.15160191059113</v>
+        <v>1.15160179138184</v>
       </c>
       <c r="H523" t="n">
         <v>36800</v>
@@ -15565,7 +15565,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G524" t="n">
-        <v>1.13491213321686</v>
+        <v>1.13491201400757</v>
       </c>
       <c r="H524" t="n">
         <v>34800</v>
@@ -15623,7 +15623,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G526" t="n">
-        <v>1.12656700611115</v>
+        <v>1.12656712532043</v>
       </c>
       <c r="H526" t="n">
         <v>42000</v>
@@ -15768,7 +15768,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G531" t="n">
-        <v>1.11822211742401</v>
+        <v>1.1182222366333</v>
       </c>
       <c r="H531" t="n">
         <v>2800</v>
@@ -15797,7 +15797,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G532" t="n">
-        <v>1.10153245925903</v>
+        <v>1.10153222084045</v>
       </c>
       <c r="H532" t="n">
         <v>15200</v>
@@ -15855,7 +15855,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G534" t="n">
-        <v>1.07649731636047</v>
+        <v>1.07649743556976</v>
       </c>
       <c r="H534" t="n">
         <v>32000</v>
@@ -15884,7 +15884,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>1.07649731636047</v>
+        <v>1.07649743556976</v>
       </c>
       <c r="H535" t="n">
         <v>4000</v>
@@ -15913,7 +15913,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G536" t="n">
-        <v>1.0598076581955</v>
+        <v>1.05980753898621</v>
       </c>
       <c r="H536" t="n">
         <v>30400</v>
@@ -15942,7 +15942,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G537" t="n">
-        <v>0.997220516204834</v>
+        <v>0.997220575809479</v>
       </c>
       <c r="H537" t="n">
         <v>70800</v>
@@ -16116,7 +16116,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G543" t="n">
-        <v>0.947150826454163</v>
+        <v>0.947150886058807</v>
       </c>
       <c r="H543" t="n">
         <v>27200</v>
@@ -16145,7 +16145,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G544" t="n">
-        <v>0.951323330402374</v>
+        <v>0.951323390007019</v>
       </c>
       <c r="H544" t="n">
         <v>21600</v>
@@ -16174,7 +16174,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G545" t="n">
-        <v>0.934633433818817</v>
+        <v>0.934633374214172</v>
       </c>
       <c r="H545" t="n">
         <v>107200</v>
@@ -16203,7 +16203,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G546" t="n">
-        <v>0.926288425922394</v>
+        <v>0.926288485527039</v>
       </c>
       <c r="H546" t="n">
         <v>20800</v>
@@ -16232,7 +16232,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G547" t="n">
-        <v>0.934633433818817</v>
+        <v>0.934633374214172</v>
       </c>
       <c r="H547" t="n">
         <v>5600</v>
@@ -16261,7 +16261,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G548" t="n">
-        <v>0.934633433818817</v>
+        <v>0.934633374214172</v>
       </c>
       <c r="H548" t="n">
         <v>3200</v>
@@ -16348,7 +16348,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G551" t="n">
-        <v>0.947150826454163</v>
+        <v>0.947150886058807</v>
       </c>
       <c r="H551" t="n">
         <v>61600</v>
@@ -16377,7 +16377,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G552" t="n">
-        <v>0.934633433818817</v>
+        <v>0.934633374214172</v>
       </c>
       <c r="H552" t="n">
         <v>15600</v>
@@ -16464,7 +16464,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G555" t="n">
-        <v>0.926288425922394</v>
+        <v>0.926288485527039</v>
       </c>
       <c r="H555" t="n">
         <v>32800</v>
@@ -16493,7 +16493,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G556" t="n">
-        <v>0.922116160392761</v>
+        <v>0.922116041183472</v>
       </c>
       <c r="H556" t="n">
         <v>47200</v>
@@ -16551,7 +16551,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G558" t="n">
-        <v>0.922116160392761</v>
+        <v>0.922116041183472</v>
       </c>
       <c r="H558" t="n">
         <v>7600</v>
@@ -16609,7 +16609,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>0.922116160392761</v>
+        <v>0.922116041183472</v>
       </c>
       <c r="H560" t="n">
         <v>1600</v>
@@ -16667,7 +16667,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G562" t="n">
-        <v>0.94297844171524</v>
+        <v>0.942978382110596</v>
       </c>
       <c r="H562" t="n">
         <v>11200</v>
@@ -16725,7 +16725,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G564" t="n">
-        <v>0.934633433818817</v>
+        <v>0.934633374214172</v>
       </c>
       <c r="H564" t="n">
         <v>2400</v>
@@ -16783,7 +16783,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G566" t="n">
-        <v>0.951323330402374</v>
+        <v>0.951323390007019</v>
       </c>
       <c r="H566" t="n">
         <v>33200</v>
@@ -16812,7 +16812,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G567" t="n">
-        <v>0.955495774745941</v>
+        <v>0.955495834350586</v>
       </c>
       <c r="H567" t="n">
         <v>5200</v>
@@ -16841,7 +16841,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G568" t="n">
-        <v>0.951323330402374</v>
+        <v>0.951323390007019</v>
       </c>
       <c r="H568" t="n">
         <v>2800</v>
@@ -16928,7 +16928,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G571" t="n">
-        <v>1.03060030937195</v>
+        <v>1.03060019016266</v>
       </c>
       <c r="H571" t="n">
         <v>4000</v>
@@ -16957,7 +16957,7 @@
         <v>1.25</v>
       </c>
       <c r="G572" t="n">
-        <v>1.04311776161194</v>
+        <v>1.04311764240265</v>
       </c>
       <c r="H572" t="n">
         <v>18800</v>
@@ -16986,7 +16986,7 @@
         <v>1.25</v>
       </c>
       <c r="G573" t="n">
-        <v>1.04311776161194</v>
+        <v>1.04311764240265</v>
       </c>
       <c r="H573" t="n">
         <v>13600</v>
@@ -17015,7 +17015,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.06397986412048</v>
+        <v>1.06398010253906</v>
       </c>
       <c r="H574" t="n">
         <v>18800</v>
@@ -17247,7 +17247,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>1.0598076581955</v>
+        <v>1.05980753898621</v>
       </c>
       <c r="H582" t="n">
         <v>129600</v>
@@ -17305,7 +17305,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G584" t="n">
-        <v>1.13491213321686</v>
+        <v>1.13491201400757</v>
       </c>
       <c r="H584" t="n">
         <v>77200</v>
@@ -17392,7 +17392,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>1.19749903678894</v>
+        <v>1.19749915599823</v>
       </c>
       <c r="H587" t="n">
         <v>127600</v>
@@ -17450,7 +17450,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G589" t="n">
-        <v>1.21001660823822</v>
+        <v>1.21001648902893</v>
       </c>
       <c r="H589" t="n">
         <v>34400</v>
@@ -17479,7 +17479,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G590" t="n">
-        <v>1.19332671165466</v>
+        <v>1.19332659244537</v>
       </c>
       <c r="H590" t="n">
         <v>18400</v>
@@ -17537,7 +17537,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G592" t="n">
-        <v>1.17663669586182</v>
+        <v>1.17663681507111</v>
       </c>
       <c r="H592" t="n">
         <v>2800</v>
@@ -17566,7 +17566,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G593" t="n">
-        <v>1.19332671165466</v>
+        <v>1.19332659244537</v>
       </c>
       <c r="H593" t="n">
         <v>14800</v>
@@ -17653,7 +17653,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>1.28512096405029</v>
+        <v>1.28512108325958</v>
       </c>
       <c r="H596" t="n">
         <v>419200</v>
@@ -17711,7 +17711,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G598" t="n">
-        <v>1.3354823589325</v>
+        <v>1.33548247814178</v>
       </c>
       <c r="H598" t="n">
         <v>36400</v>
@@ -18030,7 +18030,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G609" t="n">
-        <v>1.24904346466064</v>
+        <v>1.24904358386993</v>
       </c>
       <c r="H609" t="n">
         <v>25200</v>
@@ -18146,7 +18146,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G613" t="n">
-        <v>1.18421423435211</v>
+        <v>1.1842143535614</v>
       </c>
       <c r="H613" t="n">
         <v>29200</v>
@@ -18175,7 +18175,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G614" t="n">
-        <v>1.11938500404358</v>
+        <v>1.11938488483429</v>
       </c>
       <c r="H614" t="n">
         <v>28800</v>
@@ -18204,7 +18204,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G615" t="n">
-        <v>1.21014595031738</v>
+        <v>1.21014583110809</v>
       </c>
       <c r="H615" t="n">
         <v>69200</v>
@@ -18291,7 +18291,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G618" t="n">
-        <v>1.33116054534912</v>
+        <v>1.33116042613983</v>
       </c>
       <c r="H618" t="n">
         <v>26000</v>
@@ -18320,7 +18320,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G619" t="n">
-        <v>1.3354823589325</v>
+        <v>1.33548247814178</v>
       </c>
       <c r="H619" t="n">
         <v>46400</v>
@@ -18378,7 +18378,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>1.33116054534912</v>
+        <v>1.33116042613983</v>
       </c>
       <c r="H621" t="n">
         <v>10400</v>
@@ -18552,7 +18552,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G627" t="n">
-        <v>1.3009067773819</v>
+        <v>1.30090689659119</v>
       </c>
       <c r="H627" t="n">
         <v>16400</v>
@@ -18726,7 +18726,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G633" t="n">
-        <v>1.4262433052063</v>
+        <v>1.42624342441559</v>
       </c>
       <c r="H633" t="n">
         <v>158400</v>
@@ -18755,7 +18755,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G634" t="n">
-        <v>1.41327750682831</v>
+        <v>1.4132776260376</v>
       </c>
       <c r="H634" t="n">
         <v>123200</v>
@@ -18784,7 +18784,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G635" t="n">
-        <v>1.40895569324493</v>
+        <v>1.40895557403564</v>
       </c>
       <c r="H635" t="n">
         <v>83600</v>
@@ -18987,7 +18987,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G642" t="n">
-        <v>1.46514105796814</v>
+        <v>1.46514093875885</v>
       </c>
       <c r="H642" t="n">
         <v>54000</v>
@@ -19016,7 +19016,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G643" t="n">
-        <v>1.49971663951874</v>
+        <v>1.49971652030945</v>
       </c>
       <c r="H643" t="n">
         <v>56800</v>
@@ -19132,7 +19132,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G647" t="n">
-        <v>1.41327750682831</v>
+        <v>1.4132776260376</v>
       </c>
       <c r="H647" t="n">
         <v>15200</v>
@@ -19161,7 +19161,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G648" t="n">
-        <v>1.41759955883026</v>
+        <v>1.41759943962097</v>
       </c>
       <c r="H648" t="n">
         <v>37600</v>
@@ -19190,7 +19190,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.45649695396423</v>
+        <v>1.45649707317352</v>
       </c>
       <c r="H649" t="n">
         <v>72000</v>
@@ -19364,7 +19364,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72013604640961</v>
+        <v>1.72013592720032</v>
       </c>
       <c r="H655" t="n">
         <v>149600</v>
@@ -19393,7 +19393,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G656" t="n">
-        <v>1.81521892547607</v>
+        <v>1.81521880626678</v>
       </c>
       <c r="H656" t="n">
         <v>71200</v>
@@ -19422,7 +19422,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G657" t="n">
-        <v>1.98809695243835</v>
+        <v>1.98809683322906</v>
       </c>
       <c r="H657" t="n">
         <v>588000</v>
@@ -19509,7 +19509,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G660" t="n">
-        <v>1.9016580581665</v>
+        <v>1.90165793895721</v>
       </c>
       <c r="H660" t="n">
         <v>41600</v>
@@ -19567,7 +19567,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G662" t="n">
-        <v>1.9016580581665</v>
+        <v>1.90165793895721</v>
       </c>
       <c r="H662" t="n">
         <v>45200</v>
@@ -19596,7 +19596,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G663" t="n">
-        <v>1.91894555091858</v>
+        <v>1.91894578933716</v>
       </c>
       <c r="H663" t="n">
         <v>15600</v>
@@ -19625,7 +19625,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G664" t="n">
-        <v>1.9016580581665</v>
+        <v>1.90165793895721</v>
       </c>
       <c r="H664" t="n">
         <v>21200</v>
@@ -19654,7 +19654,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>1.91030204296112</v>
+        <v>1.91030168533325</v>
       </c>
       <c r="H665" t="n">
         <v>1600</v>
@@ -19683,7 +19683,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G666" t="n">
-        <v>1.91894555091858</v>
+        <v>1.91894578933716</v>
       </c>
       <c r="H666" t="n">
         <v>10400</v>
@@ -19741,7 +19741,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G668" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945308685303</v>
       </c>
       <c r="H668" t="n">
         <v>50400</v>
@@ -19770,7 +19770,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G669" t="n">
-        <v>1.98809695243835</v>
+        <v>1.98809683322906</v>
       </c>
       <c r="H669" t="n">
         <v>24800</v>
@@ -19799,7 +19799,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.98809695243835</v>
+        <v>1.98809683322906</v>
       </c>
       <c r="H670" t="n">
         <v>18400</v>
@@ -19886,7 +19886,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G673" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945308685303</v>
       </c>
       <c r="H673" t="n">
         <v>17200</v>
@@ -19973,7 +19973,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945308685303</v>
       </c>
       <c r="H676" t="n">
         <v>10000</v>
@@ -20002,7 +20002,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>1.91894555091858</v>
+        <v>1.91894578933716</v>
       </c>
       <c r="H677" t="n">
         <v>38000</v>
@@ -20031,7 +20031,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G678" t="n">
-        <v>1.93623340129852</v>
+        <v>1.93623352050781</v>
       </c>
       <c r="H678" t="n">
         <v>6400</v>
@@ -20060,7 +20060,7 @@
         <v>2.25</v>
       </c>
       <c r="G679" t="n">
-        <v>1.94487738609314</v>
+        <v>1.94487750530243</v>
       </c>
       <c r="H679" t="n">
         <v>400</v>
@@ -20089,7 +20089,7 @@
         <v>2.25</v>
       </c>
       <c r="G680" t="n">
-        <v>1.94487738609314</v>
+        <v>1.94487750530243</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G681" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945308685303</v>
       </c>
       <c r="H681" t="n">
         <v>18000</v>
@@ -20147,7 +20147,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G682" t="n">
-        <v>1.98809695243835</v>
+        <v>1.98809683322906</v>
       </c>
       <c r="H682" t="n">
         <v>10000</v>
@@ -20176,7 +20176,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>1.97945296764374</v>
+        <v>1.97945308685303</v>
       </c>
       <c r="H683" t="n">
         <v>16000</v>
@@ -20205,7 +20205,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>1.99674069881439</v>
+        <v>1.9967405796051</v>
       </c>
       <c r="H684" t="n">
         <v>23600</v>
@@ -20263,7 +20263,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G686" t="n">
-        <v>2.11775541305542</v>
+        <v>2.117755651474</v>
       </c>
       <c r="H686" t="n">
         <v>130800</v>
@@ -20350,7 +20350,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>2.23012590408325</v>
+        <v>2.23012614250183</v>
       </c>
       <c r="H689" t="n">
         <v>28400</v>
@@ -20379,7 +20379,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G690" t="n">
-        <v>2.26470184326172</v>
+        <v>2.26470160484314</v>
       </c>
       <c r="H690" t="n">
         <v>39200</v>
@@ -20408,7 +20408,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G691" t="n">
-        <v>2.40300393104553</v>
+        <v>2.40300416946411</v>
       </c>
       <c r="H691" t="n">
         <v>131200</v>
@@ -20524,7 +20524,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G695" t="n">
-        <v>2.42029190063477</v>
+        <v>2.42029166221619</v>
       </c>
       <c r="H695" t="n">
         <v>59200</v>
@@ -20582,7 +20582,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>2.5067310333252</v>
+        <v>2.50673079490662</v>
       </c>
       <c r="H697" t="n">
         <v>142400</v>
@@ -20611,7 +20611,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G698" t="n">
-        <v>2.42029190063477</v>
+        <v>2.42029166221619</v>
       </c>
       <c r="H698" t="n">
         <v>497600</v>
@@ -20640,7 +20640,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>2.42029190063477</v>
+        <v>2.42029166221619</v>
       </c>
       <c r="H699" t="n">
         <v>70400</v>
@@ -20814,7 +20814,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>2.29063320159912</v>
+        <v>2.29063367843628</v>
       </c>
       <c r="H705" t="n">
         <v>46800</v>
@@ -20959,7 +20959,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G710" t="n">
-        <v>2.26470184326172</v>
+        <v>2.26470160484314</v>
       </c>
       <c r="H710" t="n">
         <v>29600</v>
@@ -21104,7 +21104,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G715" t="n">
-        <v>2.51537466049194</v>
+        <v>2.51537489891052</v>
       </c>
       <c r="H715" t="n">
         <v>298000</v>
@@ -21191,7 +21191,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G718" t="n">
-        <v>2.54995059967041</v>
+        <v>2.54995036125183</v>
       </c>
       <c r="H718" t="n">
         <v>42400</v>
@@ -21220,7 +21220,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G719" t="n">
-        <v>2.52401876449585</v>
+        <v>2.52401852607727</v>
       </c>
       <c r="H719" t="n">
         <v>26400</v>
@@ -21365,7 +21365,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>2.99078917503357</v>
+        <v>2.99078941345215</v>
       </c>
       <c r="H724" t="n">
         <v>239200</v>
@@ -21423,7 +21423,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G726" t="n">
-        <v>3.13773536682129</v>
+        <v>3.13773560523987</v>
       </c>
       <c r="H726" t="n">
         <v>204400</v>
@@ -21481,7 +21481,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G728" t="n">
-        <v>3.05129647254944</v>
+        <v>3.05129671096802</v>
       </c>
       <c r="H728" t="n">
         <v>77200</v>
@@ -21539,7 +21539,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>3.17231130599976</v>
+        <v>3.17231106758118</v>
       </c>
       <c r="H730" t="n">
         <v>191600</v>
@@ -21655,7 +21655,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G734" t="n">
-        <v>3.1809549331665</v>
+        <v>3.18095517158508</v>
       </c>
       <c r="H734" t="n">
         <v>10000</v>
@@ -21713,7 +21713,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>3.12909173965454</v>
+        <v>3.12909150123596</v>
       </c>
       <c r="H736" t="n">
         <v>30800</v>
@@ -21829,7 +21829,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G740" t="n">
-        <v>3.12909173965454</v>
+        <v>3.12909150123596</v>
       </c>
       <c r="H740" t="n">
         <v>38800</v>
@@ -21858,7 +21858,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G741" t="n">
-        <v>3.13773536682129</v>
+        <v>3.13773560523987</v>
       </c>
       <c r="H741" t="n">
         <v>12000</v>
@@ -21887,7 +21887,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G742" t="n">
-        <v>3.17231130599976</v>
+        <v>3.17231106758118</v>
       </c>
       <c r="H742" t="n">
         <v>45600</v>
@@ -22032,7 +22032,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G747" t="n">
-        <v>2.7833354473114</v>
+        <v>2.78333568572998</v>
       </c>
       <c r="H747" t="n">
         <v>56800</v>
@@ -22177,7 +22177,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G752" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H752" t="n">
         <v>13600</v>
@@ -22235,7 +22235,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G754" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H754" t="n">
         <v>5200</v>
@@ -22264,7 +22264,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G755" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H755" t="n">
         <v>3200</v>
@@ -22293,7 +22293,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G756" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H756" t="n">
         <v>4800</v>
@@ -22409,7 +22409,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G760" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H760" t="n">
         <v>24000</v>
@@ -22496,7 +22496,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G763" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H763" t="n">
         <v>53600</v>
@@ -22525,7 +22525,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G764" t="n">
-        <v>2.67096471786499</v>
+        <v>2.67096495628357</v>
       </c>
       <c r="H764" t="n">
         <v>14000</v>
@@ -22554,7 +22554,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G765" t="n">
-        <v>2.60181355476379</v>
+        <v>2.60181379318237</v>
       </c>
       <c r="H765" t="n">
         <v>39600</v>
@@ -22612,7 +22612,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G767" t="n">
-        <v>2.47215533256531</v>
+        <v>2.47215509414673</v>
       </c>
       <c r="H767" t="n">
         <v>44400</v>
@@ -22670,7 +22670,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>2.52401876449585</v>
+        <v>2.52401852607727</v>
       </c>
       <c r="H769" t="n">
         <v>4800</v>
@@ -22757,7 +22757,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>2.61910152435303</v>
+        <v>2.61910128593445</v>
       </c>
       <c r="H772" t="n">
         <v>5600</v>
@@ -22902,7 +22902,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G777" t="n">
-        <v>2.8524866104126</v>
+        <v>2.85248684883118</v>
       </c>
       <c r="H777" t="n">
         <v>69600</v>
@@ -22931,7 +22931,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G778" t="n">
-        <v>2.8524866104126</v>
+        <v>2.85248684883118</v>
       </c>
       <c r="H778" t="n">
         <v>10400</v>
@@ -22960,7 +22960,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>2.91299390792847</v>
+        <v>2.91299414634705</v>
       </c>
       <c r="H779" t="n">
         <v>18800</v>
@@ -23018,7 +23018,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G781" t="n">
-        <v>2.93028211593628</v>
+        <v>2.9302818775177</v>
       </c>
       <c r="H781" t="n">
         <v>134400</v>
@@ -23047,7 +23047,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G782" t="n">
-        <v>2.8524866104126</v>
+        <v>2.85248684883118</v>
       </c>
       <c r="H782" t="n">
         <v>8400</v>
@@ -23076,7 +23076,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>2.87841844558716</v>
+        <v>2.87841868400574</v>
       </c>
       <c r="H783" t="n">
         <v>1200</v>
@@ -23134,7 +23134,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G785" t="n">
-        <v>2.83519911766052</v>
+        <v>2.83519887924194</v>
       </c>
       <c r="H785" t="n">
         <v>28800</v>
@@ -23221,7 +23221,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G788" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H788" t="n">
         <v>2800</v>
@@ -23337,7 +23337,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G792" t="n">
-        <v>2.7833354473114</v>
+        <v>2.78333568572998</v>
       </c>
       <c r="H792" t="n">
         <v>12400</v>
@@ -23395,7 +23395,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G794" t="n">
-        <v>2.84384322166443</v>
+        <v>2.84384298324585</v>
       </c>
       <c r="H794" t="n">
         <v>10400</v>
@@ -23424,7 +23424,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G795" t="n">
-        <v>2.76604771614075</v>
+        <v>2.76604795455933</v>
       </c>
       <c r="H795" t="n">
         <v>23600</v>
@@ -23569,7 +23569,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G800" t="n">
-        <v>2.51537466049194</v>
+        <v>2.51537489891052</v>
       </c>
       <c r="H800" t="n">
         <v>28800</v>
@@ -23598,7 +23598,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>2.51537466049194</v>
+        <v>2.51537489891052</v>
       </c>
       <c r="H801" t="n">
         <v>12800</v>
@@ -23627,7 +23627,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>2.51537466049194</v>
+        <v>2.51537489891052</v>
       </c>
       <c r="H802" t="n">
         <v>119200</v>
@@ -23656,7 +23656,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G803" t="n">
-        <v>2.48079895973206</v>
+        <v>2.48079919815063</v>
       </c>
       <c r="H803" t="n">
         <v>10000</v>
@@ -23685,7 +23685,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G804" t="n">
-        <v>2.52401876449585</v>
+        <v>2.52401852607727</v>
       </c>
       <c r="H804" t="n">
         <v>136800</v>
@@ -23830,7 +23830,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>2.42029190063477</v>
+        <v>2.42029166221619</v>
       </c>
       <c r="H809" t="n">
         <v>7200</v>
@@ -23859,7 +23859,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G810" t="n">
-        <v>2.40300393104553</v>
+        <v>2.40300416946411</v>
       </c>
       <c r="H810" t="n">
         <v>3600</v>
@@ -24120,7 +24120,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G819" t="n">
-        <v>2.54995059967041</v>
+        <v>2.54995036125183</v>
       </c>
       <c r="H819" t="n">
         <v>40400</v>
@@ -24178,7 +24178,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G821" t="n">
-        <v>2.83519911766052</v>
+        <v>2.83519887924194</v>
       </c>
       <c r="H821" t="n">
         <v>121200</v>
@@ -24207,7 +24207,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G822" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H822" t="n">
         <v>44800</v>
@@ -24294,7 +24294,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G825" t="n">
-        <v>2.61910152435303</v>
+        <v>2.61910128593445</v>
       </c>
       <c r="H825" t="n">
         <v>10000</v>
@@ -24410,7 +24410,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G829" t="n">
-        <v>2.69689655303955</v>
+        <v>2.69689631462097</v>
       </c>
       <c r="H829" t="n">
         <v>4800</v>
@@ -24584,7 +24584,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G835" t="n">
-        <v>2.73147249221802</v>
+        <v>2.73147225379944</v>
       </c>
       <c r="H835" t="n">
         <v>1600</v>
@@ -24671,7 +24671,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.66232109069824</v>
+        <v>2.66232085227966</v>
       </c>
       <c r="H838" t="n">
         <v>12800</v>
@@ -24729,7 +24729,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>2.61910152435303</v>
+        <v>2.61910128593445</v>
       </c>
       <c r="H840" t="n">
         <v>12800</v>
@@ -25019,7 +25019,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G850" t="n">
-        <v>2.61199402809143</v>
+        <v>2.61199426651001</v>
       </c>
       <c r="H850" t="n">
         <v>16800</v>
@@ -25048,7 +25048,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G851" t="n">
-        <v>2.61199402809143</v>
+        <v>2.61199426651001</v>
       </c>
       <c r="H851" t="n">
         <v>0</v>
@@ -25077,7 +25077,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G852" t="n">
-        <v>2.62976288795471</v>
+        <v>2.62976264953613</v>
       </c>
       <c r="H852" t="n">
         <v>1600</v>
@@ -25135,7 +25135,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G854" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H854" t="n">
         <v>30000</v>
@@ -25222,7 +25222,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G857" t="n">
-        <v>2.48761343955994</v>
+        <v>2.48761320114136</v>
       </c>
       <c r="H857" t="n">
         <v>3600</v>
@@ -25251,7 +25251,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H858" t="n">
         <v>6800</v>
@@ -25309,7 +25309,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G860" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H860" t="n">
         <v>4000</v>
@@ -25338,7 +25338,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G861" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H861" t="n">
         <v>0</v>
@@ -25425,7 +25425,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.48761343955994</v>
+        <v>2.48761320114136</v>
       </c>
       <c r="H864" t="n">
         <v>1200</v>
@@ -25570,7 +25570,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H869" t="n">
         <v>2400</v>
@@ -25599,7 +25599,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G870" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H870" t="n">
         <v>400</v>
@@ -25628,7 +25628,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G871" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -25715,7 +25715,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G874" t="n">
-        <v>2.51426649093628</v>
+        <v>2.5142662525177</v>
       </c>
       <c r="H874" t="n">
         <v>9600</v>
@@ -25860,7 +25860,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G879" t="n">
-        <v>2.5320348739624</v>
+        <v>2.53203511238098</v>
       </c>
       <c r="H879" t="n">
         <v>3200</v>
@@ -25918,7 +25918,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G881" t="n">
-        <v>2.43430733680725</v>
+        <v>2.43430757522583</v>
       </c>
       <c r="H881" t="n">
         <v>2000</v>
@@ -26034,7 +26034,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G885" t="n">
-        <v>2.61199402809143</v>
+        <v>2.61199426651001</v>
       </c>
       <c r="H885" t="n">
         <v>16800</v>
@@ -26092,7 +26092,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>2.64753127098083</v>
+        <v>2.64753150939941</v>
       </c>
       <c r="H887" t="n">
         <v>7600</v>
@@ -26179,7 +26179,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G890" t="n">
-        <v>2.72749018669128</v>
+        <v>2.72749042510986</v>
       </c>
       <c r="H890" t="n">
         <v>7200</v>
@@ -26440,7 +26440,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>2.7186062335968</v>
+        <v>2.71860599517822</v>
       </c>
       <c r="H899" t="n">
         <v>3600</v>
@@ -26469,7 +26469,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G900" t="n">
-        <v>2.7186062335968</v>
+        <v>2.71860599517822</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -26585,7 +26585,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G904" t="n">
-        <v>2.51426649093628</v>
+        <v>2.5142662525177</v>
       </c>
       <c r="H904" t="n">
         <v>13600</v>
@@ -26614,7 +26614,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G905" t="n">
-        <v>2.48761343955994</v>
+        <v>2.48761320114136</v>
       </c>
       <c r="H905" t="n">
         <v>11600</v>
@@ -26643,7 +26643,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G906" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H906" t="n">
         <v>6000</v>
@@ -26672,7 +26672,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -26701,7 +26701,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G908" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H908" t="n">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G909" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H909" t="n">
         <v>400</v>
@@ -26759,7 +26759,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G910" t="n">
-        <v>2.51426649093628</v>
+        <v>2.5142662525177</v>
       </c>
       <c r="H910" t="n">
         <v>400</v>
@@ -26788,7 +26788,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>2.51426649093628</v>
+        <v>2.5142662525177</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -26904,7 +26904,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G915" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H915" t="n">
         <v>6400</v>
@@ -26933,7 +26933,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G916" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -27020,7 +27020,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>2.34546422958374</v>
+        <v>2.34546399116516</v>
       </c>
       <c r="H919" t="n">
         <v>7200</v>
@@ -27049,7 +27049,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G920" t="n">
-        <v>2.37211728096008</v>
+        <v>2.3721170425415</v>
       </c>
       <c r="H920" t="n">
         <v>14000</v>
@@ -27078,7 +27078,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G921" t="n">
-        <v>2.37211728096008</v>
+        <v>2.3721170425415</v>
       </c>
       <c r="H921" t="n">
         <v>800</v>
@@ -27107,7 +27107,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G922" t="n">
-        <v>2.37211728096008</v>
+        <v>2.3721170425415</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G927" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H927" t="n">
         <v>400</v>
@@ -27281,7 +27281,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G928" t="n">
-        <v>2.59422564506531</v>
+        <v>2.59422540664673</v>
       </c>
       <c r="H928" t="n">
         <v>26400</v>
@@ -27310,7 +27310,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G929" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H929" t="n">
         <v>23600</v>
@@ -27339,7 +27339,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G930" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H930" t="n">
         <v>17600</v>
@@ -27368,7 +27368,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G931" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H931" t="n">
         <v>2800</v>
@@ -27397,7 +27397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G932" t="n">
-        <v>2.48761343955994</v>
+        <v>2.48761320114136</v>
       </c>
       <c r="H932" t="n">
         <v>1600</v>
@@ -27426,7 +27426,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>2.48761343955994</v>
+        <v>2.48761320114136</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -27455,7 +27455,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>2.48761343955994</v>
+        <v>2.48761320114136</v>
       </c>
       <c r="H934" t="n">
         <v>4400</v>
@@ -27513,7 +27513,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G936" t="n">
-        <v>2.45207619667053</v>
+        <v>2.45207595825195</v>
       </c>
       <c r="H936" t="n">
         <v>1200</v>
@@ -27600,7 +27600,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G939" t="n">
-        <v>2.5320348739624</v>
+        <v>2.53203511238098</v>
       </c>
       <c r="H939" t="n">
         <v>40800</v>
@@ -27745,7 +27745,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G944" t="n">
-        <v>2.61199402809143</v>
+        <v>2.61199426651001</v>
       </c>
       <c r="H944" t="n">
         <v>4800</v>
@@ -27774,7 +27774,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G945" t="n">
-        <v>2.59422564506531</v>
+        <v>2.59422540664673</v>
       </c>
       <c r="H945" t="n">
         <v>4800</v>
@@ -27890,7 +27890,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G949" t="n">
-        <v>2.496497631073</v>
+        <v>2.49649786949158</v>
       </c>
       <c r="H949" t="n">
         <v>10800</v>
@@ -27919,7 +27919,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G950" t="n">
-        <v>2.51426649093628</v>
+        <v>2.5142662525177</v>
       </c>
       <c r="H950" t="n">
         <v>19200</v>
@@ -27977,7 +27977,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G952" t="n">
-        <v>2.48761343955994</v>
+        <v>2.48761320114136</v>
       </c>
       <c r="H952" t="n">
         <v>25600</v>
@@ -28006,7 +28006,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G953" t="n">
-        <v>2.51426649093628</v>
+        <v>2.5142662525177</v>
       </c>
       <c r="H953" t="n">
         <v>8800</v>
@@ -28064,7 +28064,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G955" t="n">
-        <v>2.51426649093628</v>
+        <v>2.5142662525177</v>
       </c>
       <c r="H955" t="n">
         <v>6400</v>
@@ -28847,7 +28847,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>2.30992674827576</v>
+        <v>2.30992650985718</v>
       </c>
       <c r="H982" t="n">
         <v>2000</v>
@@ -28876,7 +28876,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G983" t="n">
-        <v>2.31881093978882</v>
+        <v>2.3188111782074</v>
       </c>
       <c r="H983" t="n">
         <v>800</v>
@@ -29021,7 +29021,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G988" t="n">
-        <v>2.31881093978882</v>
+        <v>2.3188111782074</v>
       </c>
       <c r="H988" t="n">
         <v>4400</v>
@@ -29311,7 +29311,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>2.18554592132568</v>
+        <v>2.18554615974426</v>
       </c>
       <c r="H998" t="n">
         <v>10400</v>
@@ -29340,7 +29340,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>2.18554592132568</v>
+        <v>2.18554615974426</v>
       </c>
       <c r="H999" t="n">
         <v>1600</v>
@@ -29398,7 +29398,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.18554592132568</v>
+        <v>2.18554615974426</v>
       </c>
       <c r="H1001" t="n">
         <v>4000</v>
@@ -29514,7 +29514,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.13224029541016</v>
+        <v>2.13224005699158</v>
       </c>
       <c r="H1005" t="n">
         <v>7600</v>
@@ -29543,7 +29543,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.15000867843628</v>
+        <v>2.15000891685486</v>
       </c>
       <c r="H1006" t="n">
         <v>6000</v>
@@ -29572,7 +29572,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.13224029541016</v>
+        <v>2.13224005699158</v>
       </c>
       <c r="H1007" t="n">
         <v>6800</v>
@@ -29862,7 +29862,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.15000867843628</v>
+        <v>2.15000891685486</v>
       </c>
       <c r="H1017" t="n">
         <v>7600</v>
@@ -29949,7 +29949,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.15000867843628</v>
+        <v>2.15000891685486</v>
       </c>
       <c r="H1020" t="n">
         <v>7200</v>
@@ -30007,7 +30007,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.15000867843628</v>
+        <v>2.15000891685486</v>
       </c>
       <c r="H1022" t="n">
         <v>16800</v>
@@ -30036,7 +30036,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.13224029541016</v>
+        <v>2.13224005699158</v>
       </c>
       <c r="H1023" t="n">
         <v>1600</v>
@@ -30094,7 +30094,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.11447143554688</v>
+        <v>2.11447167396545</v>
       </c>
       <c r="H1025" t="n">
         <v>1600</v>
@@ -30123,7 +30123,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.11447143554688</v>
+        <v>2.11447167396545</v>
       </c>
       <c r="H1026" t="n">
         <v>9600</v>
@@ -30181,7 +30181,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.13224029541016</v>
+        <v>2.13224005699158</v>
       </c>
       <c r="H1028" t="n">
         <v>4800</v>
@@ -30210,7 +30210,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.13224029541016</v>
+        <v>2.13224005699158</v>
       </c>
       <c r="H1029" t="n">
         <v>800</v>
@@ -30268,7 +30268,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.16777753829956</v>
+        <v>2.16777729988098</v>
       </c>
       <c r="H1031" t="n">
         <v>3600</v>
@@ -30355,7 +30355,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.15000867843628</v>
+        <v>2.15000891685486</v>
       </c>
       <c r="H1034" t="n">
         <v>8000</v>
@@ -30384,7 +30384,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1035" t="n">
-        <v>2.15000867843628</v>
+        <v>2.15000891685486</v>
       </c>
       <c r="H1035" t="n">
         <v>2400</v>
@@ -30558,7 +30558,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1041" t="n">
-        <v>2.22996759414673</v>
+        <v>2.22996783256531</v>
       </c>
       <c r="H1041" t="n">
         <v>44000</v>
@@ -30616,7 +30616,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.25662088394165</v>
+        <v>2.25662064552307</v>
       </c>
       <c r="H1043" t="n">
         <v>18400</v>
@@ -30732,7 +30732,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1047" t="n">
-        <v>2.3543484210968</v>
+        <v>2.35434865951538</v>
       </c>
       <c r="H1047" t="n">
         <v>6400</v>
@@ -30761,7 +30761,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.43430733680725</v>
+        <v>2.43430757522583</v>
       </c>
       <c r="H1048" t="n">
         <v>12400</v>
@@ -30993,7 +30993,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.11447143554688</v>
+        <v>2.11447167396545</v>
       </c>
       <c r="H1056" t="n">
         <v>8000</v>
@@ -31022,7 +31022,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.15000867843628</v>
+        <v>2.15000891685486</v>
       </c>
       <c r="H1057" t="n">
         <v>24000</v>
@@ -31051,7 +31051,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.15000867843628</v>
+        <v>2.15000891685486</v>
       </c>
       <c r="H1058" t="n">
         <v>5600</v>
@@ -31138,7 +31138,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.16777753829956</v>
+        <v>2.16777729988098</v>
       </c>
       <c r="H1061" t="n">
         <v>2000</v>
@@ -31225,7 +31225,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.83905708789825</v>
+        <v>1.83905696868896</v>
       </c>
       <c r="H1064" t="n">
         <v>8400</v>
@@ -31254,7 +31254,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.83905708789825</v>
+        <v>1.83905696868896</v>
       </c>
       <c r="H1065" t="n">
         <v>1600</v>
@@ -31399,7 +31399,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.63471734523773</v>
+        <v>1.63471746444702</v>
       </c>
       <c r="H1070" t="n">
         <v>1600</v>
@@ -31573,7 +31573,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1076" t="n">
         <v>23600</v>
@@ -31602,7 +31602,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.53698968887329</v>
+        <v>1.53698980808258</v>
       </c>
       <c r="H1077" t="n">
         <v>11200</v>
@@ -31631,7 +31631,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1078" t="n">
         <v>38800</v>
@@ -31718,7 +31718,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.59473776817322</v>
+        <v>1.59473788738251</v>
       </c>
       <c r="H1081" t="n">
         <v>4400</v>
@@ -31747,7 +31747,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.59473776817322</v>
+        <v>1.59473788738251</v>
       </c>
       <c r="H1082" t="n">
         <v>0</v>
@@ -31776,7 +31776,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.59473776817322</v>
+        <v>1.59473788738251</v>
       </c>
       <c r="H1083" t="n">
         <v>0</v>
@@ -31805,7 +31805,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1084" t="n">
         <v>1200</v>
@@ -31921,7 +31921,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.83017265796661</v>
+        <v>1.8301727771759</v>
       </c>
       <c r="H1088" t="n">
         <v>62400</v>
@@ -31950,7 +31950,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.75909805297852</v>
+        <v>1.75909817218781</v>
       </c>
       <c r="H1089" t="n">
         <v>24000</v>
@@ -32095,7 +32095,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1094" t="n">
         <v>7600</v>
@@ -32124,7 +32124,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.60806441307068</v>
+        <v>1.60806429386139</v>
       </c>
       <c r="H1095" t="n">
         <v>5200</v>
@@ -32182,7 +32182,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1097" t="n">
         <v>4000</v>
@@ -32211,7 +32211,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.63471734523773</v>
+        <v>1.63471746444702</v>
       </c>
       <c r="H1098" t="n">
         <v>1200</v>
@@ -32240,7 +32240,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.59473776817322</v>
+        <v>1.59473788738251</v>
       </c>
       <c r="H1099" t="n">
         <v>6000</v>
@@ -32269,7 +32269,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1100" t="n">
         <v>400</v>
@@ -32443,7 +32443,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1106" t="n">
         <v>2800</v>
@@ -32646,7 +32646,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.40816688537598</v>
+        <v>1.40816700458527</v>
       </c>
       <c r="H1113" t="n">
         <v>400</v>
@@ -32704,7 +32704,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.45703077316284</v>
+        <v>1.45703065395355</v>
       </c>
       <c r="H1115" t="n">
         <v>2400</v>
@@ -32762,7 +32762,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1117" t="n">
         <v>8800</v>
@@ -32791,7 +32791,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.50589466094971</v>
+        <v>1.50589454174042</v>
       </c>
       <c r="H1118" t="n">
         <v>6000</v>
@@ -32820,7 +32820,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.50589466094971</v>
+        <v>1.50589454174042</v>
       </c>
       <c r="H1119" t="n">
         <v>3200</v>
@@ -32849,7 +32849,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.50589466094971</v>
+        <v>1.50589454174042</v>
       </c>
       <c r="H1120" t="n">
         <v>1200</v>
@@ -32878,7 +32878,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.50589466094971</v>
+        <v>1.50589454174042</v>
       </c>
       <c r="H1121" t="n">
         <v>3200</v>
@@ -32907,7 +32907,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.50589466094971</v>
+        <v>1.50589454174042</v>
       </c>
       <c r="H1122" t="n">
         <v>6800</v>
@@ -32936,7 +32936,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.60806441307068</v>
+        <v>1.60806429386139</v>
       </c>
       <c r="H1123" t="n">
         <v>8800</v>
@@ -32965,7 +32965,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1124" t="n">
         <v>12800</v>
@@ -33429,7 +33429,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.74132943153381</v>
+        <v>1.7413295507431</v>
       </c>
       <c r="H1140" t="n">
         <v>1600</v>
@@ -33458,7 +33458,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.67469680309296</v>
+        <v>1.67469692230225</v>
       </c>
       <c r="H1141" t="n">
         <v>2000</v>
@@ -33545,7 +33545,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.65692818164825</v>
+        <v>1.65692830085754</v>
       </c>
       <c r="H1144" t="n">
         <v>3200</v>
@@ -33632,7 +33632,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.60806441307068</v>
+        <v>1.60806429386139</v>
       </c>
       <c r="H1147" t="n">
         <v>4000</v>
@@ -33661,7 +33661,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1148" t="n">
         <v>6000</v>
@@ -34067,7 +34067,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.63027536869049</v>
+        <v>1.6302752494812</v>
       </c>
       <c r="H1162" t="n">
         <v>4400</v>
@@ -34096,7 +34096,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1163" t="n">
         <v>3600</v>
@@ -34125,7 +34125,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1164" t="n">
         <v>0</v>
@@ -34154,7 +34154,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1165" t="n">
         <v>0</v>
@@ -34183,7 +34183,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1166" t="n">
         <v>0</v>
@@ -34502,7 +34502,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.50589466094971</v>
+        <v>1.50589454174042</v>
       </c>
       <c r="H1177" t="n">
         <v>1600</v>
@@ -34560,7 +34560,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.47479939460754</v>
+        <v>1.47479927539825</v>
       </c>
       <c r="H1179" t="n">
         <v>2000</v>
@@ -34589,7 +34589,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.47479939460754</v>
+        <v>1.47479927539825</v>
       </c>
       <c r="H1180" t="n">
         <v>5600</v>
@@ -34937,7 +34937,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1192" t="n">
         <v>5200</v>
@@ -34995,7 +34995,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.39928269386292</v>
+        <v>1.39928257465363</v>
       </c>
       <c r="H1194" t="n">
         <v>2000</v>
@@ -35024,7 +35024,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.32376563549042</v>
+        <v>1.32376575469971</v>
       </c>
       <c r="H1195" t="n">
         <v>10400</v>
@@ -35198,7 +35198,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.32376563549042</v>
+        <v>1.32376575469971</v>
       </c>
       <c r="H1201" t="n">
         <v>30000</v>
@@ -35227,7 +35227,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.2660174369812</v>
+        <v>1.26601755619049</v>
       </c>
       <c r="H1202" t="n">
         <v>11200</v>
@@ -35401,7 +35401,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.31488144397736</v>
+        <v>1.31488132476807</v>
       </c>
       <c r="H1208" t="n">
         <v>2000</v>
@@ -35459,7 +35459,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.2660174369812</v>
+        <v>1.26601755619049</v>
       </c>
       <c r="H1210" t="n">
         <v>800</v>
@@ -35604,7 +35604,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1215" t="n">
-        <v>1.1771742105484</v>
+        <v>1.17717432975769</v>
       </c>
       <c r="H1215" t="n">
         <v>9200</v>
@@ -35633,7 +35633,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.18605864048004</v>
+        <v>1.18605852127075</v>
       </c>
       <c r="H1216" t="n">
         <v>3200</v>
@@ -35662,7 +35662,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.18605864048004</v>
+        <v>1.18605852127075</v>
       </c>
       <c r="H1217" t="n">
         <v>0</v>
@@ -35778,7 +35778,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.08388876914978</v>
+        <v>1.08388864994049</v>
       </c>
       <c r="H1221" t="n">
         <v>4000</v>
@@ -35807,7 +35807,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.09277296066284</v>
+        <v>1.09277307987213</v>
       </c>
       <c r="H1222" t="n">
         <v>1200</v>
@@ -35836,7 +35836,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.07500433921814</v>
+        <v>1.07500445842743</v>
       </c>
       <c r="H1223" t="n">
         <v>2000</v>
@@ -35865,7 +35865,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.07500433921814</v>
+        <v>1.07500445842743</v>
       </c>
       <c r="H1224" t="n">
         <v>0</v>
@@ -35923,7 +35923,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.04835140705109</v>
+        <v>1.0483512878418</v>
       </c>
       <c r="H1226" t="n">
         <v>3200</v>
@@ -35952,7 +35952,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.995045304298401</v>
+        <v>0.995045363903046</v>
       </c>
       <c r="H1227" t="n">
         <v>4000</v>
@@ -35981,7 +35981,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.02614057064056</v>
+        <v>1.02614045143127</v>
       </c>
       <c r="H1228" t="n">
         <v>4400</v>
@@ -36010,7 +36010,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.06612014770508</v>
+        <v>1.06612002849579</v>
       </c>
       <c r="H1229" t="n">
         <v>8400</v>
@@ -36039,7 +36039,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.09277296066284</v>
+        <v>1.09277307987213</v>
       </c>
       <c r="H1230" t="n">
         <v>2000</v>
@@ -36068,7 +36068,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.09277296066284</v>
+        <v>1.09277307987213</v>
       </c>
       <c r="H1231" t="n">
         <v>0</v>
@@ -36271,7 +36271,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.21715366840363</v>
+        <v>1.21715378761292</v>
       </c>
       <c r="H1238" t="n">
         <v>400</v>
@@ -36329,7 +36329,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.24380671977997</v>
+        <v>1.24380660057068</v>
       </c>
       <c r="H1240" t="n">
         <v>1200</v>
@@ -36387,7 +36387,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.30599701404572</v>
+        <v>1.305997133255</v>
       </c>
       <c r="H1242" t="n">
         <v>16800</v>
@@ -36416,7 +36416,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.32376563549042</v>
+        <v>1.32376575469971</v>
       </c>
       <c r="H1243" t="n">
         <v>3200</v>
@@ -36503,7 +36503,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.41705131530762</v>
+        <v>1.41705119609833</v>
       </c>
       <c r="H1246" t="n">
         <v>8800</v>
@@ -36532,7 +36532,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1247" t="n">
         <v>2000</v>
@@ -36677,7 +36677,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1252" t="n">
         <v>7200</v>
@@ -36706,7 +36706,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.59029579162598</v>
+        <v>1.59029567241669</v>
       </c>
       <c r="H1253" t="n">
         <v>4400</v>
@@ -36735,7 +36735,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1254" t="n">
         <v>14000</v>
@@ -36764,7 +36764,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1255" t="n">
         <v>7600</v>
@@ -36822,7 +36822,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1257" t="n">
         <v>8000</v>
@@ -36880,7 +36880,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1259" t="n">
         <v>10000</v>
@@ -36909,7 +36909,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.53698968887329</v>
+        <v>1.53698980808258</v>
       </c>
       <c r="H1260" t="n">
         <v>800</v>
@@ -37025,7 +37025,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1264" t="n">
         <v>2000</v>
@@ -37083,7 +37083,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.59029579162598</v>
+        <v>1.59029567241669</v>
       </c>
       <c r="H1266" t="n">
         <v>2000</v>
@@ -37141,7 +37141,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.53698968887329</v>
+        <v>1.53698980808258</v>
       </c>
       <c r="H1268" t="n">
         <v>5200</v>
@@ -37170,7 +37170,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.53698968887329</v>
+        <v>1.53698980808258</v>
       </c>
       <c r="H1269" t="n">
         <v>400</v>
@@ -37199,7 +37199,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.53698968887329</v>
+        <v>1.53698980808258</v>
       </c>
       <c r="H1270" t="n">
         <v>5200</v>
@@ -37315,7 +37315,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1274" t="n">
         <v>61600</v>
@@ -37373,7 +37373,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.59473776817322</v>
+        <v>1.59473788738251</v>
       </c>
       <c r="H1276" t="n">
         <v>64400</v>
@@ -37518,7 +37518,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.45703077316284</v>
+        <v>1.45703065395355</v>
       </c>
       <c r="H1281" t="n">
         <v>8800</v>
@@ -37576,7 +37576,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1283" t="n">
         <v>13600</v>
@@ -38185,7 +38185,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1304" t="n">
         <v>11200</v>
@@ -38446,7 +38446,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1313" t="n">
         <v>2800</v>
@@ -38620,7 +38620,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.53698968887329</v>
+        <v>1.53698980808258</v>
       </c>
       <c r="H1319" t="n">
         <v>16800</v>
@@ -39113,7 +39113,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1336" t="n">
         <v>1200</v>
@@ -39258,7 +39258,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.59029579162598</v>
+        <v>1.59029567241669</v>
       </c>
       <c r="H1341" t="n">
         <v>7200</v>
@@ -39316,7 +39316,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.59029579162598</v>
+        <v>1.59029567241669</v>
       </c>
       <c r="H1343" t="n">
         <v>4800</v>
@@ -39345,7 +39345,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.59029579162598</v>
+        <v>1.59029567241669</v>
       </c>
       <c r="H1344" t="n">
         <v>0</v>
@@ -39548,7 +39548,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1351" t="n">
         <v>10400</v>
@@ -39751,7 +39751,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1358" t="n">
         <v>4400</v>
@@ -39780,7 +39780,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1359" t="n">
         <v>6400</v>
@@ -39867,7 +39867,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.63471734523773</v>
+        <v>1.63471746444702</v>
       </c>
       <c r="H1362" t="n">
         <v>9600</v>
@@ -39896,7 +39896,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1363" t="n">
         <v>5200</v>
@@ -39925,7 +39925,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.61250650882721</v>
+        <v>1.6125066280365</v>
       </c>
       <c r="H1364" t="n">
         <v>0</v>
@@ -40157,7 +40157,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.59473776817322</v>
+        <v>1.59473788738251</v>
       </c>
       <c r="H1372" t="n">
         <v>400</v>
@@ -40186,7 +40186,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.59473776817322</v>
+        <v>1.59473788738251</v>
       </c>
       <c r="H1373" t="n">
         <v>1200</v>
@@ -40215,7 +40215,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.59473776817322</v>
+        <v>1.59473788738251</v>
       </c>
       <c r="H1374" t="n">
         <v>8800</v>
@@ -40273,7 +40273,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.59029579162598</v>
+        <v>1.59029567241669</v>
       </c>
       <c r="H1376" t="n">
         <v>1200</v>
@@ -40389,7 +40389,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1380" t="n">
         <v>20400</v>
@@ -40563,7 +40563,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1386" t="n">
         <v>400</v>
@@ -40592,7 +40592,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1387" t="n">
         <v>0</v>
@@ -40621,7 +40621,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1388" t="n">
         <v>0</v>
@@ -40650,7 +40650,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1389" t="n">
         <v>0</v>
@@ -40679,7 +40679,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1390" t="n">
         <v>2000</v>
@@ -40708,7 +40708,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.47479939460754</v>
+        <v>1.47479927539825</v>
       </c>
       <c r="H1391" t="n">
         <v>800</v>
@@ -40766,7 +40766,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.59029579162598</v>
+        <v>1.59029567241669</v>
       </c>
       <c r="H1393" t="n">
         <v>4000</v>
@@ -41259,7 +41259,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1410" t="n">
         <v>4400</v>
@@ -41317,7 +41317,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1412" t="n">
         <v>800</v>
@@ -41346,7 +41346,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1413" t="n">
         <v>0</v>
@@ -41375,7 +41375,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1414" t="n">
         <v>0</v>
@@ -41404,7 +41404,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1415" t="n">
         <v>2000</v>
@@ -41578,7 +41578,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1421" t="n">
         <v>5600</v>
@@ -41752,7 +41752,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1427" t="n">
         <v>4800</v>
@@ -41810,7 +41810,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1429" t="n">
         <v>800</v>
@@ -41839,7 +41839,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1430" t="n">
         <v>0</v>
@@ -41868,7 +41868,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1431" t="n">
         <v>0</v>
@@ -41897,7 +41897,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1432" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1433" t="n">
         <v>0</v>
@@ -41955,7 +41955,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.36374509334564</v>
+        <v>1.36374521255493</v>
       </c>
       <c r="H1434" t="n">
         <v>800</v>
@@ -42071,7 +42071,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1438" t="n">
         <v>7200</v>
@@ -42100,7 +42100,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.40816688537598</v>
+        <v>1.40816700458527</v>
       </c>
       <c r="H1439" t="n">
         <v>400</v>
@@ -42129,7 +42129,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.40816688537598</v>
+        <v>1.40816700458527</v>
       </c>
       <c r="H1440" t="n">
         <v>0</v>
@@ -42535,7 +42535,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1454" t="n">
         <v>5600</v>
@@ -42622,7 +42622,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.45703077316284</v>
+        <v>1.45703065395355</v>
       </c>
       <c r="H1457" t="n">
         <v>12800</v>
@@ -42825,7 +42825,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1464" t="n">
         <v>25600</v>
@@ -42854,7 +42854,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1465" t="n">
         <v>20800</v>
@@ -42941,7 +42941,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.59029579162598</v>
+        <v>1.59029567241669</v>
       </c>
       <c r="H1468" t="n">
         <v>11600</v>
@@ -42970,7 +42970,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1469" t="n">
         <v>400</v>
@@ -42999,7 +42999,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1470" t="n">
         <v>4000</v>
@@ -43028,7 +43028,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.59917998313904</v>
+        <v>1.59918010234833</v>
       </c>
       <c r="H1471" t="n">
         <v>400</v>
@@ -43115,7 +43115,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.74132943153381</v>
+        <v>1.7413295507431</v>
       </c>
       <c r="H1474" t="n">
         <v>40400</v>
@@ -43144,7 +43144,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.69690763950348</v>
+        <v>1.69690775871277</v>
       </c>
       <c r="H1475" t="n">
         <v>37600</v>
@@ -43318,7 +43318,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.75909805297852</v>
+        <v>1.75909817218781</v>
       </c>
       <c r="H1481" t="n">
         <v>88000</v>
@@ -43550,7 +43550,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.63027536869049</v>
+        <v>1.6302752494812</v>
       </c>
       <c r="H1489" t="n">
         <v>2400</v>
@@ -43579,7 +43579,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.63027536869049</v>
+        <v>1.6302752494812</v>
       </c>
       <c r="H1490" t="n">
         <v>3200</v>
@@ -43608,7 +43608,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.74132943153381</v>
+        <v>1.7413295507431</v>
       </c>
       <c r="H1491" t="n">
         <v>86400</v>
@@ -43724,7 +43724,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.74132943153381</v>
+        <v>1.7413295507431</v>
       </c>
       <c r="H1495" t="n">
         <v>16400</v>
@@ -43840,7 +43840,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.63471734523773</v>
+        <v>1.63471746444702</v>
       </c>
       <c r="H1499" t="n">
         <v>6400</v>
@@ -43956,7 +43956,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.67469680309296</v>
+        <v>1.67469692230225</v>
       </c>
       <c r="H1503" t="n">
         <v>19600</v>
@@ -44072,7 +44072,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.53698968887329</v>
+        <v>1.53698980808258</v>
       </c>
       <c r="H1507" t="n">
         <v>400</v>
@@ -44188,7 +44188,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1511" t="n">
         <v>1200</v>
@@ -44217,7 +44217,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1512" t="n">
         <v>800</v>
@@ -44246,7 +44246,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.54587411880493</v>
+        <v>1.54587399959564</v>
       </c>
       <c r="H1513" t="n">
         <v>0</v>
@@ -44652,7 +44652,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.45703077316284</v>
+        <v>1.45703065395355</v>
       </c>
       <c r="H1527" t="n">
         <v>400</v>
@@ -44710,7 +44710,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.45703077316284</v>
+        <v>1.45703065395355</v>
       </c>
       <c r="H1529" t="n">
         <v>16000</v>
@@ -44739,7 +44739,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.45703077316284</v>
+        <v>1.45703065395355</v>
       </c>
       <c r="H1530" t="n">
         <v>0</v>
@@ -44797,7 +44797,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.47924149036407</v>
+        <v>1.47924160957336</v>
       </c>
       <c r="H1532" t="n">
         <v>5600</v>
@@ -44826,7 +44826,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.47479939460754</v>
+        <v>1.47479927539825</v>
       </c>
       <c r="H1533" t="n">
         <v>2000</v>
@@ -44913,7 +44913,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.42593550682068</v>
+        <v>1.42593562602997</v>
       </c>
       <c r="H1536" t="n">
         <v>6400</v>
@@ -45058,7 +45058,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.39928269386292</v>
+        <v>1.39928257465363</v>
       </c>
       <c r="H1541" t="n">
         <v>38400</v>
@@ -45087,7 +45087,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1542" t="n">
         <v>2400</v>
@@ -45145,7 +45145,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.40816688537598</v>
+        <v>1.40816700458527</v>
       </c>
       <c r="H1544" t="n">
         <v>2400</v>
@@ -45203,7 +45203,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1546" t="n">
         <v>16800</v>
@@ -45232,7 +45232,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1547" t="n">
         <v>0</v>
@@ -45261,7 +45261,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.40816688537598</v>
+        <v>1.40816700458527</v>
       </c>
       <c r="H1548" t="n">
         <v>2800</v>
@@ -45290,7 +45290,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.39928269386292</v>
+        <v>1.39928257465363</v>
       </c>
       <c r="H1549" t="n">
         <v>2000</v>
@@ -45319,7 +45319,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1550" t="n">
         <v>2800</v>
@@ -45348,7 +45348,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.3593031167984</v>
+        <v>1.35930299758911</v>
       </c>
       <c r="H1551" t="n">
         <v>11600</v>
@@ -45377,7 +45377,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.36374509334564</v>
+        <v>1.36374521255493</v>
       </c>
       <c r="H1552" t="n">
         <v>800</v>
@@ -45406,7 +45406,7 @@
         <v>1.5349999666214</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.36374509334564</v>
+        <v>1.36374521255493</v>
       </c>
       <c r="H1553" t="n">
         <v>0</v>
@@ -45580,7 +45580,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1559" t="n">
         <v>5200</v>
@@ -45609,7 +45609,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1560" t="n">
         <v>800</v>
@@ -45638,7 +45638,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1561" t="n">
         <v>0</v>
@@ -45667,7 +45667,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.39928269386292</v>
+        <v>1.39928257465363</v>
       </c>
       <c r="H1562" t="n">
         <v>5200</v>
@@ -45696,7 +45696,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.39928269386292</v>
+        <v>1.39928257465363</v>
       </c>
       <c r="H1563" t="n">
         <v>2800</v>
@@ -45725,7 +45725,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.39928269386292</v>
+        <v>1.39928257465363</v>
       </c>
       <c r="H1564" t="n">
         <v>0</v>
@@ -45812,7 +45812,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.30599701404572</v>
+        <v>1.305997133255</v>
       </c>
       <c r="H1567" t="n">
         <v>6400</v>
@@ -45841,7 +45841,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.31488144397736</v>
+        <v>1.31488132476807</v>
       </c>
       <c r="H1568" t="n">
         <v>1600</v>
@@ -45928,7 +45928,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.24380671977997</v>
+        <v>1.24380660057068</v>
       </c>
       <c r="H1571" t="n">
         <v>10400</v>
@@ -45957,7 +45957,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.31488144397736</v>
+        <v>1.31488132476807</v>
       </c>
       <c r="H1572" t="n">
         <v>12000</v>
@@ -46189,7 +46189,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.30599701404572</v>
+        <v>1.305997133255</v>
       </c>
       <c r="H1580" t="n">
         <v>800</v>
@@ -46218,7 +46218,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.30599701404572</v>
+        <v>1.305997133255</v>
       </c>
       <c r="H1581" t="n">
         <v>0</v>
@@ -46450,7 +46450,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.45703077316284</v>
+        <v>1.45703065395355</v>
       </c>
       <c r="H1589" t="n">
         <v>57600</v>
@@ -46479,7 +46479,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.45703077316284</v>
+        <v>1.45703065395355</v>
       </c>
       <c r="H1590" t="n">
         <v>101600</v>
@@ -46624,7 +46624,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1595" t="n">
         <v>5200</v>
@@ -46653,7 +46653,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1596" t="n">
         <v>0</v>
@@ -46885,7 +46885,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1604" t="n">
         <v>2000</v>
@@ -46943,7 +46943,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.40372478961945</v>
+        <v>1.40372467041016</v>
       </c>
       <c r="H1606" t="n">
         <v>800</v>

--- a/data/NPI.MI.xlsx
+++ b/data/NPI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G2" t="n">
-        <v>1.53830981254578</v>
+        <v>1.53830993175507</v>
       </c>
       <c r="H2" t="n">
         <v>2000</v>
@@ -456,7 +456,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>1.52042269706726</v>
+        <v>1.52042245864868</v>
       </c>
       <c r="H3" t="n">
         <v>2400</v>
@@ -514,7 +514,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G5" t="n">
-        <v>1.43918430805206</v>
+        <v>1.43918442726135</v>
       </c>
       <c r="H5" t="n">
         <v>10800</v>
@@ -572,7 +572,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G7" t="n">
-        <v>1.39968311786652</v>
+        <v>1.3996833562851</v>
       </c>
       <c r="H7" t="n">
         <v>3600</v>
@@ -601,7 +601,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39968311786652</v>
+        <v>1.3996833562851</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G11" t="n">
-        <v>1.39968311786652</v>
+        <v>1.3996833562851</v>
       </c>
       <c r="H11" t="n">
         <v>2400</v>
@@ -717,7 +717,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G12" t="n">
-        <v>1.39968311786652</v>
+        <v>1.3996833562851</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G13" t="n">
-        <v>1.39968311786652</v>
+        <v>1.3996833562851</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G14" t="n">
-        <v>1.33931350708008</v>
+        <v>1.33931362628937</v>
       </c>
       <c r="H14" t="n">
         <v>2800</v>
@@ -804,7 +804,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G15" t="n">
-        <v>1.31919026374817</v>
+        <v>1.31919014453888</v>
       </c>
       <c r="H15" t="n">
         <v>4000</v>
@@ -891,7 +891,7 @@
         <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30428409576416</v>
+        <v>1.30428397655487</v>
       </c>
       <c r="H18" t="n">
         <v>8800</v>
@@ -920,7 +920,7 @@
         <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.30428409576416</v>
+        <v>1.30428397655487</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>1.74399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>1.29981219768524</v>
+        <v>1.29981231689453</v>
       </c>
       <c r="H21" t="n">
         <v>1200</v>
@@ -1007,7 +1007,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G22" t="n">
-        <v>1.27447199821472</v>
+        <v>1.27447187900543</v>
       </c>
       <c r="H22" t="n">
         <v>1200</v>
@@ -1036,7 +1036,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G23" t="n">
-        <v>1.22379100322723</v>
+        <v>1.22379112243652</v>
       </c>
       <c r="H23" t="n">
         <v>5600</v>
@@ -1065,7 +1065,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G24" t="n">
-        <v>1.22379100322723</v>
+        <v>1.22379112243652</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G27" t="n">
-        <v>1.08069276809692</v>
+        <v>1.08069252967834</v>
       </c>
       <c r="H27" t="n">
         <v>3600</v>
@@ -1181,7 +1181,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G28" t="n">
-        <v>0.991255879402161</v>
+        <v>0.99125599861145</v>
       </c>
       <c r="H28" t="n">
         <v>4000</v>
@@ -1210,7 +1210,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G29" t="n">
-        <v>1.02703070640564</v>
+        <v>1.02703046798706</v>
       </c>
       <c r="H29" t="n">
         <v>3600</v>
@@ -1239,7 +1239,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>0.961443603038788</v>
+        <v>0.961443722248077</v>
       </c>
       <c r="H30" t="n">
         <v>2400</v>
@@ -1384,7 +1384,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G35" t="n">
-        <v>1.01510572433472</v>
+        <v>1.01510560512543</v>
       </c>
       <c r="H35" t="n">
         <v>4400</v>
@@ -1471,7 +1471,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G38" t="n">
-        <v>1.02106809616089</v>
+        <v>1.02106821537018</v>
       </c>
       <c r="H38" t="n">
         <v>400</v>
@@ -1500,7 +1500,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G39" t="n">
-        <v>1.02106809616089</v>
+        <v>1.02106821537018</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1529,7 +1529,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G40" t="n">
-        <v>1.02106809616089</v>
+        <v>1.02106821537018</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G41" t="n">
-        <v>1.02106809616089</v>
+        <v>1.02106821537018</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G44" t="n">
-        <v>0.983802914619446</v>
+        <v>0.983802795410156</v>
       </c>
       <c r="H44" t="n">
         <v>7200</v>
@@ -1703,7 +1703,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G46" t="n">
-        <v>0.983802914619446</v>
+        <v>0.983802795410156</v>
       </c>
       <c r="H46" t="n">
         <v>5600</v>
@@ -1790,7 +1790,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G49" t="n">
-        <v>0.994237065315247</v>
+        <v>0.994237124919891</v>
       </c>
       <c r="H49" t="n">
         <v>2400</v>
@@ -1819,7 +1819,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G50" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H50" t="n">
         <v>400</v>
@@ -1848,7 +1848,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G51" t="n">
-        <v>0.953990519046783</v>
+        <v>0.953990638256073</v>
       </c>
       <c r="H51" t="n">
         <v>8400</v>
@@ -1877,7 +1877,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G52" t="n">
-        <v>0.953990519046783</v>
+        <v>0.953990638256073</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G53" t="n">
-        <v>0.961443603038788</v>
+        <v>0.961443722248077</v>
       </c>
       <c r="H53" t="n">
         <v>18800</v>
@@ -1935,7 +1935,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G54" t="n">
-        <v>0.967406213283539</v>
+        <v>0.967406153678894</v>
       </c>
       <c r="H54" t="n">
         <v>7200</v>
@@ -1964,7 +1964,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G55" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H55" t="n">
         <v>800</v>
@@ -1993,7 +1993,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G56" t="n">
-        <v>0.968151390552521</v>
+        <v>0.968151450157166</v>
       </c>
       <c r="H56" t="n">
         <v>1200</v>
@@ -2022,7 +2022,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G57" t="n">
-        <v>0.968151390552521</v>
+        <v>0.968151450157166</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G58" t="n">
-        <v>0.950264155864716</v>
+        <v>0.95026421546936</v>
       </c>
       <c r="H58" t="n">
         <v>400</v>
@@ -2080,7 +2080,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>0.946537613868713</v>
+        <v>0.946537494659424</v>
       </c>
       <c r="H59" t="n">
         <v>400</v>
@@ -2109,7 +2109,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G60" t="n">
-        <v>0.961443603038788</v>
+        <v>0.961443722248077</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G61" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H61" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H62" t="n">
         <v>2400</v>
@@ -2196,7 +2196,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G63" t="n">
-        <v>1.05833327770233</v>
+        <v>1.05833351612091</v>
       </c>
       <c r="H63" t="n">
         <v>28400</v>
@@ -2225,7 +2225,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G64" t="n">
-        <v>1.02703070640564</v>
+        <v>1.02703046798706</v>
       </c>
       <c r="H64" t="n">
         <v>9600</v>
@@ -2254,7 +2254,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G65" t="n">
-        <v>0.991255879402161</v>
+        <v>0.99125599861145</v>
       </c>
       <c r="H65" t="n">
         <v>7200</v>
@@ -2283,7 +2283,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G66" t="n">
-        <v>0.991255879402161</v>
+        <v>0.99125599861145</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H67" t="n">
         <v>6000</v>
@@ -2341,7 +2341,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H68" t="n">
         <v>4800</v>
@@ -2370,7 +2370,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G69" t="n">
-        <v>0.969642162322998</v>
+        <v>0.969642043113708</v>
       </c>
       <c r="H69" t="n">
         <v>6400</v>
@@ -2399,7 +2399,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G70" t="n">
-        <v>0.958462536334991</v>
+        <v>0.958462417125702</v>
       </c>
       <c r="H70" t="n">
         <v>8400</v>
@@ -2428,7 +2428,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G71" t="n">
-        <v>0.961443603038788</v>
+        <v>0.961443722248077</v>
       </c>
       <c r="H71" t="n">
         <v>24800</v>
@@ -2457,7 +2457,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G72" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H72" t="n">
         <v>6000</v>
@@ -2486,7 +2486,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G73" t="n">
-        <v>0.940575182437897</v>
+        <v>0.940575122833252</v>
       </c>
       <c r="H73" t="n">
         <v>2400</v>
@@ -2515,7 +2515,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G74" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H74" t="n">
         <v>8000</v>
@@ -2544,7 +2544,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>0.946537613868713</v>
+        <v>0.946537494659424</v>
       </c>
       <c r="H75" t="n">
         <v>17200</v>
@@ -2573,7 +2573,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G76" t="n">
-        <v>0.932376980781555</v>
+        <v>0.932376861572266</v>
       </c>
       <c r="H76" t="n">
         <v>13200</v>
@@ -2602,7 +2602,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9241783618927</v>
+        <v>0.92417848110199</v>
       </c>
       <c r="H77" t="n">
         <v>4800</v>
@@ -2631,7 +2631,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G78" t="n">
-        <v>0.949519038200378</v>
+        <v>0.949518978595734</v>
       </c>
       <c r="H78" t="n">
         <v>34400</v>
@@ -2660,7 +2660,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G79" t="n">
-        <v>0.968896687030792</v>
+        <v>0.968896746635437</v>
       </c>
       <c r="H79" t="n">
         <v>27200</v>
@@ -2689,7 +2689,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G80" t="n">
-        <v>0.978585720062256</v>
+        <v>0.978585779666901</v>
       </c>
       <c r="H80" t="n">
         <v>15200</v>
@@ -2718,7 +2718,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G81" t="n">
-        <v>0.978585720062256</v>
+        <v>0.978585779666901</v>
       </c>
       <c r="H81" t="n">
         <v>22000</v>
@@ -2747,7 +2747,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G82" t="n">
-        <v>0.943556427955627</v>
+        <v>0.943556368350983</v>
       </c>
       <c r="H82" t="n">
         <v>7200</v>
@@ -2776,7 +2776,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G83" t="n">
-        <v>0.912998914718628</v>
+        <v>0.912998855113983</v>
       </c>
       <c r="H83" t="n">
         <v>15600</v>
@@ -2805,7 +2805,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G84" t="n">
-        <v>0.983802914619446</v>
+        <v>0.983802795410156</v>
       </c>
       <c r="H84" t="n">
         <v>51600</v>
@@ -2863,7 +2863,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G86" t="n">
-        <v>0.985293507575989</v>
+        <v>0.985293567180634</v>
       </c>
       <c r="H86" t="n">
         <v>58000</v>
@@ -2892,7 +2892,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G87" t="n">
-        <v>1.02852118015289</v>
+        <v>1.02852129936218</v>
       </c>
       <c r="H87" t="n">
         <v>6000</v>
@@ -2921,7 +2921,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G88" t="n">
-        <v>1.02852118015289</v>
+        <v>1.02852129936218</v>
       </c>
       <c r="H88" t="n">
         <v>20800</v>
@@ -2950,7 +2950,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G89" t="n">
-        <v>0.991255879402161</v>
+        <v>0.99125599861145</v>
       </c>
       <c r="H89" t="n">
         <v>30000</v>
@@ -3008,7 +3008,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G91" t="n">
-        <v>0.99601411819458</v>
+        <v>0.996013998985291</v>
       </c>
       <c r="H91" t="n">
         <v>8400</v>
@@ -3095,7 +3095,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G94" t="n">
-        <v>1.04438734054565</v>
+        <v>1.04438722133636</v>
       </c>
       <c r="H94" t="n">
         <v>1200</v>
@@ -3269,7 +3269,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G100" t="n">
-        <v>0.990462899208069</v>
+        <v>0.990462779998779</v>
       </c>
       <c r="H100" t="n">
         <v>13200</v>
@@ -3414,7 +3414,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G105" t="n">
-        <v>0.935745596885681</v>
+        <v>0.935745537281036</v>
       </c>
       <c r="H105" t="n">
         <v>4400</v>
@@ -3530,7 +3530,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G109" t="n">
-        <v>0.945261716842651</v>
+        <v>0.945261597633362</v>
       </c>
       <c r="H109" t="n">
         <v>4000</v>
@@ -3559,7 +3559,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G110" t="n">
-        <v>0.945261716842651</v>
+        <v>0.945261597633362</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G114" t="n">
-        <v>0.903232395648956</v>
+        <v>0.903232455253601</v>
       </c>
       <c r="H114" t="n">
         <v>19200</v>
@@ -3704,7 +3704,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G115" t="n">
-        <v>0.904025495052338</v>
+        <v>0.904025435447693</v>
       </c>
       <c r="H115" t="n">
         <v>800</v>
@@ -3791,7 +3791,7 @@
         <v>1.11600005626678</v>
       </c>
       <c r="G118" t="n">
-        <v>0.884993374347687</v>
+        <v>0.884993314743042</v>
       </c>
       <c r="H118" t="n">
         <v>4800</v>
@@ -3820,7 +3820,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G119" t="n">
-        <v>0.915920495986938</v>
+        <v>0.915920436382294</v>
       </c>
       <c r="H119" t="n">
         <v>2000</v>
@@ -3849,7 +3849,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G120" t="n">
-        <v>0.915920495986938</v>
+        <v>0.915920436382294</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G121" t="n">
-        <v>0.915920495986938</v>
+        <v>0.915920436382294</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G122" t="n">
-        <v>0.864375174045563</v>
+        <v>0.864375114440918</v>
       </c>
       <c r="H122" t="n">
         <v>59600</v>
@@ -3965,7 +3965,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G124" t="n">
-        <v>0.824724972248077</v>
+        <v>0.824724912643433</v>
       </c>
       <c r="H124" t="n">
         <v>2800</v>
@@ -4023,7 +4023,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G126" t="n">
-        <v>0.796969830989838</v>
+        <v>0.796969771385193</v>
       </c>
       <c r="H126" t="n">
         <v>42400</v>
@@ -4226,7 +4226,7 @@
         <v>0.925000011920929</v>
       </c>
       <c r="G133" t="n">
-        <v>0.733529388904572</v>
+        <v>0.733529508113861</v>
       </c>
       <c r="H133" t="n">
         <v>800</v>
@@ -4516,7 +4516,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G143" t="n">
-        <v>0.839792013168335</v>
+        <v>0.83979195356369</v>
       </c>
       <c r="H143" t="n">
         <v>90800</v>
@@ -4661,7 +4661,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G148" t="n">
-        <v>0.85168719291687</v>
+        <v>0.851687133312225</v>
       </c>
       <c r="H148" t="n">
         <v>2000</v>
@@ -4690,7 +4690,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>0.840584993362427</v>
+        <v>0.840584933757782</v>
       </c>
       <c r="H149" t="n">
         <v>12400</v>
@@ -4719,7 +4719,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G150" t="n">
-        <v>0.848515093326569</v>
+        <v>0.848515152931213</v>
       </c>
       <c r="H150" t="n">
         <v>400</v>
@@ -4864,7 +4864,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>0.824724972248077</v>
+        <v>0.824724912643433</v>
       </c>
       <c r="H155" t="n">
         <v>5600</v>
@@ -4893,7 +4893,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>0.824724972248077</v>
+        <v>0.824724912643433</v>
       </c>
       <c r="H156" t="n">
         <v>2400</v>
@@ -5009,7 +5009,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G160" t="n">
-        <v>0.779127240180969</v>
+        <v>0.779127180576324</v>
       </c>
       <c r="H160" t="n">
         <v>5200</v>
@@ -5038,7 +5038,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G161" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H161" t="n">
         <v>12400</v>
@@ -5067,7 +5067,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G162" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G167" t="n">
-        <v>0.779127240180969</v>
+        <v>0.779127180576324</v>
       </c>
       <c r="H167" t="n">
         <v>400</v>
@@ -5270,7 +5270,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G169" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H169" t="n">
         <v>2400</v>
@@ -5705,7 +5705,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G184" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H184" t="n">
         <v>31600</v>
@@ -5763,7 +5763,7 @@
         <v>0.904999971389771</v>
       </c>
       <c r="G186" t="n">
-        <v>0.717669308185577</v>
+        <v>0.717669188976288</v>
       </c>
       <c r="H186" t="n">
         <v>10800</v>
@@ -5792,7 +5792,7 @@
         <v>0.967000007629395</v>
       </c>
       <c r="G187" t="n">
-        <v>0.766835629940033</v>
+        <v>0.766835570335388</v>
       </c>
       <c r="H187" t="n">
         <v>41200</v>
@@ -5850,7 +5850,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>0.689914107322693</v>
+        <v>0.689914166927338</v>
       </c>
       <c r="H189" t="n">
         <v>35200</v>
@@ -5879,7 +5879,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G190" t="n">
-        <v>0.689121127128601</v>
+        <v>0.689121067523956</v>
       </c>
       <c r="H190" t="n">
         <v>10000</v>
@@ -5908,7 +5908,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G191" t="n">
-        <v>0.689121127128601</v>
+        <v>0.689121067523956</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G192" t="n">
-        <v>0.681984126567841</v>
+        <v>0.681984066963196</v>
       </c>
       <c r="H192" t="n">
         <v>24800</v>
@@ -5966,7 +5966,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G193" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H193" t="n">
         <v>27600</v>
@@ -5995,7 +5995,7 @@
         <v>0.807500004768372</v>
       </c>
       <c r="G194" t="n">
-        <v>0.640351355075836</v>
+        <v>0.640351414680481</v>
       </c>
       <c r="H194" t="n">
         <v>51200</v>
@@ -6024,7 +6024,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G195" t="n">
-        <v>0.634403884410858</v>
+        <v>0.634403824806213</v>
       </c>
       <c r="H195" t="n">
         <v>15200</v>
@@ -6053,7 +6053,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G196" t="n">
-        <v>0.628852725028992</v>
+        <v>0.628852784633636</v>
       </c>
       <c r="H196" t="n">
         <v>64400</v>
@@ -6111,7 +6111,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G198" t="n">
-        <v>0.607441544532776</v>
+        <v>0.607441604137421</v>
       </c>
       <c r="H198" t="n">
         <v>14400</v>
@@ -6227,7 +6227,7 @@
         <v>0.72299998998642</v>
       </c>
       <c r="G202" t="n">
-        <v>0.573342442512512</v>
+        <v>0.573342382907867</v>
       </c>
       <c r="H202" t="n">
         <v>28400</v>
@@ -6285,7 +6285,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>0.555499792098999</v>
+        <v>0.555499851703644</v>
       </c>
       <c r="H204" t="n">
         <v>38000</v>
@@ -6372,7 +6372,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G207" t="n">
-        <v>0.547173202037811</v>
+        <v>0.547173321247101</v>
       </c>
       <c r="H207" t="n">
         <v>53600</v>
@@ -6401,7 +6401,7 @@
         <v>0.722500026226044</v>
       </c>
       <c r="G208" t="n">
-        <v>0.572946012020111</v>
+        <v>0.572945892810822</v>
       </c>
       <c r="H208" t="n">
         <v>74800</v>
@@ -6488,7 +6488,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G211" t="n">
-        <v>0.559068381786346</v>
+        <v>0.559068322181702</v>
       </c>
       <c r="H211" t="n">
         <v>28000</v>
@@ -6604,7 +6604,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G215" t="n">
-        <v>0.569377422332764</v>
+        <v>0.569377481937408</v>
       </c>
       <c r="H215" t="n">
         <v>22400</v>
@@ -6662,7 +6662,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G217" t="n">
-        <v>0.547173202037811</v>
+        <v>0.547173321247101</v>
       </c>
       <c r="H217" t="n">
         <v>24400</v>
@@ -6720,7 +6720,7 @@
         <v>0.715499997138977</v>
       </c>
       <c r="G219" t="n">
-        <v>0.567394912242889</v>
+        <v>0.567394852638245</v>
       </c>
       <c r="H219" t="n">
         <v>18000</v>
@@ -6778,7 +6778,7 @@
         <v>0.672500014305115</v>
       </c>
       <c r="G221" t="n">
-        <v>0.533295691013336</v>
+        <v>0.533295750617981</v>
       </c>
       <c r="H221" t="n">
         <v>6800</v>
@@ -6807,7 +6807,7 @@
         <v>0.698499977588654</v>
       </c>
       <c r="G222" t="n">
-        <v>0.553913831710815</v>
+        <v>0.553913772106171</v>
       </c>
       <c r="H222" t="n">
         <v>52000</v>
@@ -6865,7 +6865,7 @@
         <v>0.672500014305115</v>
       </c>
       <c r="G224" t="n">
-        <v>0.533295691013336</v>
+        <v>0.533295750617981</v>
       </c>
       <c r="H224" t="n">
         <v>12400</v>
@@ -6894,7 +6894,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G225" t="n">
-        <v>0.52338308095932</v>
+        <v>0.523383140563965</v>
       </c>
       <c r="H225" t="n">
         <v>7600</v>
@@ -6952,7 +6952,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G227" t="n">
-        <v>0.507523059844971</v>
+        <v>0.507523000240326</v>
       </c>
       <c r="H227" t="n">
         <v>52000</v>
@@ -6981,7 +6981,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>0.513867020606995</v>
+        <v>0.513867139816284</v>
       </c>
       <c r="H228" t="n">
         <v>34800</v>
@@ -7097,7 +7097,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G232" t="n">
-        <v>0.559068381786346</v>
+        <v>0.559068322181702</v>
       </c>
       <c r="H232" t="n">
         <v>400</v>
@@ -7155,7 +7155,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G234" t="n">
-        <v>0.531313240528107</v>
+        <v>0.531313180923462</v>
       </c>
       <c r="H234" t="n">
         <v>4800</v>
@@ -7184,7 +7184,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G235" t="n">
-        <v>0.531313240528107</v>
+        <v>0.531313180923462</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>0.521797120571136</v>
+        <v>0.521797060966492</v>
       </c>
       <c r="H239" t="n">
         <v>10000</v>
@@ -7416,7 +7416,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G243" t="n">
-        <v>0.52338308095932</v>
+        <v>0.523383140563965</v>
       </c>
       <c r="H243" t="n">
         <v>8000</v>
@@ -7445,7 +7445,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G244" t="n">
-        <v>0.52338308095932</v>
+        <v>0.523383140563965</v>
       </c>
       <c r="H244" t="n">
         <v>10400</v>
@@ -7474,7 +7474,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G245" t="n">
-        <v>0.52338308095932</v>
+        <v>0.523383140563965</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G246" t="n">
-        <v>0.52338308095932</v>
+        <v>0.523383140563965</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>0.703499972820282</v>
       </c>
       <c r="G249" t="n">
-        <v>0.557878792285919</v>
+        <v>0.557878851890564</v>
       </c>
       <c r="H249" t="n">
         <v>17200</v>
@@ -7619,7 +7619,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G250" t="n">
-        <v>0.551931321620941</v>
+        <v>0.551931262016296</v>
       </c>
       <c r="H250" t="n">
         <v>72000</v>
@@ -7648,7 +7648,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G251" t="n">
-        <v>0.566205382347107</v>
+        <v>0.566205322742462</v>
       </c>
       <c r="H251" t="n">
         <v>59600</v>
@@ -7677,7 +7677,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G252" t="n">
-        <v>0.580479502677917</v>
+        <v>0.580479443073273</v>
       </c>
       <c r="H252" t="n">
         <v>288000</v>
@@ -7735,7 +7735,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G254" t="n">
-        <v>0.626473724842072</v>
+        <v>0.626473784446716</v>
       </c>
       <c r="H254" t="n">
         <v>97200</v>
@@ -7764,7 +7764,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G255" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H255" t="n">
         <v>39600</v>
@@ -7793,7 +7793,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G256" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H256" t="n">
         <v>27200</v>
@@ -7822,7 +7822,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G257" t="n">
-        <v>0.66533100605011</v>
+        <v>0.665330946445465</v>
       </c>
       <c r="H257" t="n">
         <v>88400</v>
@@ -7851,7 +7851,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G258" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H258" t="n">
         <v>111600</v>
@@ -8025,7 +8025,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G264" t="n">
-        <v>0.796969830989838</v>
+        <v>0.796969771385193</v>
       </c>
       <c r="H264" t="n">
         <v>3600</v>
@@ -8373,7 +8373,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G276" t="n">
-        <v>0.76524955034256</v>
+        <v>0.765249609947205</v>
       </c>
       <c r="H276" t="n">
         <v>8400</v>
@@ -8402,7 +8402,7 @@
         <v>0.968999981880188</v>
       </c>
       <c r="G277" t="n">
-        <v>0.768421590328217</v>
+        <v>0.768421649932861</v>
       </c>
       <c r="H277" t="n">
         <v>1200</v>
@@ -8460,7 +8460,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G279" t="n">
-        <v>0.788246691226959</v>
+        <v>0.788246750831604</v>
       </c>
       <c r="H279" t="n">
         <v>8800</v>
@@ -8489,7 +8489,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G280" t="n">
-        <v>0.788246691226959</v>
+        <v>0.788246750831604</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G282" t="n">
-        <v>0.792211711406708</v>
+        <v>0.792211771011353</v>
       </c>
       <c r="H282" t="n">
         <v>25600</v>
@@ -8576,7 +8576,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G283" t="n">
-        <v>0.769214689731598</v>
+        <v>0.769214630126953</v>
       </c>
       <c r="H283" t="n">
         <v>3200</v>
@@ -8605,7 +8605,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G284" t="n">
-        <v>0.754147469997406</v>
+        <v>0.754147529602051</v>
       </c>
       <c r="H284" t="n">
         <v>17600</v>
@@ -8634,7 +8634,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G285" t="n">
-        <v>0.721634328365326</v>
+        <v>0.721634387969971</v>
       </c>
       <c r="H285" t="n">
         <v>38400</v>
@@ -8692,7 +8692,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G287" t="n">
-        <v>0.666124045848846</v>
+        <v>0.666123986244202</v>
       </c>
       <c r="H287" t="n">
         <v>27200</v>
@@ -8721,7 +8721,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G288" t="n">
-        <v>0.647884845733643</v>
+        <v>0.647884905338287</v>
       </c>
       <c r="H288" t="n">
         <v>14800</v>
@@ -8779,7 +8779,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G290" t="n">
-        <v>0.642333805561066</v>
+        <v>0.64233386516571</v>
       </c>
       <c r="H290" t="n">
         <v>23200</v>
@@ -8837,7 +8837,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G292" t="n">
-        <v>0.662159025669098</v>
+        <v>0.662158966064453</v>
       </c>
       <c r="H292" t="n">
         <v>8000</v>
@@ -9040,7 +9040,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G299" t="n">
-        <v>0.674054086208344</v>
+        <v>0.674054026603699</v>
       </c>
       <c r="H299" t="n">
         <v>47200</v>
@@ -9069,7 +9069,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>0.689914107322693</v>
+        <v>0.689914166927338</v>
       </c>
       <c r="H300" t="n">
         <v>30800</v>
@@ -9098,7 +9098,7 @@
         <v>0.856500029563904</v>
       </c>
       <c r="G301" t="n">
-        <v>0.679208517074585</v>
+        <v>0.67920857667923</v>
       </c>
       <c r="H301" t="n">
         <v>12800</v>
@@ -9156,7 +9156,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G303" t="n">
-        <v>0.674054086208344</v>
+        <v>0.674054026603699</v>
       </c>
       <c r="H303" t="n">
         <v>6000</v>
@@ -9272,7 +9272,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G307" t="n">
-        <v>0.662951946258545</v>
+        <v>0.66295200586319</v>
       </c>
       <c r="H307" t="n">
         <v>5200</v>
@@ -9301,7 +9301,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G308" t="n">
-        <v>0.672864496707916</v>
+        <v>0.672864615917206</v>
       </c>
       <c r="H308" t="n">
         <v>2800</v>
@@ -9330,7 +9330,7 @@
         <v>0.84850001335144</v>
       </c>
       <c r="G309" t="n">
-        <v>0.672864496707916</v>
+        <v>0.672864615917206</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G310" t="n">
-        <v>0.674054086208344</v>
+        <v>0.674054026603699</v>
       </c>
       <c r="H310" t="n">
         <v>10400</v>
@@ -9388,7 +9388,7 @@
         <v>0.834999978542328</v>
       </c>
       <c r="G311" t="n">
-        <v>0.662159025669098</v>
+        <v>0.662158966064453</v>
       </c>
       <c r="H311" t="n">
         <v>50000</v>
@@ -9417,7 +9417,7 @@
         <v>0.817499995231628</v>
       </c>
       <c r="G312" t="n">
-        <v>0.648281395435333</v>
+        <v>0.648281455039978</v>
       </c>
       <c r="H312" t="n">
         <v>141600</v>
@@ -9446,7 +9446,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G313" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H313" t="n">
         <v>40800</v>
@@ -9504,7 +9504,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G315" t="n">
-        <v>0.650263845920563</v>
+        <v>0.650263905525208</v>
       </c>
       <c r="H315" t="n">
         <v>88400</v>
@@ -9562,7 +9562,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>0.649470865726471</v>
+        <v>0.649470925331116</v>
       </c>
       <c r="H317" t="n">
         <v>30000</v>
@@ -9591,7 +9591,7 @@
         <v>0.862500011920929</v>
       </c>
       <c r="G318" t="n">
-        <v>0.68396657705307</v>
+        <v>0.683966636657715</v>
       </c>
       <c r="H318" t="n">
         <v>142000</v>
@@ -9649,7 +9649,7 @@
         <v>0.869000017642975</v>
       </c>
       <c r="G320" t="n">
-        <v>0.689121127128601</v>
+        <v>0.689121067523956</v>
       </c>
       <c r="H320" t="n">
         <v>149200</v>
@@ -9678,7 +9678,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G321" t="n">
-        <v>0.689914107322693</v>
+        <v>0.689914166927338</v>
       </c>
       <c r="H321" t="n">
         <v>191200</v>
@@ -9794,7 +9794,7 @@
         <v>0.91100001335144</v>
       </c>
       <c r="G325" t="n">
-        <v>0.722427308559418</v>
+        <v>0.722427368164062</v>
       </c>
       <c r="H325" t="n">
         <v>19600</v>
@@ -9852,7 +9852,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G327" t="n">
-        <v>0.780316770076752</v>
+        <v>0.780316710472107</v>
       </c>
       <c r="H327" t="n">
         <v>180800</v>
@@ -9881,7 +9881,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G328" t="n">
-        <v>0.814415812492371</v>
+        <v>0.814415872097015</v>
       </c>
       <c r="H328" t="n">
         <v>216400</v>
@@ -9997,7 +9997,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G332" t="n">
-        <v>0.836619973182678</v>
+        <v>0.836620032787323</v>
       </c>
       <c r="H332" t="n">
         <v>138000</v>
@@ -10026,7 +10026,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G333" t="n">
-        <v>0.836619973182678</v>
+        <v>0.836620032787323</v>
       </c>
       <c r="H333" t="n">
         <v>26800</v>
@@ -10055,7 +10055,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G334" t="n">
-        <v>0.836619973182678</v>
+        <v>0.836620032787323</v>
       </c>
       <c r="H334" t="n">
         <v>52400</v>
@@ -10171,7 +10171,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G338" t="n">
-        <v>0.855652093887329</v>
+        <v>0.855652153491974</v>
       </c>
       <c r="H338" t="n">
         <v>66000</v>
@@ -10200,7 +10200,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G339" t="n">
-        <v>0.840584993362427</v>
+        <v>0.840584933757782</v>
       </c>
       <c r="H339" t="n">
         <v>91600</v>
@@ -10229,7 +10229,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G340" t="n">
-        <v>0.843757033348083</v>
+        <v>0.843757092952728</v>
       </c>
       <c r="H340" t="n">
         <v>73600</v>
@@ -10287,7 +10287,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G342" t="n">
-        <v>0.847011506557465</v>
+        <v>0.847011566162109</v>
       </c>
       <c r="H342" t="n">
         <v>92000</v>
@@ -10316,7 +10316,7 @@
         <v>1.0110000371933</v>
       </c>
       <c r="G343" t="n">
-        <v>0.843673586845398</v>
+        <v>0.843673646450043</v>
       </c>
       <c r="H343" t="n">
         <v>36400</v>
@@ -10403,7 +10403,7 @@
         <v>1.00899994373322</v>
       </c>
       <c r="G346" t="n">
-        <v>0.842004537582397</v>
+        <v>0.842004597187042</v>
       </c>
       <c r="H346" t="n">
         <v>32400</v>
@@ -10490,7 +10490,7 @@
         <v>0.988499999046326</v>
       </c>
       <c r="G349" t="n">
-        <v>0.824897527694702</v>
+        <v>0.824897468090057</v>
       </c>
       <c r="H349" t="n">
         <v>400</v>
@@ -10548,7 +10548,7 @@
         <v>0.964999973773956</v>
       </c>
       <c r="G351" t="n">
-        <v>0.805286824703217</v>
+        <v>0.805286884307861</v>
       </c>
       <c r="H351" t="n">
         <v>7200</v>
@@ -10606,7 +10606,7 @@
         <v>0.949500024318695</v>
       </c>
       <c r="G353" t="n">
-        <v>0.792352259159088</v>
+        <v>0.792352199554443</v>
       </c>
       <c r="H353" t="n">
         <v>20800</v>
@@ -10635,7 +10635,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G354" t="n">
-        <v>0.867039501667023</v>
+        <v>0.867039442062378</v>
       </c>
       <c r="H354" t="n">
         <v>297600</v>
@@ -10664,7 +10664,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>1.00139307975769</v>
+        <v>1.0013929605484</v>
       </c>
       <c r="H355" t="n">
         <v>810400</v>
@@ -10693,7 +10693,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G356" t="n">
-        <v>0.968013226985931</v>
+        <v>0.968013167381287</v>
       </c>
       <c r="H356" t="n">
         <v>754800</v>
@@ -10780,7 +10780,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G359" t="n">
-        <v>1.11071157455444</v>
+        <v>1.11071169376373</v>
       </c>
       <c r="H359" t="n">
         <v>314400</v>
@@ -10838,7 +10838,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G361" t="n">
-        <v>1.0848423242569</v>
+        <v>1.08484220504761</v>
       </c>
       <c r="H361" t="n">
         <v>28800</v>
@@ -10983,7 +10983,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>0.988875448703766</v>
+        <v>0.988875567913055</v>
       </c>
       <c r="H366" t="n">
         <v>155200</v>
@@ -11186,7 +11186,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G373" t="n">
-        <v>1.02976584434509</v>
+        <v>1.0297657251358</v>
       </c>
       <c r="H373" t="n">
         <v>79200</v>
@@ -11244,7 +11244,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G375" t="n">
-        <v>1.03894519805908</v>
+        <v>1.03894531726837</v>
       </c>
       <c r="H375" t="n">
         <v>6400</v>
@@ -11273,7 +11273,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G376" t="n">
-        <v>1.00139307975769</v>
+        <v>1.0013929605484</v>
       </c>
       <c r="H376" t="n">
         <v>47600</v>
@@ -11418,7 +11418,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G381" t="n">
-        <v>0.974689066410065</v>
+        <v>0.974689185619354</v>
       </c>
       <c r="H381" t="n">
         <v>11200</v>
@@ -11505,7 +11505,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G384" t="n">
-        <v>0.961337089538574</v>
+        <v>0.961337149143219</v>
       </c>
       <c r="H384" t="n">
         <v>13200</v>
@@ -11563,7 +11563,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G386" t="n">
-        <v>0.95466136932373</v>
+        <v>0.954661309719086</v>
       </c>
       <c r="H386" t="n">
         <v>22000</v>
@@ -11650,7 +11650,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G389" t="n">
-        <v>0.97802722454071</v>
+        <v>0.978027105331421</v>
       </c>
       <c r="H389" t="n">
         <v>7200</v>
@@ -11679,7 +11679,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G390" t="n">
-        <v>0.968013226985931</v>
+        <v>0.968013167381287</v>
       </c>
       <c r="H390" t="n">
         <v>20000</v>
@@ -11708,7 +11708,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G391" t="n">
-        <v>0.971351206302643</v>
+        <v>0.971351265907288</v>
       </c>
       <c r="H391" t="n">
         <v>7600</v>
@@ -11737,7 +11737,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G392" t="n">
-        <v>0.971351206302643</v>
+        <v>0.971351265907288</v>
       </c>
       <c r="H392" t="n">
         <v>2400</v>
@@ -11795,7 +11795,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G394" t="n">
-        <v>0.951323390007019</v>
+        <v>0.951323330402374</v>
       </c>
       <c r="H394" t="n">
         <v>26000</v>
@@ -11824,7 +11824,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G395" t="n">
-        <v>0.968013226985931</v>
+        <v>0.968013167381287</v>
       </c>
       <c r="H395" t="n">
         <v>9600</v>
@@ -11853,7 +11853,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G396" t="n">
-        <v>0.975523591041565</v>
+        <v>0.975523710250854</v>
       </c>
       <c r="H396" t="n">
         <v>20400</v>
@@ -11882,7 +11882,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G397" t="n">
-        <v>0.951323390007019</v>
+        <v>0.951323330402374</v>
       </c>
       <c r="H397" t="n">
         <v>4800</v>
@@ -11911,7 +11911,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G398" t="n">
-        <v>0.951323390007019</v>
+        <v>0.951323330402374</v>
       </c>
       <c r="H398" t="n">
         <v>5600</v>
@@ -11969,7 +11969,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G400" t="n">
-        <v>0.96384072303772</v>
+        <v>0.963840663433075</v>
       </c>
       <c r="H400" t="n">
         <v>50000</v>
@@ -11998,7 +11998,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.00139307975769</v>
+        <v>1.0013929605484</v>
       </c>
       <c r="H401" t="n">
         <v>25600</v>
@@ -12114,7 +12114,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G405" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H405" t="n">
         <v>6000</v>
@@ -12143,7 +12143,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G406" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H406" t="n">
         <v>36800</v>
@@ -12230,7 +12230,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G409" t="n">
-        <v>1.03894519805908</v>
+        <v>1.03894531726837</v>
       </c>
       <c r="H409" t="n">
         <v>22400</v>
@@ -12346,7 +12346,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G413" t="n">
-        <v>0.986372172832489</v>
+        <v>0.986372053623199</v>
       </c>
       <c r="H413" t="n">
         <v>21200</v>
@@ -12375,7 +12375,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G414" t="n">
-        <v>0.974689066410065</v>
+        <v>0.974689185619354</v>
       </c>
       <c r="H414" t="n">
         <v>14000</v>
@@ -12404,7 +12404,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G415" t="n">
-        <v>0.971351206302643</v>
+        <v>0.971351265907288</v>
       </c>
       <c r="H415" t="n">
         <v>30800</v>
@@ -12491,7 +12491,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G418" t="n">
-        <v>1.00139307975769</v>
+        <v>1.0013929605484</v>
       </c>
       <c r="H418" t="n">
         <v>15600</v>
@@ -12578,7 +12578,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G421" t="n">
-        <v>0.968013226985931</v>
+        <v>0.968013167381287</v>
       </c>
       <c r="H421" t="n">
         <v>800</v>
@@ -12752,7 +12752,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G427" t="n">
-        <v>0.97802722454071</v>
+        <v>0.978027105331421</v>
       </c>
       <c r="H427" t="n">
         <v>31600</v>
@@ -12781,7 +12781,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G428" t="n">
-        <v>1.00055861473083</v>
+        <v>1.00055849552155</v>
       </c>
       <c r="H428" t="n">
         <v>11200</v>
@@ -12810,7 +12810,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G429" t="n">
-        <v>0.98804098367691</v>
+        <v>0.9880411028862</v>
       </c>
       <c r="H429" t="n">
         <v>5200</v>
@@ -12839,7 +12839,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G430" t="n">
-        <v>1.00055861473083</v>
+        <v>1.00055849552155</v>
       </c>
       <c r="H430" t="n">
         <v>2800</v>
@@ -12897,7 +12897,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G432" t="n">
-        <v>0.96384072303772</v>
+        <v>0.963840663433075</v>
       </c>
       <c r="H432" t="n">
         <v>3200</v>
@@ -13013,7 +13013,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>0.96384072303772</v>
+        <v>0.963840663433075</v>
       </c>
       <c r="H436" t="n">
         <v>32400</v>
@@ -13042,7 +13042,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G437" t="n">
-        <v>0.96384072303772</v>
+        <v>0.963840663433075</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G438" t="n">
-        <v>0.91794353723526</v>
+        <v>0.917943596839905</v>
       </c>
       <c r="H438" t="n">
         <v>164800</v>
@@ -13129,7 +13129,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G440" t="n">
-        <v>0.91794353723526</v>
+        <v>0.917943596839905</v>
       </c>
       <c r="H440" t="n">
         <v>138000</v>
@@ -13245,7 +13245,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G444" t="n">
-        <v>0.932964503765106</v>
+        <v>0.932964444160461</v>
       </c>
       <c r="H444" t="n">
         <v>26400</v>
@@ -13274,7 +13274,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G445" t="n">
-        <v>0.935468018054962</v>
+        <v>0.935467958450317</v>
       </c>
       <c r="H445" t="n">
         <v>21600</v>
@@ -13390,7 +13390,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>0.949654340744019</v>
+        <v>0.949654281139374</v>
       </c>
       <c r="H449" t="n">
         <v>18400</v>
@@ -13419,7 +13419,7 @@
         <v>1.14400005340576</v>
       </c>
       <c r="G450" t="n">
-        <v>0.95466136932373</v>
+        <v>0.954661309719086</v>
       </c>
       <c r="H450" t="n">
         <v>4800</v>
@@ -13477,7 +13477,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G452" t="n">
-        <v>0.949654340744019</v>
+        <v>0.949654281139374</v>
       </c>
       <c r="H452" t="n">
         <v>32800</v>
@@ -13506,7 +13506,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G453" t="n">
-        <v>0.965509653091431</v>
+        <v>0.965509712696075</v>
       </c>
       <c r="H453" t="n">
         <v>68000</v>
@@ -13883,7 +13883,7 @@
         <v>1.51300001144409</v>
       </c>
       <c r="G466" t="n">
-        <v>1.26258969306946</v>
+        <v>1.26258957386017</v>
       </c>
       <c r="H466" t="n">
         <v>254400</v>
@@ -14144,7 +14144,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G475" t="n">
-        <v>1.31850075721741</v>
+        <v>1.31850063800812</v>
       </c>
       <c r="H475" t="n">
         <v>29200</v>
@@ -14289,7 +14289,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G480" t="n">
-        <v>1.16912627220154</v>
+        <v>1.16912615299225</v>
       </c>
       <c r="H480" t="n">
         <v>12000</v>
@@ -14405,7 +14405,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G484" t="n">
-        <v>1.15076744556427</v>
+        <v>1.15076732635498</v>
       </c>
       <c r="H484" t="n">
         <v>24000</v>
@@ -14463,7 +14463,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G486" t="n">
-        <v>1.15994679927826</v>
+        <v>1.15994691848755</v>
       </c>
       <c r="H486" t="n">
         <v>10000</v>
@@ -14492,7 +14492,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G487" t="n">
-        <v>1.17246437072754</v>
+        <v>1.17246425151825</v>
       </c>
       <c r="H487" t="n">
         <v>8800</v>
@@ -14608,7 +14608,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G491" t="n">
-        <v>1.15994679927826</v>
+        <v>1.15994691848755</v>
       </c>
       <c r="H491" t="n">
         <v>11600</v>
@@ -14637,7 +14637,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G492" t="n">
-        <v>1.16829180717468</v>
+        <v>1.16829168796539</v>
       </c>
       <c r="H492" t="n">
         <v>17200</v>
@@ -14985,7 +14985,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G504" t="n">
-        <v>1.15577435493469</v>
+        <v>1.15577447414398</v>
       </c>
       <c r="H504" t="n">
         <v>4800</v>
@@ -15014,7 +15014,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G505" t="n">
-        <v>1.15577435493469</v>
+        <v>1.15577447414398</v>
       </c>
       <c r="H505" t="n">
         <v>12800</v>
@@ -15043,7 +15043,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G506" t="n">
-        <v>1.09652519226074</v>
+        <v>1.09652531147003</v>
       </c>
       <c r="H506" t="n">
         <v>207600</v>
@@ -15188,7 +15188,7 @@
         <v>1.36300003528595</v>
       </c>
       <c r="G511" t="n">
-        <v>1.13741540908813</v>
+        <v>1.13741552829742</v>
       </c>
       <c r="H511" t="n">
         <v>19600</v>
@@ -16000,7 +16000,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G539" t="n">
-        <v>1.00139307975769</v>
+        <v>1.0013929605484</v>
       </c>
       <c r="H539" t="n">
         <v>48800</v>
@@ -16029,7 +16029,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G540" t="n">
-        <v>1.00139307975769</v>
+        <v>1.0013929605484</v>
       </c>
       <c r="H540" t="n">
         <v>18400</v>
@@ -16058,7 +16058,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>1.00139307975769</v>
+        <v>1.0013929605484</v>
       </c>
       <c r="H541" t="n">
         <v>9200</v>
@@ -16087,7 +16087,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>0.972185671329498</v>
+        <v>0.972185730934143</v>
       </c>
       <c r="H542" t="n">
         <v>2000</v>
@@ -16116,7 +16116,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G543" t="n">
-        <v>0.947150886058807</v>
+        <v>0.947150826454163</v>
       </c>
       <c r="H543" t="n">
         <v>27200</v>
@@ -16145,7 +16145,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G544" t="n">
-        <v>0.951323390007019</v>
+        <v>0.951323330402374</v>
       </c>
       <c r="H544" t="n">
         <v>21600</v>
@@ -16174,7 +16174,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G545" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H545" t="n">
         <v>107200</v>
@@ -16203,7 +16203,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G546" t="n">
-        <v>0.926288485527039</v>
+        <v>0.926288545131683</v>
       </c>
       <c r="H546" t="n">
         <v>20800</v>
@@ -16232,7 +16232,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G547" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H547" t="n">
         <v>5600</v>
@@ -16261,7 +16261,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G548" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H548" t="n">
         <v>3200</v>
@@ -16319,7 +16319,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G550" t="n">
-        <v>0.959668278694153</v>
+        <v>0.959668219089508</v>
       </c>
       <c r="H550" t="n">
         <v>41200</v>
@@ -16348,7 +16348,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G551" t="n">
-        <v>0.947150886058807</v>
+        <v>0.947150826454163</v>
       </c>
       <c r="H551" t="n">
         <v>61600</v>
@@ -16377,7 +16377,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G552" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H552" t="n">
         <v>15600</v>
@@ -16464,7 +16464,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G555" t="n">
-        <v>0.926288485527039</v>
+        <v>0.926288545131683</v>
       </c>
       <c r="H555" t="n">
         <v>32800</v>
@@ -16638,7 +16638,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G561" t="n">
-        <v>0.930460929870605</v>
+        <v>0.93046098947525</v>
       </c>
       <c r="H561" t="n">
         <v>6000</v>
@@ -16667,7 +16667,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G562" t="n">
-        <v>0.942978382110596</v>
+        <v>0.94297844171524</v>
       </c>
       <c r="H562" t="n">
         <v>11200</v>
@@ -16725,7 +16725,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G564" t="n">
-        <v>0.934633374214172</v>
+        <v>0.934633433818817</v>
       </c>
       <c r="H564" t="n">
         <v>2400</v>
@@ -16754,7 +16754,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G565" t="n">
-        <v>0.972185671329498</v>
+        <v>0.972185730934143</v>
       </c>
       <c r="H565" t="n">
         <v>10400</v>
@@ -16783,7 +16783,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G566" t="n">
-        <v>0.951323390007019</v>
+        <v>0.951323330402374</v>
       </c>
       <c r="H566" t="n">
         <v>33200</v>
@@ -16841,7 +16841,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G568" t="n">
-        <v>0.951323390007019</v>
+        <v>0.951323330402374</v>
       </c>
       <c r="H568" t="n">
         <v>2800</v>
@@ -16870,7 +16870,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>1.00973796844482</v>
+        <v>1.00973808765411</v>
       </c>
       <c r="H569" t="n">
         <v>29600</v>
@@ -16928,7 +16928,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G571" t="n">
-        <v>1.03060019016266</v>
+        <v>1.03060030937195</v>
       </c>
       <c r="H571" t="n">
         <v>4000</v>
@@ -17015,7 +17015,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G574" t="n">
-        <v>1.06398010253906</v>
+        <v>1.06397998332977</v>
       </c>
       <c r="H574" t="n">
         <v>18800</v>
@@ -17276,7 +17276,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G583" t="n">
-        <v>1.0848423242569</v>
+        <v>1.08484220504761</v>
       </c>
       <c r="H583" t="n">
         <v>18800</v>
@@ -17479,7 +17479,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G590" t="n">
-        <v>1.19332659244537</v>
+        <v>1.19332647323608</v>
       </c>
       <c r="H590" t="n">
         <v>18400</v>
@@ -17508,7 +17508,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G591" t="n">
-        <v>1.16829180717468</v>
+        <v>1.16829168796539</v>
       </c>
       <c r="H591" t="n">
         <v>14000</v>
@@ -17566,7 +17566,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G593" t="n">
-        <v>1.19332659244537</v>
+        <v>1.19332647323608</v>
       </c>
       <c r="H593" t="n">
         <v>14800</v>
@@ -17653,7 +17653,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>1.28512108325958</v>
+        <v>1.28512096405029</v>
       </c>
       <c r="H596" t="n">
         <v>419200</v>
@@ -80154,6 +80154,64 @@
         <v>1600</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.904999971389771</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.910000026226044</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.915000021457672</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>
